--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1064F231-231F-4985-92B0-37E26623AAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4BF94E-84A0-4148-928D-7D55855F8C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Graphic - Annual" sheetId="13" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Assets">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
+    <definedName name="Assets">'Balance &amp; Tracking'!$B$7:$B$9</definedName>
     <definedName name="Categories">Expenses!$A$7:$A$18</definedName>
     <definedName name="Dash">'Graphic - Annual'!$A$1:$P$26</definedName>
     <definedName name="Discount">'Net Salary'!$A$8:$A$12</definedName>
@@ -29,7 +29,7 @@
     <definedName name="Investments">'Net Salary'!$A$13:$A$14</definedName>
     <definedName name="Months">'Net Salary'!$B$2:$M$2</definedName>
     <definedName name="Net_Salary">'Net Salary'!$A$3:$A$14</definedName>
-    <definedName name="Transfer">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
+    <definedName name="Transfer">'Balance &amp; Tracking'!$B$7:$B$9</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
   <si>
     <t>Total</t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>Expenses</t>
-  </si>
-  <si>
-    <t>Type</t>
   </si>
   <si>
     <t>Balance</t>
@@ -298,6 +295,9 @@
   <si>
     <t>Bank Fee I</t>
   </si>
+  <si>
+    <t>SubTotal</t>
+  </si>
 </sst>
 </file>
 
@@ -348,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,12 +388,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,9 +660,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -678,8 +669,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -702,37 +691,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -774,19 +732,55 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9347,243 +9341,246 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="48" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="50" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="48" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="53" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="52" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="48" customWidth="1"/>
-    <col min="10" max="10" width="10" style="48" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="48"/>
+    <col min="1" max="1" width="11.42578125" style="67" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="65" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" style="66" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="67" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="70" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="69" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="67" customWidth="1"/>
+    <col min="10" max="10" width="10" style="67" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="67"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="79" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="52" t="str" cm="1">
-        <f t="array" ref="E3:E14">IF(C3="Expenses",Categories,IF(C3="Net Salary",Net_Salary,""))</f>
+      <c r="C3" s="45">
+        <f>IF(B3="Expenses",HLOOKUP(B2,Expenses!B2:M20,19,FALSE),IF(B3="Net Salary",HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE),""))</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="69" t="str" cm="1">
+        <f t="array" ref="E3:E14">IF(B3="Expenses",Categories,IF(B3="Net Salary",Net_Salary,""))</f>
         <v>Bills</v>
       </c>
-      <c r="F3" s="79" cm="1">
-        <f t="array" ref="F3:F14">IF(C3="Expenses",_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses!B2:M2=C2),IF(C3="Net Salary",_xlfn._xlws.FILTER('Net Salary'!B3:M14,'Net Salary'!B2:M2=C2),""))</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="48"/>
+      <c r="F3" s="77" cm="1">
+        <f t="array" ref="F3:F14">IF(B3="Expenses",_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses!B2:M2=B2),IF(B3="Net Salary",_xlfn._xlws.FILTER('Net Salary'!B3:M14,'Net Salary'!B2:M2=B2),""))</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="67"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="59">
-        <f>IF(C3="Expenses",HLOOKUP(C2,Expenses!B2:M20,19,FALSE),IF(C3="Net Salary",HLOOKUP(C2,'Net Salary'!B2:M16,15,FALSE),""))</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="52" t="str">
+        <v>22</v>
+      </c>
+      <c r="C4" s="45">
+        <f>VLOOKUP(B2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="69" t="str">
         <v>Car maintenance</v>
       </c>
-      <c r="F4" s="79">
-        <v>0</v>
-      </c>
-      <c r="H4" s="48"/>
+      <c r="F4" s="77">
+        <v>0</v>
+      </c>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="E5" s="52" t="str">
+      <c r="B5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="45">
+        <f>'Graphic - Annual'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="69" t="str">
         <v>Clothing</v>
       </c>
-      <c r="F5" s="79">
-        <v>0</v>
-      </c>
-      <c r="H5" s="48"/>
-    </row>
-    <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="59">
-        <f>VLOOKUP(C2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="52" t="str">
+      <c r="F5" s="77">
+        <v>0</v>
+      </c>
+      <c r="H5" s="67"/>
+    </row>
+    <row r="6" spans="1:8" ht="10.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="E6" s="69" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="F6" s="79">
-        <v>0</v>
-      </c>
-      <c r="H6" s="48"/>
+      <c r="F6" s="77">
+        <v>0</v>
+      </c>
+      <c r="H6" s="67"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="59">
-        <f>'Graphic - Annual'!I15</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="52" t="str">
+      <c r="C7" s="46" cm="1">
+        <f t="array" aca="1" ref="C7" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B7,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B7,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B7,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>150</v>
+      </c>
+      <c r="E7" s="69" t="str">
         <v>Food</v>
       </c>
-      <c r="F7" s="79">
-        <v>0</v>
-      </c>
-      <c r="H7" s="48"/>
+      <c r="F7" s="77">
+        <v>0</v>
+      </c>
+      <c r="H7" s="67"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="52" t="str">
+      <c r="B8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="46" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B8,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B8,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B8,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="69" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F8" s="79">
-        <v>0</v>
-      </c>
-      <c r="H8" s="48"/>
+      <c r="F8" s="77">
+        <v>0</v>
+      </c>
+      <c r="H8" s="67"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="60" cm="1">
+        <v>26</v>
+      </c>
+      <c r="C9" s="46" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="69" t="str">
+        <v>Hang out</v>
+      </c>
+      <c r="F9" s="77">
+        <v>0</v>
+      </c>
+      <c r="H9" s="67"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="66"/>
+      <c r="B10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="46">
+        <f ca="1">SUM(C7:C9)</f>
         <v>150</v>
       </c>
-      <c r="E9" s="52" t="str">
-        <v>Hang out</v>
-      </c>
-      <c r="F9" s="79">
-        <v>0</v>
-      </c>
-      <c r="H9" s="48"/>
-    </row>
-    <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="50"/>
-      <c r="B10" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="60" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="52" t="str">
+      <c r="E10" s="69" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="F10" s="79">
-        <v>0</v>
-      </c>
-      <c r="H10" s="48"/>
+      <c r="F10" s="77">
+        <v>0</v>
+      </c>
+      <c r="H10" s="67"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="50"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="60" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="52" t="str">
+        <v>28</v>
+      </c>
+      <c r="C11" s="45">
+        <f ca="1">ROUND(C4-C10,2)</f>
+        <v>-150</v>
+      </c>
+      <c r="E11" s="69" t="str">
         <v>Insurance</v>
       </c>
-      <c r="F11" s="79">
-        <v>0</v>
-      </c>
-      <c r="H11" s="48"/>
+      <c r="F11" s="77">
+        <v>0</v>
+      </c>
+      <c r="H11" s="67"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
-      <c r="B12" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="60">
-        <f ca="1">SUM(C9:C11)</f>
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="E12" s="69" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F12" s="77">
+        <v>0</v>
+      </c>
+      <c r="H12" s="67"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="66"/>
+      <c r="B13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="1">
+        <f>SUBTOTAL(9,Tabela1[Amount])</f>
         <v>150</v>
       </c>
-      <c r="E12" s="52" t="str">
-        <v>Personal Care</v>
-      </c>
-      <c r="F12" s="79">
-        <v>0</v>
-      </c>
-      <c r="H12" s="48"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50"/>
-      <c r="B13" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="59">
-        <f ca="1">ROUND(C6-C12,2)</f>
-        <v>-150</v>
-      </c>
-      <c r="E13" s="52" t="str">
+      <c r="E13" s="69" t="str">
         <v>Travel</v>
       </c>
-      <c r="F13" s="79">
-        <v>0</v>
-      </c>
-      <c r="H13" s="48"/>
+      <c r="F13" s="77">
+        <v>0</v>
+      </c>
+      <c r="H13" s="67"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="E14" s="52" t="str">
+      <c r="A14" s="66"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="E14" s="69" t="str">
         <v>General expen.</v>
       </c>
-      <c r="F14" s="80">
-        <v>0</v>
-      </c>
-      <c r="H14" s="48"/>
+      <c r="F14" s="76">
+        <v>0</v>
+      </c>
+      <c r="H14" s="67"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="48"/>
-      <c r="H15" s="48"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="67"/>
+      <c r="H15" s="67"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58">
+      <c r="A16" s="75">
         <f>SUBTOTAL(2,Tabela1[Date])</f>
         <v>1</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="F16" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -9595,15 +9592,15 @@
         <v>Janeiro</v>
       </c>
       <c r="D17" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>50</v>
-      </c>
       <c r="F17" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="61">
+        <v>24</v>
+      </c>
+      <c r="G17" s="47">
         <v>150</v>
       </c>
       <c r="H17" s="24"/>
@@ -9617,7 +9614,7 @@
       <c r="D18" s="22"/>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
-      <c r="G18" s="61"/>
+      <c r="G18" s="47"/>
       <c r="H18" s="24"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
@@ -9629,7 +9626,7 @@
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="61"/>
+      <c r="G19" s="47"/>
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -9641,3210 +9638,3210 @@
       <c r="D20" s="22"/>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
-      <c r="G20" s="61"/>
+      <c r="G20" s="47"/>
       <c r="H20" s="24"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="51"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="51"/>
+      <c r="G25" s="68"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="51"/>
+      <c r="G26" s="68"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="51"/>
+      <c r="G27" s="68"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="51"/>
+      <c r="G28" s="68"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="48" t="s">
+      <c r="I38" s="67" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="51"/>
+      <c r="G137" s="68"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="51"/>
+      <c r="G139" s="68"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="51"/>
+      <c r="G140" s="68"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="51"/>
+      <c r="G141" s="68"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="51"/>
+      <c r="G142" s="68"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="50" t="str">
+      <c r="C248" s="66" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="50" t="str">
+      <c r="C249" s="66" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="54"/>
+      <c r="G249" s="71"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="50" t="str">
+      <c r="C258" s="66" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="50" t="str">
+      <c r="D258" s="66" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="50" t="str">
+      <c r="E258" s="66" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="50" t="str">
+      <c r="F258" s="66" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="50" t="str">
+      <c r="G258" s="66" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="50" t="str">
+      <c r="C267" s="66" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="50" t="str">
+      <c r="C268" s="66" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="50" t="str">
+      <c r="C269" s="66" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="50" t="str">
+      <c r="C270" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="50" t="str">
+      <c r="C271" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="50" t="str">
+      <c r="C272" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="50" t="str">
+      <c r="C273" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="50" t="str">
+      <c r="C274" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="50" t="str">
+      <c r="C275" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="50" t="str">
+      <c r="C276" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="50" t="str">
+      <c r="C277" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="50" t="str">
+      <c r="C278" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="50" t="str">
+      <c r="C279" s="66" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="50" t="str">
+      <c r="C280" s="66" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="50" t="str">
+      <c r="C281" s="66" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="50" t="str">
+      <c r="C282" s="66" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="51"/>
-      <c r="H282" s="55"/>
+      <c r="G282" s="68"/>
+      <c r="H282" s="72"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="48"/>
-      <c r="C283" s="48"/>
-      <c r="D283" s="48"/>
-      <c r="E283" s="56"/>
-      <c r="F283" s="56"/>
-      <c r="G283" s="51"/>
-      <c r="H283" s="55"/>
+      <c r="B283" s="67"/>
+      <c r="C283" s="67"/>
+      <c r="D283" s="67"/>
+      <c r="E283" s="73"/>
+      <c r="F283" s="73"/>
+      <c r="G283" s="68"/>
+      <c r="H283" s="72"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="48"/>
-      <c r="C284" s="48"/>
-      <c r="D284" s="48"/>
-      <c r="E284" s="56"/>
-      <c r="F284" s="56"/>
-      <c r="G284" s="51"/>
-      <c r="H284" s="55"/>
+      <c r="B284" s="67"/>
+      <c r="C284" s="67"/>
+      <c r="D284" s="67"/>
+      <c r="E284" s="73"/>
+      <c r="F284" s="73"/>
+      <c r="G284" s="68"/>
+      <c r="H284" s="72"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="48"/>
-      <c r="C285" s="48"/>
-      <c r="D285" s="48"/>
-      <c r="E285" s="56"/>
-      <c r="F285" s="56"/>
-      <c r="G285" s="51"/>
-      <c r="H285" s="55"/>
+      <c r="B285" s="67"/>
+      <c r="C285" s="67"/>
+      <c r="D285" s="67"/>
+      <c r="E285" s="73"/>
+      <c r="F285" s="73"/>
+      <c r="G285" s="68"/>
+      <c r="H285" s="72"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="48"/>
-      <c r="C286" s="57"/>
-      <c r="D286" s="57"/>
-      <c r="E286" s="56"/>
-      <c r="F286" s="56"/>
-      <c r="G286" s="51"/>
-      <c r="H286" s="55"/>
+      <c r="B286" s="67"/>
+      <c r="C286" s="74"/>
+      <c r="D286" s="74"/>
+      <c r="E286" s="73"/>
+      <c r="F286" s="73"/>
+      <c r="G286" s="68"/>
+      <c r="H286" s="72"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="48"/>
-      <c r="C287" s="48"/>
-      <c r="D287" s="48"/>
-      <c r="G287" s="48"/>
+      <c r="B287" s="67"/>
+      <c r="C287" s="67"/>
+      <c r="D287" s="67"/>
+      <c r="G287" s="67"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="48"/>
-      <c r="C288" s="48"/>
-      <c r="D288" s="48"/>
-      <c r="G288" s="48"/>
+      <c r="B288" s="67"/>
+      <c r="C288" s="67"/>
+      <c r="D288" s="67"/>
+      <c r="G288" s="67"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="48"/>
-      <c r="C289" s="48"/>
-      <c r="D289" s="48"/>
-      <c r="G289" s="48"/>
+      <c r="B289" s="67"/>
+      <c r="C289" s="67"/>
+      <c r="D289" s="67"/>
+      <c r="G289" s="67"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="48"/>
-      <c r="C290" s="48"/>
-      <c r="D290" s="48"/>
-      <c r="G290" s="48"/>
+      <c r="B290" s="67"/>
+      <c r="C290" s="67"/>
+      <c r="D290" s="67"/>
+      <c r="G290" s="67"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="48"/>
-      <c r="C291" s="48"/>
-      <c r="D291" s="48"/>
-      <c r="G291" s="48"/>
+      <c r="B291" s="67"/>
+      <c r="C291" s="67"/>
+      <c r="D291" s="67"/>
+      <c r="G291" s="67"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="48"/>
-      <c r="C292" s="48"/>
-      <c r="D292" s="48"/>
-      <c r="G292" s="48"/>
+      <c r="B292" s="67"/>
+      <c r="C292" s="67"/>
+      <c r="D292" s="67"/>
+      <c r="G292" s="67"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="48"/>
-      <c r="C293" s="48"/>
-      <c r="D293" s="48"/>
-      <c r="G293" s="48"/>
+      <c r="B293" s="67"/>
+      <c r="C293" s="67"/>
+      <c r="D293" s="67"/>
+      <c r="G293" s="67"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="50" t="str">
+      <c r="C294" s="66" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="50" t="str">
+      <c r="C295" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="50" t="str">
+      <c r="C296" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="50" t="str">
+      <c r="C297" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="50" t="str">
+      <c r="C298" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="50" t="str">
+      <c r="C299" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="50" t="str">
+      <c r="C300" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="50" t="str">
+      <c r="C301" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="50" t="str">
+      <c r="C302" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="50" t="str">
+      <c r="C303" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="50" t="str">
+      <c r="C304" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="50" t="str">
+      <c r="C305" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="50" t="str">
+      <c r="C306" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="50" t="str">
+      <c r="C307" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="50" t="str">
+      <c r="C308" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="50" t="str">
+      <c r="C309" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="50" t="str">
+      <c r="C310" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="50" t="str">
+      <c r="C311" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="50" t="str">
+      <c r="C312" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="50" t="str">
+      <c r="C313" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="50" t="str">
+      <c r="C314" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="50" t="str">
+      <c r="C315" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="50" t="str">
+      <c r="C316" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="50" t="str">
+      <c r="C317" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="50" t="str">
+      <c r="C318" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="50" t="str">
+      <c r="C319" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="50" t="str">
+      <c r="C320" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="50" t="str">
+      <c r="C321" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="50" t="str">
+      <c r="C322" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="50" t="str">
+      <c r="C323" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="50" t="str">
+      <c r="C324" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="50" t="str">
+      <c r="C325" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="50" t="str">
+      <c r="C326" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="50" t="str">
+      <c r="C327" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="50" t="str">
+      <c r="C328" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="50" t="str">
+      <c r="C329" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="50" t="str">
+      <c r="C330" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="50" t="str">
+      <c r="C331" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="50" t="str">
+      <c r="C332" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="50" t="str">
+      <c r="C333" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="50" t="str">
+      <c r="C334" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="50" t="str">
+      <c r="C335" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="50" t="str">
+      <c r="C336" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="50" t="str">
+      <c r="C337" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="50" t="str">
+      <c r="C338" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="50" t="str">
+      <c r="C339" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="50" t="str">
+      <c r="C340" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="50" t="str">
+      <c r="C341" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="50" t="str">
+      <c r="C342" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="50" t="str">
+      <c r="C343" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="50" t="str">
+      <c r="C344" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="50" t="str">
+      <c r="C345" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="50" t="str">
+      <c r="C346" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="50" t="str">
+      <c r="C347" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="50" t="str">
+      <c r="C348" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="50" t="str">
+      <c r="C349" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="50" t="str">
+      <c r="C350" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="50" t="str">
+      <c r="C351" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="50" t="str">
+      <c r="C352" s="66" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="50" t="str">
+      <c r="C353" s="66" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="50" t="str">
+      <c r="C354" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="50" t="str">
+      <c r="C355" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="50" t="str">
+      <c r="C356" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="50" t="str">
+      <c r="C357" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="50" t="str">
+      <c r="C358" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="50" t="str">
+      <c r="C359" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="50" t="str">
+      <c r="C360" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="50" t="str">
+      <c r="C361" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="50" t="str">
+      <c r="C362" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="50" t="str">
+      <c r="C363" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="50" t="str">
+      <c r="C364" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="50" t="str">
+      <c r="C365" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="50" t="str">
+      <c r="C366" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="50" t="str">
+      <c r="C367" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="50" t="str">
+      <c r="C368" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="50" t="str">
+      <c r="C369" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="50" t="str">
+      <c r="C370" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="50" t="str">
+      <c r="C371" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="50" t="str">
+      <c r="C372" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="50" t="str">
+      <c r="C373" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="50" t="str">
+      <c r="C374" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="50" t="str">
+      <c r="C375" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="50" t="str">
+      <c r="C376" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="50" t="str">
+      <c r="C377" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="50" t="str">
+      <c r="C378" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="50" t="str">
+      <c r="C379" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="50" t="str">
+      <c r="C380" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="50" t="str">
+      <c r="C381" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="50" t="str">
+      <c r="C382" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="50" t="str">
+      <c r="C383" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="50" t="str">
+      <c r="C384" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="50" t="str">
+      <c r="C385" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="50" t="str">
+      <c r="C386" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="50" t="str">
+      <c r="C387" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="50" t="str">
+      <c r="C388" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="50" t="str">
+      <c r="C389" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="50" t="str">
+      <c r="C390" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="50" t="str">
+      <c r="C391" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="50" t="str">
+      <c r="C392" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="50" t="str">
+      <c r="C393" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="50" t="str">
+      <c r="C394" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="50" t="str">
+      <c r="C395" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="50" t="str">
+      <c r="C396" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="50" t="str">
+      <c r="C397" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="50" t="str">
+      <c r="C398" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="50" t="str">
+      <c r="C399" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="50" t="str">
+      <c r="C400" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="50" t="str">
+      <c r="C401" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="50" t="str">
+      <c r="C402" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="50" t="str">
+      <c r="C403" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="50" t="str">
+      <c r="C404" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="50" t="str">
+      <c r="C405" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="50" t="str">
+      <c r="C406" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="50" t="str">
+      <c r="C407" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="50" t="str">
+      <c r="C408" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="50" t="str">
+      <c r="C409" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="50" t="str">
+      <c r="C410" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="50" t="str">
+      <c r="C411" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="50" t="str">
+      <c r="C412" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="50" t="str">
+      <c r="C413" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="50" t="str">
+      <c r="C414" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="50" t="str">
+      <c r="C415" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="50" t="str">
+      <c r="C416" s="66" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="50" t="str">
+      <c r="C417" s="66" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="50" t="str">
+      <c r="C418" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="50" t="str">
+      <c r="C419" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="50" t="str">
+      <c r="C420" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="50" t="str">
+      <c r="C421" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="50" t="str">
+      <c r="C422" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="50" t="str">
+      <c r="C423" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="50" t="str">
+      <c r="C424" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="50" t="str">
+      <c r="C425" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="50" t="str">
+      <c r="C426" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="50" t="str">
+      <c r="C427" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="50" t="str">
+      <c r="C428" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="50" t="str">
+      <c r="C429" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="50" t="str">
+      <c r="C430" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="50" t="str">
+      <c r="C431" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="50" t="str">
+      <c r="C432" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="50" t="str">
+      <c r="C433" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="50" t="str">
+      <c r="C434" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="50" t="str">
+      <c r="C435" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="50" t="str">
+      <c r="C436" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="50" t="str">
+      <c r="C437" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="50" t="str">
+      <c r="C438" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="50" t="str">
+      <c r="C439" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="50" t="str">
+      <c r="C440" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="50" t="str">
+      <c r="C441" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="50" t="str">
+      <c r="C442" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="50" t="str">
+      <c r="C443" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="50" t="str">
+      <c r="C444" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="50" t="str">
+      <c r="C445" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="50" t="str">
+      <c r="C446" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="50" t="str">
+      <c r="C447" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="50" t="str">
+      <c r="C448" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="50" t="str">
+      <c r="C449" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="50" t="str">
+      <c r="C450" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="50" t="str">
+      <c r="C451" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="50" t="str">
+      <c r="C452" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="50" t="str">
+      <c r="C453" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="50" t="str">
+      <c r="C454" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="50" t="str">
+      <c r="C455" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="50" t="str">
+      <c r="C456" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="50" t="str">
+      <c r="C457" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="50" t="str">
+      <c r="C458" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="50" t="str">
+      <c r="C459" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="50" t="str">
+      <c r="C460" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="50" t="str">
+      <c r="C461" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="50" t="str">
+      <c r="C462" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="50" t="str">
+      <c r="C463" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="50" t="str">
+      <c r="C464" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="50" t="str">
+      <c r="C465" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="50" t="str">
+      <c r="C466" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="50" t="str">
+      <c r="C467" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="50" t="str">
+      <c r="C468" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="50" t="str">
+      <c r="C469" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="50" t="str">
+      <c r="C470" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="50" t="str">
+      <c r="C471" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="50" t="str">
+      <c r="C472" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="50" t="str">
+      <c r="C473" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="50" t="str">
+      <c r="C474" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="50" t="str">
+      <c r="C475" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="50" t="str">
+      <c r="C476" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="50" t="str">
+      <c r="C477" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="50" t="str">
+      <c r="C478" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="50" t="str">
+      <c r="C479" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="50" t="str">
+      <c r="C480" s="66" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="50" t="str">
+      <c r="C481" s="66" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="50" t="str">
+      <c r="C482" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="50" t="str">
+      <c r="C483" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="50" t="str">
+      <c r="C484" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="50" t="str">
+      <c r="C485" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="50" t="str">
+      <c r="C486" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="50" t="str">
+      <c r="C487" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="50" t="str">
+      <c r="C488" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="50" t="str">
+      <c r="C489" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="50" t="str">
+      <c r="C490" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="50" t="str">
+      <c r="C491" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="50" t="str">
+      <c r="C492" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="50" t="str">
+      <c r="C493" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="50" t="str">
+      <c r="C494" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="50" t="str">
+      <c r="C495" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="50" t="str">
+      <c r="C496" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="50" t="str">
+      <c r="C497" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="50" t="str">
+      <c r="C498" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="50" t="str">
+      <c r="C499" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="50" t="str">
+      <c r="C500" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="50" t="str">
+      <c r="C501" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="50" t="str">
+      <c r="C502" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="50" t="str">
+      <c r="C503" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="50" t="str">
+      <c r="C504" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="50" t="str">
+      <c r="C505" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="50" t="str">
+      <c r="C506" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="50" t="str">
+      <c r="C507" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="50" t="str">
+      <c r="C508" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="50" t="str">
+      <c r="C509" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="50" t="str">
+      <c r="C510" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="50" t="str">
+      <c r="C511" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="50" t="str">
+      <c r="C512" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="50" t="str">
+      <c r="C513" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="50" t="str">
+      <c r="C514" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="50" t="str">
+      <c r="C515" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="50" t="str">
+      <c r="C516" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="50" t="str">
+      <c r="C517" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="50" t="str">
+      <c r="C518" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="50" t="str">
+      <c r="C519" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="50" t="str">
+      <c r="C520" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="50" t="str">
+      <c r="C521" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="50" t="str">
+      <c r="C522" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="50" t="str">
+      <c r="C523" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="50" t="str">
+      <c r="C524" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="50" t="str">
+      <c r="C525" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="50" t="str">
+      <c r="C526" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="50" t="str">
+      <c r="C527" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="50" t="str">
+      <c r="C528" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="50" t="str">
+      <c r="C529" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="50" t="str">
+      <c r="C530" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="50" t="str">
+      <c r="C531" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="50" t="str">
+      <c r="C532" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="50" t="str">
+      <c r="C533" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="50" t="str">
+      <c r="C534" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="50" t="str">
+      <c r="C535" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="50" t="str">
+      <c r="C536" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="50" t="str">
+      <c r="C537" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="50" t="str">
+      <c r="C538" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="50" t="str">
+      <c r="C539" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="50" t="str">
+      <c r="C540" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="50" t="str">
+      <c r="C541" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="50" t="str">
+      <c r="C542" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="50" t="str">
+      <c r="C543" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="50" t="str">
+      <c r="C544" s="66" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="50" t="str">
+      <c r="C545" s="66" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="50" t="str">
+      <c r="C546" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="50" t="str">
+      <c r="C547" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="50" t="str">
+      <c r="C548" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="50" t="str">
+      <c r="C549" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="50" t="str">
+      <c r="C550" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="50" t="str">
+      <c r="C551" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="50" t="str">
+      <c r="C552" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="50" t="str">
+      <c r="C553" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="50" t="str">
+      <c r="C554" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="50" t="str">
+      <c r="C555" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="50" t="str">
+      <c r="C556" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="50" t="str">
+      <c r="C557" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="50" t="str">
+      <c r="C558" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="50" t="str">
+      <c r="C559" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="50" t="str">
+      <c r="C560" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="50" t="str">
+      <c r="C561" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="50" t="str">
+      <c r="C562" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="50" t="str">
+      <c r="C563" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="50" t="str">
+      <c r="C564" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="50" t="str">
+      <c r="C565" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="50" t="str">
+      <c r="C566" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="50" t="str">
+      <c r="C567" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="50" t="str">
+      <c r="C568" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="50" t="str">
+      <c r="C569" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="50" t="str">
+      <c r="C570" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="50" t="str">
+      <c r="C571" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="50" t="str">
+      <c r="C572" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="50" t="str">
+      <c r="C573" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="50" t="str">
+      <c r="C574" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="50" t="str">
+      <c r="C575" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="50" t="str">
+      <c r="C576" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="50" t="str">
+      <c r="C577" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="50" t="str">
+      <c r="C578" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="50" t="str">
+      <c r="C579" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="50" t="str">
+      <c r="C580" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="50" t="str">
+      <c r="C581" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="50" t="str">
+      <c r="C582" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="50" t="str">
+      <c r="C583" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="50" t="str">
+      <c r="C584" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="50" t="str">
+      <c r="C585" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="50" t="str">
+      <c r="C586" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="50" t="str">
+      <c r="C587" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="50" t="str">
+      <c r="C588" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="50" t="str">
+      <c r="C589" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="50" t="str">
+      <c r="C590" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="50" t="str">
+      <c r="C591" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="50" t="str">
+      <c r="C592" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="50" t="str">
+      <c r="C593" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="50" t="str">
+      <c r="C594" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="50" t="str">
+      <c r="C595" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="50" t="str">
+      <c r="C596" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="50" t="str">
+      <c r="C597" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="50" t="str">
+      <c r="C598" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="50" t="str">
+      <c r="C599" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="50" t="str">
+      <c r="C600" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="50" t="str">
+      <c r="C601" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="50" t="str">
+      <c r="C602" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="50" t="str">
+      <c r="C603" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="50" t="str">
+      <c r="C604" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="50" t="str">
+      <c r="C605" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="50" t="str">
+      <c r="C606" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="50" t="str">
+      <c r="C607" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="50" t="str">
+      <c r="C608" s="66" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="50" t="str">
+      <c r="C609" s="66" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="50" t="str">
+      <c r="C610" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="50" t="str">
+      <c r="C611" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="50" t="str">
+      <c r="C612" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="50" t="str">
+      <c r="C613" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="50" t="str">
+      <c r="C614" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="50" t="str">
+      <c r="C615" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="50" t="str">
+      <c r="C616" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="50" t="str">
+      <c r="C617" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="50" t="str">
+      <c r="C618" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="50" t="str">
+      <c r="C619" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="50" t="str">
+      <c r="C620" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="50" t="str">
+      <c r="C621" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="50" t="str">
+      <c r="C622" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="50" t="str">
+      <c r="C623" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="50" t="str">
+      <c r="C624" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="50" t="str">
+      <c r="C625" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="50" t="str">
+      <c r="C626" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="50" t="str">
+      <c r="C627" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="50" t="str">
+      <c r="C628" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="50" t="str">
+      <c r="C629" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="50" t="str">
+      <c r="C630" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="50" t="str">
+      <c r="C631" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="50" t="str">
+      <c r="C632" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="50" t="str">
+      <c r="C633" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="50" t="str">
+      <c r="C634" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="50" t="str">
+      <c r="C635" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="50" t="str">
+      <c r="C636" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="50" t="str">
+      <c r="C637" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="50" t="str">
+      <c r="C638" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="50" t="str">
+      <c r="C639" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="50" t="str">
+      <c r="C640" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="50" t="str">
+      <c r="C641" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="50" t="str">
+      <c r="C642" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="50" t="str">
+      <c r="C643" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="50" t="str">
+      <c r="C644" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="50" t="str">
+      <c r="C645" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="50" t="str">
+      <c r="C646" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="50" t="str">
+      <c r="C647" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="50" t="str">
+      <c r="C648" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="50" t="str">
+      <c r="C649" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="50" t="str">
+      <c r="C650" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="50" t="str">
+      <c r="C651" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="50" t="str">
+      <c r="C652" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="50" t="str">
+      <c r="C653" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="50" t="str">
+      <c r="C654" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="50" t="str">
+      <c r="C655" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="50" t="str">
+      <c r="C656" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="50" t="str">
+      <c r="C657" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="50" t="str">
+      <c r="C658" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="50" t="str">
+      <c r="C659" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="50" t="str">
+      <c r="C660" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="50" t="str">
+      <c r="C661" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="50" t="str">
+      <c r="C662" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="50" t="str">
+      <c r="C663" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="50" t="str">
+      <c r="C664" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="50" t="str">
+      <c r="C665" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="50" t="str">
+      <c r="C666" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="50" t="str">
+      <c r="C667" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="50" t="str">
+      <c r="C668" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="50" t="str">
+      <c r="C669" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="50" t="str">
+      <c r="C670" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="50" t="str">
+      <c r="C671" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="50" t="str">
+      <c r="C672" s="66" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="50" t="str">
+      <c r="C673" s="66" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="50" t="str">
+      <c r="C674" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="50" t="str">
+      <c r="C675" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="50" t="str">
+      <c r="C676" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="50" t="str">
+      <c r="C677" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="50" t="str">
+      <c r="C678" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="50" t="str">
+      <c r="C679" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="50" t="str">
+      <c r="C680" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="50" t="str">
+      <c r="C681" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="50" t="str">
+      <c r="C682" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="50" t="str">
+      <c r="C683" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="50" t="str">
+      <c r="C684" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="50" t="str">
+      <c r="C685" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="50" t="str">
+      <c r="C686" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="50" t="str">
+      <c r="C687" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="50" t="str">
+      <c r="C688" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="50" t="str">
+      <c r="C689" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="50" t="str">
+      <c r="C690" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="50" t="str">
+      <c r="C691" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="50" t="str">
+      <c r="C692" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="50" t="str">
+      <c r="C693" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="50" t="str">
+      <c r="C694" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="50" t="str">
+      <c r="C695" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="50" t="str">
+      <c r="C696" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="50" t="str">
+      <c r="C697" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="50" t="str">
+      <c r="C698" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="50" t="str">
+      <c r="C699" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="50" t="str">
+      <c r="C700" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="50" t="str">
+      <c r="C701" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="50" t="str">
+      <c r="C702" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="50" t="str">
+      <c r="C703" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="50" t="str">
+      <c r="C704" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="50" t="str">
+      <c r="C705" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="50" t="str">
+      <c r="C706" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="50" t="str">
+      <c r="C707" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="50" t="str">
+      <c r="C708" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="50" t="str">
+      <c r="C709" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="50" t="str">
+      <c r="C710" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="50" t="str">
+      <c r="C711" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="50" t="str">
+      <c r="C712" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="50" t="str">
+      <c r="C713" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="50" t="str">
+      <c r="C714" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="50" t="str">
+      <c r="C715" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="50" t="str">
+      <c r="C716" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="50" t="str">
+      <c r="C717" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="50" t="str">
+      <c r="C718" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="50" t="str">
+      <c r="C719" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="50" t="str">
+      <c r="C720" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="50" t="str">
+      <c r="C721" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="50" t="str">
+      <c r="C722" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="50" t="str">
+      <c r="C723" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="50" t="str">
+      <c r="C724" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="50" t="str">
+      <c r="C725" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="50" t="str">
+      <c r="C726" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="50" t="str">
+      <c r="C727" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="50" t="str">
+      <c r="C728" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="50" t="str">
+      <c r="C729" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="50" t="str">
+      <c r="C730" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="50" t="str">
+      <c r="C731" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="50" t="str">
+      <c r="C732" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="50" t="str">
+      <c r="C733" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="50" t="str">
+      <c r="C734" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="50" t="str">
+      <c r="C735" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="50" t="str">
+      <c r="C736" s="66" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="50" t="str">
+      <c r="C737" s="66" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="50" t="str">
+      <c r="C738" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="50" t="str">
+      <c r="C739" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="50" t="str">
+      <c r="C740" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="50" t="str">
+      <c r="C741" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="50" t="str">
+      <c r="C742" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="50" t="str">
+      <c r="C743" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="50" t="str">
+      <c r="C744" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="50" t="str">
+      <c r="C745" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="50" t="str">
+      <c r="C746" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="50" t="str">
+      <c r="C747" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="50" t="str">
+      <c r="C748" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="50" t="str">
+      <c r="C749" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="50" t="str">
+      <c r="C750" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="50" t="str">
+      <c r="C751" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="50" t="str">
+      <c r="C752" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="50" t="str">
+      <c r="C753" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="50" t="str">
+      <c r="C754" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="50" t="str">
+      <c r="C755" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="50" t="str">
+      <c r="C756" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="50" t="str">
+      <c r="C757" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="50" t="str">
+      <c r="C758" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="50" t="str">
+      <c r="C759" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="50" t="str">
+      <c r="C760" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="50" t="str">
+      <c r="C761" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="50" t="str">
+      <c r="C762" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="50" t="str">
+      <c r="C763" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="50" t="str">
+      <c r="C764" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="50" t="str">
+      <c r="C765" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="50" t="str">
+      <c r="C766" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="50" t="str">
+      <c r="C767" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="50" t="str">
+      <c r="C768" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="50" t="str">
+      <c r="C769" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="50" t="str">
+      <c r="C770" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="50" t="str">
+      <c r="C771" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="50" t="str">
+      <c r="C772" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="50" t="str">
+      <c r="C773" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="50" t="str">
+      <c r="C774" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="50" t="str">
+      <c r="C775" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="50" t="str">
+      <c r="C776" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="50" t="str">
+      <c r="C777" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="50" t="str">
+      <c r="C778" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="50" t="str">
+      <c r="C779" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="50" t="str">
+      <c r="C780" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="50" t="str">
+      <c r="C781" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="50" t="str">
+      <c r="C782" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="50" t="str">
+      <c r="C783" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="50" t="str">
+      <c r="C784" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="50" t="str">
+      <c r="C785" s="66" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C13">
+  <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -12853,7 +12850,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Expenses, Net Salary"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E257" xr:uid="{E4F2BDDC-1223-4DFF-8087-7B85DF038B73}">
@@ -12882,7 +12879,7 @@
           <x14:formula1>
             <xm:f>'Net Salary'!$B$2:$M$2</xm:f>
           </x14:formula1>
-          <xm:sqref>C2</xm:sqref>
+          <xm:sqref>B2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12906,675 +12903,675 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="B4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="B7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
+      <c r="B11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="B12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43" t="s">
+      <c r="B13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="60">
+      <c r="B14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="60">
+      <c r="G14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="60">
+      <c r="H14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="60">
+      <c r="I14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="60">
+      <c r="J14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="60">
+      <c r="K14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="60">
+      <c r="L14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="60">
+      <c r="M14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
@@ -13583,51 +13580,51 @@
       <c r="A16" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="60">
+      <c r="B16" s="46">
         <f>ROUND(SUM(B3:B7)-SUM(B8:B14),2)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="46">
         <f t="shared" ref="C16:M16" si="0">ROUND(SUM(C3:C7)-SUM(C8:C14),2)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="60">
+      <c r="J16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="60">
+      <c r="K16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="60">
+      <c r="L16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M16" s="60">
+      <c r="M16" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -13701,157 +13698,157 @@
   <dimension ref="A2:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="36" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="36" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="36" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="36" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="36"/>
+    <col min="1" max="1" width="17.140625" style="35" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="35" customWidth="1"/>
+    <col min="5" max="10" width="17.85546875" style="35" customWidth="1"/>
+    <col min="11" max="13" width="17.7109375" style="35" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="35"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="34" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36"/>
-      <c r="B2" s="33" t="s">
+    <row r="2" spans="1:13" s="33" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35"/>
+      <c r="B2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="60">
+    <row r="3" spans="1:13" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="46">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="C3" s="60">
+      <c r="C3" s="46">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="60">
+      <c r="D3" s="46">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="46">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="46">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="60">
+      <c r="G3" s="46">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="46">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="60">
+      <c r="I3" s="46">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="60">
+      <c r="J3" s="46">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="60">
+      <c r="K3" s="46">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="60">
+      <c r="L3" s="46">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="60">
+      <c r="M3" s="46">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="74">
+      <c r="A4" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="60">
         <f>B3-(SUM(B7:B18))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="60">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="74">
+      <c r="G4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="74">
+      <c r="H4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="74">
+      <c r="I4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="74">
+      <c r="J4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="74">
+      <c r="K4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="74">
+      <c r="L4" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="74">
+      <c r="M4" s="60">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>0</v>
       </c>
@@ -13872,307 +13869,307 @@
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="47" t="s">
+      <c r="A6" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="47" t="s">
+      <c r="H6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="L6" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="M6" s="44" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="60">
+        <v>57</v>
+      </c>
+      <c r="B7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="60">
+      <c r="I7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="60">
+      <c r="K7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="60">
+      <c r="M7" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="60">
+        <v>58</v>
+      </c>
+      <c r="B8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="60">
+      <c r="K8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="60">
+      <c r="M8" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="60">
+        <v>59</v>
+      </c>
+      <c r="B9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="60">
+      <c r="H9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="60">
+      <c r="K9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="60">
+      <c r="L9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="60">
+      <c r="M9" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="60">
+        <v>60</v>
+      </c>
+      <c r="B10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="60">
+      <c r="G10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="60">
+      <c r="I10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="60">
+      <c r="K10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="60">
+      <c r="M10" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="60">
+        <v>56</v>
+      </c>
+      <c r="B11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="60">
+      <c r="G11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="60">
+      <c r="J11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="60">
+      <c r="K11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="60">
+      <c r="L11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="60">
+      <c r="M11" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
@@ -14181,440 +14178,440 @@
       <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="60">
+      <c r="I12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="60">
+      <c r="J12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="60">
+      <c r="K12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="60">
+      <c r="M12" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="46">
+        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="60">
-        <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="81" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="60">
+      <c r="B14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="60">
+      <c r="D14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="60">
+      <c r="E14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="60">
+      <c r="G14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="60">
+      <c r="H14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="60">
+      <c r="I14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="60">
+      <c r="J14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="60">
+      <c r="K14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="60">
+      <c r="L14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="60">
+      <c r="M14" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="60">
+        <v>71</v>
+      </c>
+      <c r="B15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="60">
+      <c r="G15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="60">
+      <c r="H15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="60">
+      <c r="I15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="60">
+      <c r="L15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="60">
+      <c r="M15" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="60">
+        <v>69</v>
+      </c>
+      <c r="B16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="60">
+      <c r="J16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="60">
+      <c r="K16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="60">
+      <c r="L16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="60">
+      <c r="M16" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="60">
+        <v>70</v>
+      </c>
+      <c r="B17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="60">
+      <c r="F17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="60">
+      <c r="G17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="60">
+      <c r="H17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="60">
+      <c r="J17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="60">
+      <c r="K17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="60">
+      <c r="L17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="60">
+      <c r="M17" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="60">
+        <v>63</v>
+      </c>
+      <c r="B18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="60">
+      <c r="E18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="60">
+      <c r="F18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="60">
+      <c r="G18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="60">
+      <c r="H18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="60">
+      <c r="I18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="60">
+      <c r="J18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="60">
+      <c r="K18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="60">
+      <c r="L18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="60">
+      <c r="M18" s="46">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-    </row>
-    <row r="20" spans="1:14" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="75">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+    </row>
+    <row r="20" spans="1:14" s="34" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="61">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="75">
+      <c r="H20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="75">
+      <c r="I20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="75">
+      <c r="J20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="75">
+      <c r="K20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="75">
+      <c r="L20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="75">
+      <c r="M20" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="37"/>
+      <c r="N20" s="36"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -14656,231 +14653,231 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="2" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="2"/>
-    <col min="14" max="14" width="7.140625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8.5703125" style="80" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="80" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="80" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="80" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="80" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="80" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="80"/>
+    <col min="14" max="14" width="7.140625" style="80" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="80"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I2" s="29" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="41">
+      <c r="B3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="38">
         <f>SUM(C6:C17)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="41">
+      <c r="I3" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="38">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="81" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="str" cm="1">
+      <c r="B6" s="80" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="C6" s="76" cm="1">
+      <c r="C6" s="82" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic - Categories'!C2))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="str" cm="1">
+      <c r="I6" s="80" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="J6" s="76" cm="1">
+      <c r="J6" s="82" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Categories='Graphic - Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="80" t="str">
         <v>February</v>
       </c>
-      <c r="C7" s="76">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="str">
+      <c r="C7" s="82">
+        <v>0</v>
+      </c>
+      <c r="I7" s="80" t="str">
         <v>February</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="str">
+      <c r="B8" s="80" t="str">
         <v>March</v>
       </c>
-      <c r="C8" s="76">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="str">
+      <c r="C8" s="82">
+        <v>0</v>
+      </c>
+      <c r="I8" s="80" t="str">
         <v>March</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="str">
+      <c r="B9" s="80" t="str">
         <v>April</v>
       </c>
-      <c r="C9" s="76">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="str">
+      <c r="C9" s="82">
+        <v>0</v>
+      </c>
+      <c r="I9" s="80" t="str">
         <v>April</v>
       </c>
-      <c r="J9" s="76">
+      <c r="J9" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="str">
+      <c r="B10" s="80" t="str">
         <v>May</v>
       </c>
-      <c r="C10" s="76">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="str">
+      <c r="C10" s="82">
+        <v>0</v>
+      </c>
+      <c r="I10" s="80" t="str">
         <v>May</v>
       </c>
-      <c r="J10" s="76">
+      <c r="J10" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="str">
+      <c r="B11" s="80" t="str">
         <v>June</v>
       </c>
-      <c r="C11" s="76">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="str">
+      <c r="C11" s="82">
+        <v>0</v>
+      </c>
+      <c r="I11" s="80" t="str">
         <v>June</v>
       </c>
-      <c r="J11" s="76">
+      <c r="J11" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="str">
+      <c r="B12" s="80" t="str">
         <v>July</v>
       </c>
-      <c r="C12" s="76">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="str">
+      <c r="C12" s="82">
+        <v>0</v>
+      </c>
+      <c r="I12" s="80" t="str">
         <v>July</v>
       </c>
-      <c r="J12" s="76">
+      <c r="J12" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="str">
+      <c r="B13" s="80" t="str">
         <v>August</v>
       </c>
-      <c r="C13" s="76">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="str">
+      <c r="C13" s="82">
+        <v>0</v>
+      </c>
+      <c r="I13" s="80" t="str">
         <v>August</v>
       </c>
-      <c r="J13" s="76">
+      <c r="J13" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="str">
+      <c r="B14" s="80" t="str">
         <v>September</v>
       </c>
-      <c r="C14" s="76">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="str">
+      <c r="C14" s="82">
+        <v>0</v>
+      </c>
+      <c r="I14" s="80" t="str">
         <v>September</v>
       </c>
-      <c r="J14" s="76">
+      <c r="J14" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="str">
+      <c r="B15" s="80" t="str">
         <v>October</v>
       </c>
-      <c r="C15" s="76">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2" t="str">
+      <c r="C15" s="82">
+        <v>0</v>
+      </c>
+      <c r="I15" s="80" t="str">
         <v>October</v>
       </c>
-      <c r="J15" s="76">
+      <c r="J15" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="str">
+      <c r="B16" s="80" t="str">
         <v>November</v>
       </c>
-      <c r="C16" s="76">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="str">
+      <c r="C16" s="82">
+        <v>0</v>
+      </c>
+      <c r="I16" s="80" t="str">
         <v>November</v>
       </c>
-      <c r="J16" s="76">
+      <c r="J16" s="82">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="str">
+      <c r="B17" s="80" t="str">
         <v>December</v>
       </c>
-      <c r="C17" s="76">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="str">
+      <c r="C17" s="82">
+        <v>0</v>
+      </c>
+      <c r="I17" s="80" t="str">
         <v>December</v>
       </c>
-      <c r="J17" s="76">
+      <c r="J17" s="82">
         <v>0</v>
       </c>
     </row>
@@ -14934,10 +14931,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3" t="s">
@@ -14945,52 +14942,52 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="83"/>
+      <c r="K2" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="64"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="82" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" s="83"/>
+      <c r="N2" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="64"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="62">
+      <c r="C3" s="48">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="49">
         <f>SUM('Net Salary'!B$13:B$14)</f>
         <v>0</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="68">
+      <c r="F3" s="54">
         <f>SUM(Expenses!B20:B20)</f>
         <v>0</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="62">
+      <c r="H3" s="48">
         <f>I3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="65">
+      <c r="I3" s="51">
         <f>Expenses!B4</f>
         <v>0</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="63">
+        <v>42</v>
+      </c>
+      <c r="L3" s="49">
         <f>SUM('Net Salary'!B3:M7)</f>
         <v>0</v>
       </c>
@@ -14999,7 +14996,7 @@
         <f t="array" ref="N3:N14">Categories</f>
         <v>Bills</v>
       </c>
-      <c r="O3" s="72">
+      <c r="O3" s="58">
         <f>SUM(Expenses!B7:M7)</f>
         <v>0</v>
       </c>
@@ -15009,32 +15006,32 @@
         <v>8</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="62">
+      <c r="C4" s="48">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="49">
         <f>SUM('Net Salary'!C$13:C$14)</f>
         <v>0</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="68">
+      <c r="F4" s="54">
         <f>SUM(Expenses!C20:C20)</f>
         <v>0</v>
       </c>
       <c r="G4" s="7"/>
-      <c r="H4" s="62">
+      <c r="H4" s="48">
         <f t="shared" ref="H4:H14" si="0">I4-I3</f>
         <v>0</v>
       </c>
-      <c r="I4" s="65">
+      <c r="I4" s="51">
         <f>Expenses!C4</f>
         <v>0</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="63">
+        <v>43</v>
+      </c>
+      <c r="L4" s="49">
         <f>SUM('Net Salary'!B8:M12)</f>
         <v>0</v>
       </c>
@@ -15042,7 +15039,7 @@
       <c r="N4" s="28" t="str">
         <v>Car maintenance</v>
       </c>
-      <c r="O4" s="72">
+      <c r="O4" s="58">
         <f>SUM(Expenses!B8:M8)</f>
         <v>0</v>
       </c>
@@ -15052,32 +15049,32 @@
         <v>9</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="62">
+      <c r="C5" s="48">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="49">
         <f>SUM('Net Salary'!D$13:D$14)</f>
         <v>0</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="68">
+      <c r="F5" s="54">
         <f>SUM(Expenses!D20:D20)</f>
         <v>0</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="62">
+      <c r="H5" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="65">
+      <c r="I5" s="51">
         <f>Expenses!D4</f>
         <v>0</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="63">
+        <v>36</v>
+      </c>
+      <c r="L5" s="49">
         <f>SUM('Net Salary'!B16:M16)</f>
         <v>0</v>
       </c>
@@ -15085,7 +15082,7 @@
       <c r="N5" s="28" t="str">
         <v>Clothing</v>
       </c>
-      <c r="O5" s="72">
+      <c r="O5" s="58">
         <f>SUM(Expenses!B9:M9)</f>
         <v>0</v>
       </c>
@@ -15095,32 +15092,32 @@
         <v>10</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="62">
+      <c r="C6" s="48">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="49">
         <f>SUM('Net Salary'!E$13:E$14)</f>
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="68">
+      <c r="F6" s="54">
         <f>SUM(Expenses!E20:E20)</f>
         <v>0</v>
       </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="62">
+      <c r="H6" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="51">
         <f>Expenses!E4</f>
         <v>0</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="63">
+        <v>44</v>
+      </c>
+      <c r="L6" s="49">
         <f>SUM(Expenses!B7:B17,Expenses!C7:C17,Expenses!D7:D17,Expenses!E7:E17,Expenses!F7:F17,Expenses!G7:G17,Expenses!H7:H17,Expenses!I7:I17,Expenses!J7:J17,Expenses!K7:K17,Expenses!L7:L17,Expenses!M7:M17)</f>
         <v>0</v>
       </c>
@@ -15128,7 +15125,7 @@
       <c r="N6" s="28" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="O6" s="72">
+      <c r="O6" s="58">
         <f>SUM(Expenses!B10:M10)</f>
         <v>0</v>
       </c>
@@ -15138,32 +15135,32 @@
         <v>11</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="62">
+      <c r="C7" s="48">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="49">
         <f>SUM('Net Salary'!F$13:F$14)</f>
         <v>0</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="68">
+      <c r="F7" s="54">
         <f>SUM(Expenses!F20:F20)</f>
         <v>0</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="62">
+      <c r="H7" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="51">
         <f>Expenses!F4</f>
         <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="63">
+        <v>45</v>
+      </c>
+      <c r="L7" s="49">
         <f>SUM(Expenses!B18:B18,Expenses!C18:C18,Expenses!D18:D18,Expenses!E18:E18,Expenses!F18:F18,Expenses!G18:G18,Expenses!H18:H18,Expenses!I18:I18,Expenses!J18:J18,Expenses!K18:K18,Expenses!L18:L18,Expenses!M18:M18)</f>
         <v>0</v>
       </c>
@@ -15171,7 +15168,7 @@
       <c r="N7" s="28" t="str">
         <v>Food</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="58">
         <f>SUM(Expenses!B11:M11)</f>
         <v>0</v>
       </c>
@@ -15181,32 +15178,32 @@
         <v>12</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="62">
+      <c r="C8" s="48">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="49">
         <f>SUM('Net Salary'!G$13:G$14)</f>
         <v>0</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="68">
+      <c r="F8" s="54">
         <f>SUM(Expenses!G20:G20)</f>
         <v>0</v>
       </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="62">
+      <c r="H8" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="65">
+      <c r="I8" s="51">
         <f>Expenses!G4</f>
         <v>0</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="63">
+        <v>46</v>
+      </c>
+      <c r="L8" s="49">
         <f>SUM(L6:L7)</f>
         <v>0</v>
       </c>
@@ -15214,7 +15211,7 @@
       <c r="N8" s="28" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="58">
         <f>SUM(Expenses!B12:M12)</f>
         <v>0</v>
       </c>
@@ -15224,32 +15221,32 @@
         <v>13</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="62">
+      <c r="C9" s="48">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="49">
         <f>SUM('Net Salary'!H$13:H$14)</f>
         <v>0</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="68">
+      <c r="F9" s="54">
         <f>SUM(Expenses!H20:H20)</f>
         <v>0</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="62">
+      <c r="H9" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="65">
+      <c r="I9" s="51">
         <f>Expenses!H4</f>
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="65">
+        <v>40</v>
+      </c>
+      <c r="L9" s="51">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
@@ -15257,7 +15254,7 @@
       <c r="N9" s="28" t="str">
         <v>Hang out</v>
       </c>
-      <c r="O9" s="72">
+      <c r="O9" s="58">
         <f>SUM(Expenses!B13:M13)</f>
         <v>0</v>
       </c>
@@ -15267,32 +15264,32 @@
         <v>14</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="62">
+      <c r="C10" s="48">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="49">
         <f>SUM('Net Salary'!I$13:I$14)</f>
         <v>0</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="68">
+      <c r="F10" s="54">
         <f>SUM(Expenses!I20:I20)</f>
         <v>0</v>
       </c>
       <c r="G10" s="7"/>
-      <c r="H10" s="62">
+      <c r="H10" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="65">
+      <c r="I10" s="51">
         <f>Expenses!I4</f>
         <v>0</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="67">
+        <v>37</v>
+      </c>
+      <c r="L10" s="53">
         <f>'Graphic - Annual'!D15</f>
         <v>0</v>
       </c>
@@ -15300,7 +15297,7 @@
       <c r="N10" s="28" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="O10" s="72">
+      <c r="O10" s="58">
         <f>SUM(Expenses!B14:M14)</f>
         <v>0</v>
       </c>
@@ -15310,25 +15307,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="62">
+      <c r="C11" s="48">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="49">
         <f>SUM('Net Salary'!J$13:J$14)</f>
         <v>0</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="68">
+      <c r="F11" s="54">
         <f>SUM(Expenses!J20:J20)</f>
         <v>0</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="62">
+      <c r="H11" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="65">
+      <c r="I11" s="51">
         <f>Expenses!J4</f>
         <v>0</v>
       </c>
@@ -15337,7 +15334,7 @@
       <c r="N11" s="26" t="str">
         <v>Insurance</v>
       </c>
-      <c r="O11" s="72">
+      <c r="O11" s="58">
         <f>SUM(Expenses!B15:M15)</f>
         <v>0</v>
       </c>
@@ -15347,25 +15344,25 @@
         <v>16</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="62">
+      <c r="C12" s="48">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="49">
         <f>SUM('Net Salary'!K$13:K$14)</f>
         <v>0</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="68">
+      <c r="F12" s="54">
         <f>SUM(Expenses!K20:K20)</f>
         <v>0</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="62">
+      <c r="H12" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="65">
+      <c r="I12" s="51">
         <f>Expenses!K4</f>
         <v>0</v>
       </c>
@@ -15374,7 +15371,7 @@
       <c r="N12" s="26" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="O12" s="72">
+      <c r="O12" s="58">
         <f>SUM(Expenses!B16:M16)</f>
         <v>0</v>
       </c>
@@ -15385,25 +15382,25 @@
         <v>17</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="62">
+      <c r="C13" s="48">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="49">
         <f>SUM('Net Salary'!L$13:L$14)</f>
         <v>0</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="68">
+      <c r="F13" s="54">
         <f>SUM(Expenses!L20:L20)</f>
         <v>0</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="62">
+      <c r="H13" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="65">
+      <c r="I13" s="51">
         <f>Expenses!L4</f>
         <v>0</v>
       </c>
@@ -15412,7 +15409,7 @@
       <c r="N13" s="26" t="str">
         <v>Travel</v>
       </c>
-      <c r="O13" s="72">
+      <c r="O13" s="58">
         <f>SUM(Expenses!B17:M17)</f>
         <v>0</v>
       </c>
@@ -15423,32 +15420,32 @@
         <v>18</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="62">
+      <c r="C14" s="48">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="49">
         <f>SUM('Net Salary'!M$13:M$14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="68">
+      <c r="F14" s="54">
         <f>SUM(Expenses!M20:N20)</f>
         <v>0</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="62">
+      <c r="H14" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="65">
+      <c r="I14" s="51">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
       <c r="N14" s="27" t="str">
         <v>General expen.</v>
       </c>
-      <c r="O14" s="73">
+      <c r="O14" s="59">
         <f>SUM(Expenses!B18:M18)</f>
         <v>0</v>
       </c>
@@ -15458,43 +15455,43 @@
         <v>1</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="64">
+      <c r="C15" s="50">
         <f>SUM(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="49">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="68">
+      <c r="F15" s="54">
         <f>SUM(F3:F14)</f>
         <v>0</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="67">
+        <v>40</v>
+      </c>
+      <c r="I15" s="53">
         <f>'Graphic - Annual'!L9</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="64">
+      <c r="C16" s="50">
         <f>AVERAGE(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="49">
         <f>AVERAGE(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="69">
+      <c r="F16" s="55">
         <f>AVERAGE(F3:F14)</f>
         <v>0</v>
       </c>
@@ -15507,16 +15504,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="62">
+      <c r="C17" s="48">
         <f>SUM(C3:C8)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="51">
         <f>SUM(D3:D8)</f>
         <v>0</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="70">
+      <c r="F17" s="56">
         <f>SUM(F3:F8)</f>
         <v>0</v>
       </c>
@@ -15528,16 +15525,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="66">
+      <c r="C18" s="52">
         <f>SUM($C$9:$C$14)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="53">
         <f>SUM($D$9:$D$14)</f>
         <v>0</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="71">
+      <c r="F18" s="57">
         <f>SUM($F$9:$F$14)</f>
         <v>0</v>
       </c>

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4BF94E-84A0-4148-928D-7D55855F8C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C5085-8B16-4124-AA0C-A1B96F56362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Graphic - Annual" sheetId="13" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Assets">'Balance &amp; Tracking'!$B$7:$B$9</definedName>
+    <definedName name="Assets">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
     <definedName name="Categories">Expenses!$A$7:$A$18</definedName>
     <definedName name="Dash">'Graphic - Annual'!$A$1:$P$26</definedName>
     <definedName name="Discount">'Net Salary'!$A$8:$A$12</definedName>
@@ -29,7 +29,7 @@
     <definedName name="Investments">'Net Salary'!$A$13:$A$14</definedName>
     <definedName name="Months">'Net Salary'!$B$2:$M$2</definedName>
     <definedName name="Net_Salary">'Net Salary'!$A$3:$A$14</definedName>
-    <definedName name="Transfer">'Balance &amp; Tracking'!$B$7:$B$9</definedName>
+    <definedName name="Transfer">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
   <si>
     <t>Total</t>
   </si>
@@ -296,7 +296,10 @@
     <t>Bank Fee I</t>
   </si>
   <si>
-    <t>SubTotal</t>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>Debt/ Income</t>
   </si>
 </sst>
 </file>
@@ -575,11 +578,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -733,12 +737,6 @@
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -782,10 +780,20 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="13">
     <dxf>
@@ -8795,13 +8803,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>2</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>36214</xdr:rowOff>
+      <xdr:rowOff>21124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2254313</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>24479</xdr:rowOff>
+      <xdr:rowOff>9389</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9341,15 +9349,16 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="67" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="65" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="66" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="67" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="70" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="69" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="67" customWidth="1"/>
-    <col min="10" max="10" width="10" style="67" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="67"/>
+    <col min="1" max="1" width="14.28515625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="63" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="64" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="64" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="65" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="68" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="67" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="65" customWidth="1"/>
+    <col min="10" max="10" width="10" style="65" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9360,204 +9369,206 @@
       <c r="C2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="77" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="81" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="45">
         <f>IF(B3="Expenses",HLOOKUP(B2,Expenses!B2:M20,19,FALSE),IF(B3="Net Salary",HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE),""))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="69" t="str" cm="1">
+      <c r="E3" s="67" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(B3="Expenses",Categories,IF(B3="Net Salary",Net_Salary,""))</f>
         <v>Bills</v>
       </c>
-      <c r="F3" s="77" cm="1">
+      <c r="F3" s="75" cm="1">
         <f t="array" ref="F3:F14">IF(B3="Expenses",_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses!B2:M2=B2),IF(B3="Net Salary",_xlfn._xlws.FILTER('Net Salary'!B3:M14,'Net Salary'!B2:M2=B2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="67"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="45">
-        <f>VLOOKUP(B2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="69" t="str">
+        <v>74</v>
+      </c>
+      <c r="C4" s="82" t="e">
+        <f>HLOOKUP(B2,Expenses!B2:M20,19,FALSE)/HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E4" s="67" t="str">
         <v>Car maintenance</v>
       </c>
-      <c r="F4" s="77">
-        <v>0</v>
-      </c>
-      <c r="H4" s="67"/>
+      <c r="F4" s="75">
+        <v>0</v>
+      </c>
+      <c r="H4" s="65"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="45">
+        <f>VLOOKUP(B2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="67" t="str">
+        <v>Clothing</v>
+      </c>
+      <c r="F5" s="75">
+        <v>0</v>
+      </c>
+      <c r="H5" s="65"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C6" s="45">
         <f>'Graphic - Annual'!I15</f>
         <v>0</v>
       </c>
-      <c r="E5" s="69" t="str">
-        <v>Clothing</v>
-      </c>
-      <c r="F5" s="77">
-        <v>0</v>
-      </c>
-      <c r="H5" s="67"/>
-    </row>
-    <row r="6" spans="1:8" ht="10.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="E6" s="69" t="str">
+      <c r="E6" s="67" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="F6" s="77">
-        <v>0</v>
-      </c>
-      <c r="H6" s="67"/>
+      <c r="F6" s="75">
+        <v>0</v>
+      </c>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="46" cm="1">
-        <f t="array" aca="1" ref="C7" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B7,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B7,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B7,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
-        <v>150</v>
-      </c>
-      <c r="E7" s="69" t="str">
+      <c r="E7" s="67" t="str">
         <v>Food</v>
       </c>
-      <c r="F7" s="77">
-        <v>0</v>
-      </c>
-      <c r="H7" s="67"/>
+      <c r="F7" s="75">
+        <v>0</v>
+      </c>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="46" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B8,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B8,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B8,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="69" t="str">
+      <c r="B8" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="67" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F8" s="77">
-        <v>0</v>
-      </c>
-      <c r="H8" s="67"/>
+      <c r="F8" s="75">
+        <v>0</v>
+      </c>
+      <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="46" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="69" t="str">
+        <v>150</v>
+      </c>
+      <c r="E9" s="67" t="str">
         <v>Hang out</v>
       </c>
-      <c r="F9" s="77">
-        <v>0</v>
-      </c>
-      <c r="H9" s="67"/>
+      <c r="F9" s="75">
+        <v>0</v>
+      </c>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="66"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="46" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="67" t="str">
+        <v>Healthcare</v>
+      </c>
+      <c r="F10" s="75">
+        <v>0</v>
+      </c>
+      <c r="H10" s="65"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64"/>
+      <c r="B11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="46" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="67" t="str">
+        <v>Insurance</v>
+      </c>
+      <c r="F11" s="75">
+        <v>0</v>
+      </c>
+      <c r="H11" s="65"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64"/>
+      <c r="B12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="46">
-        <f ca="1">SUM(C7:C9)</f>
+      <c r="C12" s="46">
+        <f ca="1">SUM(C9:C11)</f>
         <v>150</v>
       </c>
-      <c r="E10" s="69" t="str">
-        <v>Healthcare</v>
-      </c>
-      <c r="F10" s="77">
-        <v>0</v>
-      </c>
-      <c r="H10" s="67"/>
-    </row>
-    <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66"/>
-      <c r="B11" s="15" t="s">
+      <c r="E12" s="67" t="str">
+        <v>Personal Care</v>
+      </c>
+      <c r="F12" s="75">
+        <v>0</v>
+      </c>
+      <c r="H12" s="65"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="64"/>
+      <c r="B13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="45">
-        <f ca="1">ROUND(C4-C10,2)</f>
+      <c r="C13" s="45">
+        <f ca="1">ROUND(C5-C12,2)</f>
         <v>-150</v>
       </c>
-      <c r="E11" s="69" t="str">
-        <v>Insurance</v>
-      </c>
-      <c r="F11" s="77">
-        <v>0</v>
-      </c>
-      <c r="H11" s="67"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="E12" s="69" t="str">
-        <v>Personal Care</v>
-      </c>
-      <c r="F12" s="77">
-        <v>0</v>
-      </c>
-      <c r="H12" s="67"/>
-    </row>
-    <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="66"/>
-      <c r="B13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="1">
-        <f>SUBTOTAL(9,Tabela1[Amount])</f>
-        <v>150</v>
-      </c>
-      <c r="E13" s="69" t="str">
+      <c r="E13" s="67" t="str">
         <v>Travel</v>
       </c>
-      <c r="F13" s="77">
-        <v>0</v>
-      </c>
-      <c r="H13" s="67"/>
+      <c r="F13" s="75">
+        <v>0</v>
+      </c>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="66"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="E14" s="69" t="str">
+      <c r="A14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="E14" s="67" t="str">
         <v>General expen.</v>
       </c>
-      <c r="F14" s="76">
-        <v>0</v>
-      </c>
-      <c r="H14" s="67"/>
+      <c r="F14" s="74">
+        <v>0</v>
+      </c>
+      <c r="H14" s="65"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="67"/>
-      <c r="H15" s="67"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="65"/>
+      <c r="H15" s="65"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="75">
+      <c r="A16" s="73">
         <f>SUBTOTAL(2,Tabela1[Date])</f>
         <v>1</v>
       </c>
@@ -9642,3210 +9653,3224 @@
       <c r="H20" s="24"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="68"/>
+      <c r="G23" s="66"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="68"/>
+      <c r="G25" s="66"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="68"/>
+      <c r="G26" s="66"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="68"/>
+      <c r="G27" s="66"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="68"/>
+      <c r="G28" s="66"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="67" t="s">
+      <c r="I38" s="65" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="68"/>
+      <c r="G137" s="66"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="68"/>
+      <c r="G139" s="66"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="68"/>
+      <c r="G140" s="66"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="68"/>
+      <c r="G141" s="66"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="68"/>
+      <c r="G142" s="66"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="66" t="str">
+      <c r="C248" s="64" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="66" t="str">
+      <c r="C249" s="64" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="71"/>
+      <c r="G249" s="69"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="66" t="str">
+      <c r="C258" s="64" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="66" t="str">
+      <c r="D258" s="64" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="66" t="str">
+      <c r="E258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="66" t="str">
+      <c r="F258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="66" t="str">
+      <c r="G258" s="64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="66" t="str">
+      <c r="C267" s="64" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="66" t="str">
+      <c r="C268" s="64" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="66" t="str">
+      <c r="C269" s="64" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="66" t="str">
+      <c r="C270" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="66" t="str">
+      <c r="C271" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="66" t="str">
+      <c r="C272" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="66" t="str">
+      <c r="C273" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="66" t="str">
+      <c r="C274" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="66" t="str">
+      <c r="C275" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="66" t="str">
+      <c r="C276" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="66" t="str">
+      <c r="C277" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="66" t="str">
+      <c r="C278" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="66" t="str">
+      <c r="C279" s="64" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="66" t="str">
+      <c r="C280" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="66" t="str">
+      <c r="C281" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="66" t="str">
+      <c r="C282" s="64" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="68"/>
-      <c r="H282" s="72"/>
+      <c r="G282" s="66"/>
+      <c r="H282" s="70"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="67"/>
-      <c r="C283" s="67"/>
-      <c r="D283" s="67"/>
-      <c r="E283" s="73"/>
-      <c r="F283" s="73"/>
-      <c r="G283" s="68"/>
-      <c r="H283" s="72"/>
+      <c r="B283" s="65"/>
+      <c r="C283" s="65"/>
+      <c r="D283" s="65"/>
+      <c r="E283" s="71"/>
+      <c r="F283" s="71"/>
+      <c r="G283" s="66"/>
+      <c r="H283" s="70"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="67"/>
-      <c r="C284" s="67"/>
-      <c r="D284" s="67"/>
-      <c r="E284" s="73"/>
-      <c r="F284" s="73"/>
-      <c r="G284" s="68"/>
-      <c r="H284" s="72"/>
+      <c r="B284" s="65"/>
+      <c r="C284" s="65"/>
+      <c r="D284" s="65"/>
+      <c r="E284" s="71"/>
+      <c r="F284" s="71"/>
+      <c r="G284" s="66"/>
+      <c r="H284" s="70"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="67"/>
-      <c r="C285" s="67"/>
-      <c r="D285" s="67"/>
-      <c r="E285" s="73"/>
-      <c r="F285" s="73"/>
-      <c r="G285" s="68"/>
-      <c r="H285" s="72"/>
+      <c r="B285" s="65"/>
+      <c r="C285" s="65"/>
+      <c r="D285" s="65"/>
+      <c r="E285" s="71"/>
+      <c r="F285" s="71"/>
+      <c r="G285" s="66"/>
+      <c r="H285" s="70"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="67"/>
-      <c r="C286" s="74"/>
-      <c r="D286" s="74"/>
-      <c r="E286" s="73"/>
-      <c r="F286" s="73"/>
-      <c r="G286" s="68"/>
-      <c r="H286" s="72"/>
+      <c r="B286" s="65"/>
+      <c r="C286" s="72"/>
+      <c r="D286" s="72"/>
+      <c r="E286" s="71"/>
+      <c r="F286" s="71"/>
+      <c r="G286" s="66"/>
+      <c r="H286" s="70"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="67"/>
-      <c r="C287" s="67"/>
-      <c r="D287" s="67"/>
-      <c r="G287" s="67"/>
+      <c r="B287" s="65"/>
+      <c r="C287" s="65"/>
+      <c r="D287" s="65"/>
+      <c r="G287" s="65"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="67"/>
-      <c r="C288" s="67"/>
-      <c r="D288" s="67"/>
-      <c r="G288" s="67"/>
+      <c r="B288" s="65"/>
+      <c r="C288" s="65"/>
+      <c r="D288" s="65"/>
+      <c r="G288" s="65"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="67"/>
-      <c r="C289" s="67"/>
-      <c r="D289" s="67"/>
-      <c r="G289" s="67"/>
+      <c r="B289" s="65"/>
+      <c r="C289" s="65"/>
+      <c r="D289" s="65"/>
+      <c r="G289" s="65"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="67"/>
-      <c r="C290" s="67"/>
-      <c r="D290" s="67"/>
-      <c r="G290" s="67"/>
+      <c r="B290" s="65"/>
+      <c r="C290" s="65"/>
+      <c r="D290" s="65"/>
+      <c r="G290" s="65"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="67"/>
-      <c r="C291" s="67"/>
-      <c r="D291" s="67"/>
-      <c r="G291" s="67"/>
+      <c r="B291" s="65"/>
+      <c r="C291" s="65"/>
+      <c r="D291" s="65"/>
+      <c r="G291" s="65"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="67"/>
-      <c r="C292" s="67"/>
-      <c r="D292" s="67"/>
-      <c r="G292" s="67"/>
+      <c r="B292" s="65"/>
+      <c r="C292" s="65"/>
+      <c r="D292" s="65"/>
+      <c r="G292" s="65"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="67"/>
-      <c r="C293" s="67"/>
-      <c r="D293" s="67"/>
-      <c r="G293" s="67"/>
+      <c r="B293" s="65"/>
+      <c r="C293" s="65"/>
+      <c r="D293" s="65"/>
+      <c r="G293" s="65"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="66" t="str">
+      <c r="C294" s="64" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="66" t="str">
+      <c r="C295" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="66" t="str">
+      <c r="C296" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="66" t="str">
+      <c r="C297" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="66" t="str">
+      <c r="C298" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="66" t="str">
+      <c r="C299" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="66" t="str">
+      <c r="C300" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="66" t="str">
+      <c r="C301" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="66" t="str">
+      <c r="C302" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="66" t="str">
+      <c r="C303" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="66" t="str">
+      <c r="C304" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="66" t="str">
+      <c r="C305" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="66" t="str">
+      <c r="C306" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="66" t="str">
+      <c r="C307" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="66" t="str">
+      <c r="C308" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="66" t="str">
+      <c r="C309" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="66" t="str">
+      <c r="C310" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="66" t="str">
+      <c r="C311" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="66" t="str">
+      <c r="C312" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="66" t="str">
+      <c r="C313" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="66" t="str">
+      <c r="C314" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="66" t="str">
+      <c r="C315" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="66" t="str">
+      <c r="C316" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="66" t="str">
+      <c r="C317" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="66" t="str">
+      <c r="C318" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="66" t="str">
+      <c r="C319" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="66" t="str">
+      <c r="C320" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="66" t="str">
+      <c r="C321" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="66" t="str">
+      <c r="C322" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="66" t="str">
+      <c r="C323" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="66" t="str">
+      <c r="C324" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="66" t="str">
+      <c r="C325" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="66" t="str">
+      <c r="C326" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="66" t="str">
+      <c r="C327" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="66" t="str">
+      <c r="C328" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="66" t="str">
+      <c r="C329" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="66" t="str">
+      <c r="C330" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="66" t="str">
+      <c r="C331" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="66" t="str">
+      <c r="C332" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="66" t="str">
+      <c r="C333" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="66" t="str">
+      <c r="C334" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="66" t="str">
+      <c r="C335" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="66" t="str">
+      <c r="C336" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="66" t="str">
+      <c r="C337" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="66" t="str">
+      <c r="C338" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="66" t="str">
+      <c r="C339" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="66" t="str">
+      <c r="C340" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="66" t="str">
+      <c r="C341" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="66" t="str">
+      <c r="C342" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="66" t="str">
+      <c r="C343" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="66" t="str">
+      <c r="C344" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="66" t="str">
+      <c r="C345" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="66" t="str">
+      <c r="C346" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="66" t="str">
+      <c r="C347" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="66" t="str">
+      <c r="C348" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="66" t="str">
+      <c r="C349" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="66" t="str">
+      <c r="C350" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="66" t="str">
+      <c r="C351" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="66" t="str">
+      <c r="C352" s="64" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="66" t="str">
+      <c r="C353" s="64" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="66" t="str">
+      <c r="C354" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="66" t="str">
+      <c r="C355" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="66" t="str">
+      <c r="C356" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="66" t="str">
+      <c r="C357" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="66" t="str">
+      <c r="C358" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="66" t="str">
+      <c r="C359" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="66" t="str">
+      <c r="C360" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="66" t="str">
+      <c r="C361" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="66" t="str">
+      <c r="C362" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="66" t="str">
+      <c r="C363" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="66" t="str">
+      <c r="C364" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="66" t="str">
+      <c r="C365" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="66" t="str">
+      <c r="C366" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="66" t="str">
+      <c r="C367" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="66" t="str">
+      <c r="C368" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="66" t="str">
+      <c r="C369" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="66" t="str">
+      <c r="C370" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="66" t="str">
+      <c r="C371" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="66" t="str">
+      <c r="C372" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="66" t="str">
+      <c r="C373" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="66" t="str">
+      <c r="C374" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="66" t="str">
+      <c r="C375" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="66" t="str">
+      <c r="C376" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="66" t="str">
+      <c r="C377" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="66" t="str">
+      <c r="C378" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="66" t="str">
+      <c r="C379" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="66" t="str">
+      <c r="C380" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="66" t="str">
+      <c r="C381" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="66" t="str">
+      <c r="C382" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="66" t="str">
+      <c r="C383" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="66" t="str">
+      <c r="C384" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="66" t="str">
+      <c r="C385" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="66" t="str">
+      <c r="C386" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="66" t="str">
+      <c r="C387" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="66" t="str">
+      <c r="C388" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="66" t="str">
+      <c r="C389" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="66" t="str">
+      <c r="C390" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="66" t="str">
+      <c r="C391" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="66" t="str">
+      <c r="C392" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="66" t="str">
+      <c r="C393" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="66" t="str">
+      <c r="C394" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="66" t="str">
+      <c r="C395" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="66" t="str">
+      <c r="C396" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="66" t="str">
+      <c r="C397" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="66" t="str">
+      <c r="C398" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="66" t="str">
+      <c r="C399" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="66" t="str">
+      <c r="C400" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="66" t="str">
+      <c r="C401" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="66" t="str">
+      <c r="C402" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="66" t="str">
+      <c r="C403" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="66" t="str">
+      <c r="C404" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="66" t="str">
+      <c r="C405" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="66" t="str">
+      <c r="C406" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="66" t="str">
+      <c r="C407" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="66" t="str">
+      <c r="C408" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="66" t="str">
+      <c r="C409" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="66" t="str">
+      <c r="C410" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="66" t="str">
+      <c r="C411" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="66" t="str">
+      <c r="C412" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="66" t="str">
+      <c r="C413" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="66" t="str">
+      <c r="C414" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="66" t="str">
+      <c r="C415" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="66" t="str">
+      <c r="C416" s="64" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="66" t="str">
+      <c r="C417" s="64" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="66" t="str">
+      <c r="C418" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="66" t="str">
+      <c r="C419" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="66" t="str">
+      <c r="C420" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="66" t="str">
+      <c r="C421" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="66" t="str">
+      <c r="C422" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="66" t="str">
+      <c r="C423" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="66" t="str">
+      <c r="C424" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="66" t="str">
+      <c r="C425" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="66" t="str">
+      <c r="C426" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="66" t="str">
+      <c r="C427" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="66" t="str">
+      <c r="C428" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="66" t="str">
+      <c r="C429" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="66" t="str">
+      <c r="C430" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="66" t="str">
+      <c r="C431" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="66" t="str">
+      <c r="C432" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="66" t="str">
+      <c r="C433" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="66" t="str">
+      <c r="C434" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="66" t="str">
+      <c r="C435" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="66" t="str">
+      <c r="C436" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="66" t="str">
+      <c r="C437" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="66" t="str">
+      <c r="C438" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="66" t="str">
+      <c r="C439" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="66" t="str">
+      <c r="C440" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="66" t="str">
+      <c r="C441" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="66" t="str">
+      <c r="C442" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="66" t="str">
+      <c r="C443" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="66" t="str">
+      <c r="C444" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="66" t="str">
+      <c r="C445" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="66" t="str">
+      <c r="C446" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="66" t="str">
+      <c r="C447" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="66" t="str">
+      <c r="C448" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="66" t="str">
+      <c r="C449" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="66" t="str">
+      <c r="C450" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="66" t="str">
+      <c r="C451" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="66" t="str">
+      <c r="C452" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="66" t="str">
+      <c r="C453" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="66" t="str">
+      <c r="C454" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="66" t="str">
+      <c r="C455" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="66" t="str">
+      <c r="C456" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="66" t="str">
+      <c r="C457" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="66" t="str">
+      <c r="C458" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="66" t="str">
+      <c r="C459" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="66" t="str">
+      <c r="C460" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="66" t="str">
+      <c r="C461" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="66" t="str">
+      <c r="C462" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="66" t="str">
+      <c r="C463" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="66" t="str">
+      <c r="C464" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="66" t="str">
+      <c r="C465" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="66" t="str">
+      <c r="C466" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="66" t="str">
+      <c r="C467" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="66" t="str">
+      <c r="C468" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="66" t="str">
+      <c r="C469" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="66" t="str">
+      <c r="C470" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="66" t="str">
+      <c r="C471" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="66" t="str">
+      <c r="C472" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="66" t="str">
+      <c r="C473" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="66" t="str">
+      <c r="C474" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="66" t="str">
+      <c r="C475" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="66" t="str">
+      <c r="C476" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="66" t="str">
+      <c r="C477" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="66" t="str">
+      <c r="C478" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="66" t="str">
+      <c r="C479" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="66" t="str">
+      <c r="C480" s="64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="66" t="str">
+      <c r="C481" s="64" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="66" t="str">
+      <c r="C482" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="66" t="str">
+      <c r="C483" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="66" t="str">
+      <c r="C484" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="66" t="str">
+      <c r="C485" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="66" t="str">
+      <c r="C486" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="66" t="str">
+      <c r="C487" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="66" t="str">
+      <c r="C488" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="66" t="str">
+      <c r="C489" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="66" t="str">
+      <c r="C490" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="66" t="str">
+      <c r="C491" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="66" t="str">
+      <c r="C492" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="66" t="str">
+      <c r="C493" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="66" t="str">
+      <c r="C494" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="66" t="str">
+      <c r="C495" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="66" t="str">
+      <c r="C496" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="66" t="str">
+      <c r="C497" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="66" t="str">
+      <c r="C498" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="66" t="str">
+      <c r="C499" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="66" t="str">
+      <c r="C500" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="66" t="str">
+      <c r="C501" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="66" t="str">
+      <c r="C502" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="66" t="str">
+      <c r="C503" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="66" t="str">
+      <c r="C504" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="66" t="str">
+      <c r="C505" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="66" t="str">
+      <c r="C506" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="66" t="str">
+      <c r="C507" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="66" t="str">
+      <c r="C508" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="66" t="str">
+      <c r="C509" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="66" t="str">
+      <c r="C510" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="66" t="str">
+      <c r="C511" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="66" t="str">
+      <c r="C512" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="66" t="str">
+      <c r="C513" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="66" t="str">
+      <c r="C514" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="66" t="str">
+      <c r="C515" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="66" t="str">
+      <c r="C516" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="66" t="str">
+      <c r="C517" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="66" t="str">
+      <c r="C518" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="66" t="str">
+      <c r="C519" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="66" t="str">
+      <c r="C520" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="66" t="str">
+      <c r="C521" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="66" t="str">
+      <c r="C522" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="66" t="str">
+      <c r="C523" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="66" t="str">
+      <c r="C524" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="66" t="str">
+      <c r="C525" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="66" t="str">
+      <c r="C526" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="66" t="str">
+      <c r="C527" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="66" t="str">
+      <c r="C528" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="66" t="str">
+      <c r="C529" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="66" t="str">
+      <c r="C530" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="66" t="str">
+      <c r="C531" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="66" t="str">
+      <c r="C532" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="66" t="str">
+      <c r="C533" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="66" t="str">
+      <c r="C534" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="66" t="str">
+      <c r="C535" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="66" t="str">
+      <c r="C536" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="66" t="str">
+      <c r="C537" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="66" t="str">
+      <c r="C538" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="66" t="str">
+      <c r="C539" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="66" t="str">
+      <c r="C540" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="66" t="str">
+      <c r="C541" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="66" t="str">
+      <c r="C542" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="66" t="str">
+      <c r="C543" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="66" t="str">
+      <c r="C544" s="64" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="66" t="str">
+      <c r="C545" s="64" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="66" t="str">
+      <c r="C546" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="66" t="str">
+      <c r="C547" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="66" t="str">
+      <c r="C548" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="66" t="str">
+      <c r="C549" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="66" t="str">
+      <c r="C550" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="66" t="str">
+      <c r="C551" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="66" t="str">
+      <c r="C552" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="66" t="str">
+      <c r="C553" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="66" t="str">
+      <c r="C554" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="66" t="str">
+      <c r="C555" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="66" t="str">
+      <c r="C556" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="66" t="str">
+      <c r="C557" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="66" t="str">
+      <c r="C558" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="66" t="str">
+      <c r="C559" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="66" t="str">
+      <c r="C560" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="66" t="str">
+      <c r="C561" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="66" t="str">
+      <c r="C562" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="66" t="str">
+      <c r="C563" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="66" t="str">
+      <c r="C564" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="66" t="str">
+      <c r="C565" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="66" t="str">
+      <c r="C566" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="66" t="str">
+      <c r="C567" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="66" t="str">
+      <c r="C568" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="66" t="str">
+      <c r="C569" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="66" t="str">
+      <c r="C570" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="66" t="str">
+      <c r="C571" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="66" t="str">
+      <c r="C572" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="66" t="str">
+      <c r="C573" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="66" t="str">
+      <c r="C574" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="66" t="str">
+      <c r="C575" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="66" t="str">
+      <c r="C576" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="66" t="str">
+      <c r="C577" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="66" t="str">
+      <c r="C578" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="66" t="str">
+      <c r="C579" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="66" t="str">
+      <c r="C580" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="66" t="str">
+      <c r="C581" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="66" t="str">
+      <c r="C582" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="66" t="str">
+      <c r="C583" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="66" t="str">
+      <c r="C584" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="66" t="str">
+      <c r="C585" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="66" t="str">
+      <c r="C586" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="66" t="str">
+      <c r="C587" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="66" t="str">
+      <c r="C588" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="66" t="str">
+      <c r="C589" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="66" t="str">
+      <c r="C590" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="66" t="str">
+      <c r="C591" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="66" t="str">
+      <c r="C592" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="66" t="str">
+      <c r="C593" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="66" t="str">
+      <c r="C594" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="66" t="str">
+      <c r="C595" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="66" t="str">
+      <c r="C596" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="66" t="str">
+      <c r="C597" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="66" t="str">
+      <c r="C598" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="66" t="str">
+      <c r="C599" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="66" t="str">
+      <c r="C600" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="66" t="str">
+      <c r="C601" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="66" t="str">
+      <c r="C602" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="66" t="str">
+      <c r="C603" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="66" t="str">
+      <c r="C604" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="66" t="str">
+      <c r="C605" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="66" t="str">
+      <c r="C606" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="66" t="str">
+      <c r="C607" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="66" t="str">
+      <c r="C608" s="64" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="66" t="str">
+      <c r="C609" s="64" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="66" t="str">
+      <c r="C610" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="66" t="str">
+      <c r="C611" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="66" t="str">
+      <c r="C612" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="66" t="str">
+      <c r="C613" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="66" t="str">
+      <c r="C614" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="66" t="str">
+      <c r="C615" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="66" t="str">
+      <c r="C616" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="66" t="str">
+      <c r="C617" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="66" t="str">
+      <c r="C618" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="66" t="str">
+      <c r="C619" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="66" t="str">
+      <c r="C620" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="66" t="str">
+      <c r="C621" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="66" t="str">
+      <c r="C622" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="66" t="str">
+      <c r="C623" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="66" t="str">
+      <c r="C624" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="66" t="str">
+      <c r="C625" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="66" t="str">
+      <c r="C626" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="66" t="str">
+      <c r="C627" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="66" t="str">
+      <c r="C628" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="66" t="str">
+      <c r="C629" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="66" t="str">
+      <c r="C630" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="66" t="str">
+      <c r="C631" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="66" t="str">
+      <c r="C632" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="66" t="str">
+      <c r="C633" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="66" t="str">
+      <c r="C634" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="66" t="str">
+      <c r="C635" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="66" t="str">
+      <c r="C636" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="66" t="str">
+      <c r="C637" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="66" t="str">
+      <c r="C638" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="66" t="str">
+      <c r="C639" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="66" t="str">
+      <c r="C640" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="66" t="str">
+      <c r="C641" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="66" t="str">
+      <c r="C642" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="66" t="str">
+      <c r="C643" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="66" t="str">
+      <c r="C644" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="66" t="str">
+      <c r="C645" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="66" t="str">
+      <c r="C646" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="66" t="str">
+      <c r="C647" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="66" t="str">
+      <c r="C648" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="66" t="str">
+      <c r="C649" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="66" t="str">
+      <c r="C650" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="66" t="str">
+      <c r="C651" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="66" t="str">
+      <c r="C652" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="66" t="str">
+      <c r="C653" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="66" t="str">
+      <c r="C654" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="66" t="str">
+      <c r="C655" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="66" t="str">
+      <c r="C656" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="66" t="str">
+      <c r="C657" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="66" t="str">
+      <c r="C658" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="66" t="str">
+      <c r="C659" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="66" t="str">
+      <c r="C660" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="66" t="str">
+      <c r="C661" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="66" t="str">
+      <c r="C662" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="66" t="str">
+      <c r="C663" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="66" t="str">
+      <c r="C664" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="66" t="str">
+      <c r="C665" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="66" t="str">
+      <c r="C666" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="66" t="str">
+      <c r="C667" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="66" t="str">
+      <c r="C668" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="66" t="str">
+      <c r="C669" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="66" t="str">
+      <c r="C670" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="66" t="str">
+      <c r="C671" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="66" t="str">
+      <c r="C672" s="64" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="66" t="str">
+      <c r="C673" s="64" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="66" t="str">
+      <c r="C674" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="66" t="str">
+      <c r="C675" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="66" t="str">
+      <c r="C676" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="66" t="str">
+      <c r="C677" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="66" t="str">
+      <c r="C678" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="66" t="str">
+      <c r="C679" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="66" t="str">
+      <c r="C680" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="66" t="str">
+      <c r="C681" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="66" t="str">
+      <c r="C682" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="66" t="str">
+      <c r="C683" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="66" t="str">
+      <c r="C684" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="66" t="str">
+      <c r="C685" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="66" t="str">
+      <c r="C686" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="66" t="str">
+      <c r="C687" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="66" t="str">
+      <c r="C688" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="66" t="str">
+      <c r="C689" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="66" t="str">
+      <c r="C690" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="66" t="str">
+      <c r="C691" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="66" t="str">
+      <c r="C692" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="66" t="str">
+      <c r="C693" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="66" t="str">
+      <c r="C694" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="66" t="str">
+      <c r="C695" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="66" t="str">
+      <c r="C696" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="66" t="str">
+      <c r="C697" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="66" t="str">
+      <c r="C698" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="66" t="str">
+      <c r="C699" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="66" t="str">
+      <c r="C700" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="66" t="str">
+      <c r="C701" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="66" t="str">
+      <c r="C702" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="66" t="str">
+      <c r="C703" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="66" t="str">
+      <c r="C704" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="66" t="str">
+      <c r="C705" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="66" t="str">
+      <c r="C706" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="66" t="str">
+      <c r="C707" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="66" t="str">
+      <c r="C708" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="66" t="str">
+      <c r="C709" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="66" t="str">
+      <c r="C710" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="66" t="str">
+      <c r="C711" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="66" t="str">
+      <c r="C712" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="66" t="str">
+      <c r="C713" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="66" t="str">
+      <c r="C714" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="66" t="str">
+      <c r="C715" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="66" t="str">
+      <c r="C716" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="66" t="str">
+      <c r="C717" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="66" t="str">
+      <c r="C718" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="66" t="str">
+      <c r="C719" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="66" t="str">
+      <c r="C720" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="66" t="str">
+      <c r="C721" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="66" t="str">
+      <c r="C722" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="66" t="str">
+      <c r="C723" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="66" t="str">
+      <c r="C724" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="66" t="str">
+      <c r="C725" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="66" t="str">
+      <c r="C726" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="66" t="str">
+      <c r="C727" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="66" t="str">
+      <c r="C728" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="66" t="str">
+      <c r="C729" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="66" t="str">
+      <c r="C730" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="66" t="str">
+      <c r="C731" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="66" t="str">
+      <c r="C732" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="66" t="str">
+      <c r="C733" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="66" t="str">
+      <c r="C734" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="66" t="str">
+      <c r="C735" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="66" t="str">
+      <c r="C736" s="64" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="66" t="str">
+      <c r="C737" s="64" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="66" t="str">
+      <c r="C738" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="66" t="str">
+      <c r="C739" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="66" t="str">
+      <c r="C740" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="66" t="str">
+      <c r="C741" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="66" t="str">
+      <c r="C742" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="66" t="str">
+      <c r="C743" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="66" t="str">
+      <c r="C744" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="66" t="str">
+      <c r="C745" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="66" t="str">
+      <c r="C746" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="66" t="str">
+      <c r="C747" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="66" t="str">
+      <c r="C748" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="66" t="str">
+      <c r="C749" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="66" t="str">
+      <c r="C750" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="66" t="str">
+      <c r="C751" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="66" t="str">
+      <c r="C752" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="66" t="str">
+      <c r="C753" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="66" t="str">
+      <c r="C754" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="66" t="str">
+      <c r="C755" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="66" t="str">
+      <c r="C756" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="66" t="str">
+      <c r="C757" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="66" t="str">
+      <c r="C758" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="66" t="str">
+      <c r="C759" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="66" t="str">
+      <c r="C760" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="66" t="str">
+      <c r="C761" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="66" t="str">
+      <c r="C762" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="66" t="str">
+      <c r="C763" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="66" t="str">
+      <c r="C764" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="66" t="str">
+      <c r="C765" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="66" t="str">
+      <c r="C766" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="66" t="str">
+      <c r="C767" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="66" t="str">
+      <c r="C768" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="66" t="str">
+      <c r="C769" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="66" t="str">
+      <c r="C770" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="66" t="str">
+      <c r="C771" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="66" t="str">
+      <c r="C772" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="66" t="str">
+      <c r="C773" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="66" t="str">
+      <c r="C774" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="66" t="str">
+      <c r="C775" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="66" t="str">
+      <c r="C776" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="66" t="str">
+      <c r="C777" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="66" t="str">
+      <c r="C778" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="66" t="str">
+      <c r="C779" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="66" t="str">
+      <c r="C780" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="66" t="str">
+      <c r="C781" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="66" t="str">
+      <c r="C782" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="66" t="str">
+      <c r="C783" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="66" t="str">
+      <c r="C784" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="66" t="str">
+      <c r="C785" s="64" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="C4">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color theme="5"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D475356A-CFBB-42B9-9B17-916C094A3636}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12873,6 +12898,26 @@
     <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D475356A-CFBB-42B9-9B17-916C094A3636}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:borderColor theme="5"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C4</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
@@ -14653,16 +14698,16 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="80" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="80" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="80" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="80" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="80" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="80" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="80" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="80"/>
-    <col min="14" max="14" width="7.140625" style="80" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="80"/>
+    <col min="1" max="1" width="8.5703125" style="78" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="78" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="78" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="78" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="78" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="78" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="78" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="78"/>
+    <col min="14" max="14" width="7.140625" style="78" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="78"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
@@ -14696,188 +14741,188 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C5" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="80" t="s">
+      <c r="I5" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="81" t="s">
+      <c r="J5" s="79" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="80" t="str" cm="1">
+      <c r="B6" s="78" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="C6" s="82" cm="1">
+      <c r="C6" s="80" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic - Categories'!C2))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="80" t="str" cm="1">
+      <c r="I6" s="78" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="J6" s="82" cm="1">
+      <c r="J6" s="80" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Categories='Graphic - Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="80" t="str">
+      <c r="B7" s="78" t="str">
         <v>February</v>
       </c>
-      <c r="C7" s="82">
-        <v>0</v>
-      </c>
-      <c r="I7" s="80" t="str">
+      <c r="C7" s="80">
+        <v>0</v>
+      </c>
+      <c r="I7" s="78" t="str">
         <v>February</v>
       </c>
-      <c r="J7" s="82">
+      <c r="J7" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="80" t="str">
+      <c r="B8" s="78" t="str">
         <v>March</v>
       </c>
-      <c r="C8" s="82">
-        <v>0</v>
-      </c>
-      <c r="I8" s="80" t="str">
+      <c r="C8" s="80">
+        <v>0</v>
+      </c>
+      <c r="I8" s="78" t="str">
         <v>March</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="80" t="str">
+      <c r="B9" s="78" t="str">
         <v>April</v>
       </c>
-      <c r="C9" s="82">
-        <v>0</v>
-      </c>
-      <c r="I9" s="80" t="str">
+      <c r="C9" s="80">
+        <v>0</v>
+      </c>
+      <c r="I9" s="78" t="str">
         <v>April</v>
       </c>
-      <c r="J9" s="82">
+      <c r="J9" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="80" t="str">
+      <c r="B10" s="78" t="str">
         <v>May</v>
       </c>
-      <c r="C10" s="82">
-        <v>0</v>
-      </c>
-      <c r="I10" s="80" t="str">
+      <c r="C10" s="80">
+        <v>0</v>
+      </c>
+      <c r="I10" s="78" t="str">
         <v>May</v>
       </c>
-      <c r="J10" s="82">
+      <c r="J10" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="80" t="str">
+      <c r="B11" s="78" t="str">
         <v>June</v>
       </c>
-      <c r="C11" s="82">
-        <v>0</v>
-      </c>
-      <c r="I11" s="80" t="str">
+      <c r="C11" s="80">
+        <v>0</v>
+      </c>
+      <c r="I11" s="78" t="str">
         <v>June</v>
       </c>
-      <c r="J11" s="82">
+      <c r="J11" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="80" t="str">
+      <c r="B12" s="78" t="str">
         <v>July</v>
       </c>
-      <c r="C12" s="82">
-        <v>0</v>
-      </c>
-      <c r="I12" s="80" t="str">
+      <c r="C12" s="80">
+        <v>0</v>
+      </c>
+      <c r="I12" s="78" t="str">
         <v>July</v>
       </c>
-      <c r="J12" s="82">
+      <c r="J12" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="80" t="str">
+      <c r="B13" s="78" t="str">
         <v>August</v>
       </c>
-      <c r="C13" s="82">
-        <v>0</v>
-      </c>
-      <c r="I13" s="80" t="str">
+      <c r="C13" s="80">
+        <v>0</v>
+      </c>
+      <c r="I13" s="78" t="str">
         <v>August</v>
       </c>
-      <c r="J13" s="82">
+      <c r="J13" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="80" t="str">
+      <c r="B14" s="78" t="str">
         <v>September</v>
       </c>
-      <c r="C14" s="82">
-        <v>0</v>
-      </c>
-      <c r="I14" s="80" t="str">
+      <c r="C14" s="80">
+        <v>0</v>
+      </c>
+      <c r="I14" s="78" t="str">
         <v>September</v>
       </c>
-      <c r="J14" s="82">
+      <c r="J14" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="80" t="str">
+      <c r="B15" s="78" t="str">
         <v>October</v>
       </c>
-      <c r="C15" s="82">
-        <v>0</v>
-      </c>
-      <c r="I15" s="80" t="str">
+      <c r="C15" s="80">
+        <v>0</v>
+      </c>
+      <c r="I15" s="78" t="str">
         <v>October</v>
       </c>
-      <c r="J15" s="82">
+      <c r="J15" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="80" t="str">
+      <c r="B16" s="78" t="str">
         <v>November</v>
       </c>
-      <c r="C16" s="82">
-        <v>0</v>
-      </c>
-      <c r="I16" s="80" t="str">
+      <c r="C16" s="80">
+        <v>0</v>
+      </c>
+      <c r="I16" s="78" t="str">
         <v>November</v>
       </c>
-      <c r="J16" s="82">
+      <c r="J16" s="80">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="80" t="str">
+      <c r="B17" s="78" t="str">
         <v>December</v>
       </c>
-      <c r="C17" s="82">
-        <v>0</v>
-      </c>
-      <c r="I17" s="80" t="str">
+      <c r="C17" s="80">
+        <v>0</v>
+      </c>
+      <c r="I17" s="78" t="str">
         <v>December</v>
       </c>
-      <c r="J17" s="82">
+      <c r="J17" s="80">
         <v>0</v>
       </c>
     </row>
@@ -14947,15 +14992,15 @@
       <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="63" t="s">
+      <c r="K2" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="64"/>
+      <c r="L2" s="84"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="63" t="s">
+      <c r="N2" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="64"/>
+      <c r="O2" s="84"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C5085-8B16-4124-AA0C-A1B96F56362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E718BE-20FB-4337-A5EE-979BD24B9C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,7 +351,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,18 +379,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +571,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -678,15 +666,6 @@
     </xf>
     <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4090,7 +4069,9 @@
           <c:spPr>
             <a:ln w="34925" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4214,6 +4195,129 @@
         <c:axId val="590393455"/>
         <c:axId val="586649311"/>
       </c:lineChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Real Balance</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="dash"/>
+            <c:size val="20"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="75000"/>
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000">
+                    <a:alpha val="50000"/>
+                  </a:srgbClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront">
+                  <a:rot lat="0" lon="0" rev="0"/>
+                </a:camera>
+                <a:lightRig rig="threePt" dir="t">
+                  <a:rot lat="0" lon="0" rev="1200000"/>
+                </a:lightRig>
+              </a:scene3d>
+              <a:sp3d>
+                <a:bevelT w="63500" h="25400"/>
+              </a:sp3d>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Graphic - Annual'!$I$3:$I$14</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5287-4164-865E-BEA34211959C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="590393455"/>
+        <c:axId val="586649311"/>
+      </c:scatterChart>
       <c:catAx>
         <c:axId val="590393455"/>
         <c:scaling>
@@ -8923,13 +9027,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>6336</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>11315</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>27158</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>80769</xdr:rowOff>
+      <xdr:rowOff>101850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9349,16 +9453,16 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="65" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="63" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="64" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="64" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="65" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="68" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="67" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="65" customWidth="1"/>
-    <col min="10" max="10" width="10" style="65" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="65"/>
+    <col min="1" max="1" width="14.28515625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="60" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="61" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="61" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="62" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="65" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="64" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="62" customWidth="1"/>
+    <col min="10" max="10" width="10" style="62" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9369,87 +9473,87 @@
       <c r="C2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="77" t="s">
+      <c r="F2" s="74" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="42">
         <f>IF(B3="Expenses",HLOOKUP(B2,Expenses!B2:M20,19,FALSE),IF(B3="Net Salary",HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE),""))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="67" t="str" cm="1">
+      <c r="E3" s="64" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(B3="Expenses",Categories,IF(B3="Net Salary",Net_Salary,""))</f>
         <v>Bills</v>
       </c>
-      <c r="F3" s="75" cm="1">
+      <c r="F3" s="72" cm="1">
         <f t="array" ref="F3:F14">IF(B3="Expenses",_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses!B2:M2=B2),IF(B3="Net Salary",_xlfn._xlws.FILTER('Net Salary'!B3:M14,'Net Salary'!B2:M2=B2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="65"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="82" t="e">
+      <c r="C4" s="79" t="e">
         <f>HLOOKUP(B2,Expenses!B2:M20,19,FALSE)/HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E4" s="67" t="str">
+      <c r="E4" s="64" t="str">
         <v>Car maintenance</v>
       </c>
-      <c r="F4" s="75">
-        <v>0</v>
-      </c>
-      <c r="H4" s="65"/>
+      <c r="F4" s="72">
+        <v>0</v>
+      </c>
+      <c r="H4" s="62"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="42">
         <f>VLOOKUP(B2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="67" t="str">
+      <c r="E5" s="64" t="str">
         <v>Clothing</v>
       </c>
-      <c r="F5" s="75">
-        <v>0</v>
-      </c>
-      <c r="H5" s="65"/>
+      <c r="F5" s="72">
+        <v>0</v>
+      </c>
+      <c r="H5" s="62"/>
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="42">
         <f>'Graphic - Annual'!I15</f>
         <v>0</v>
       </c>
-      <c r="E6" s="67" t="str">
+      <c r="E6" s="64" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="F6" s="75">
-        <v>0</v>
-      </c>
-      <c r="H6" s="65"/>
+      <c r="F6" s="72">
+        <v>0</v>
+      </c>
+      <c r="H6" s="62"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="67" t="str">
+      <c r="E7" s="64" t="str">
         <v>Food</v>
       </c>
-      <c r="F7" s="75">
-        <v>0</v>
-      </c>
-      <c r="H7" s="65"/>
+      <c r="F7" s="72">
+        <v>0</v>
+      </c>
+      <c r="H7" s="62"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
@@ -9458,117 +9562,117 @@
       <c r="C8" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="67" t="str">
+      <c r="E8" s="64" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F8" s="75">
-        <v>0</v>
-      </c>
-      <c r="H8" s="65"/>
+      <c r="F8" s="72">
+        <v>0</v>
+      </c>
+      <c r="H8" s="62"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="46" cm="1">
+      <c r="C9" s="43" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>150</v>
       </c>
-      <c r="E9" s="67" t="str">
+      <c r="E9" s="64" t="str">
         <v>Hang out</v>
       </c>
-      <c r="F9" s="75">
-        <v>0</v>
-      </c>
-      <c r="H9" s="65"/>
+      <c r="F9" s="72">
+        <v>0</v>
+      </c>
+      <c r="H9" s="62"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="46" cm="1">
+      <c r="C10" s="43" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="67" t="str">
+      <c r="E10" s="64" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="F10" s="75">
-        <v>0</v>
-      </c>
-      <c r="H10" s="65"/>
+      <c r="F10" s="72">
+        <v>0</v>
+      </c>
+      <c r="H10" s="62"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="46" cm="1">
+      <c r="C11" s="43" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="67" t="str">
+      <c r="E11" s="64" t="str">
         <v>Insurance</v>
       </c>
-      <c r="F11" s="75">
-        <v>0</v>
-      </c>
-      <c r="H11" s="65"/>
+      <c r="F11" s="72">
+        <v>0</v>
+      </c>
+      <c r="H11" s="62"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="43">
         <f ca="1">SUM(C9:C11)</f>
         <v>150</v>
       </c>
-      <c r="E12" s="67" t="str">
+      <c r="E12" s="64" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="F12" s="75">
-        <v>0</v>
-      </c>
-      <c r="H12" s="65"/>
+      <c r="F12" s="72">
+        <v>0</v>
+      </c>
+      <c r="H12" s="62"/>
     </row>
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="42">
         <f ca="1">ROUND(C5-C12,2)</f>
         <v>-150</v>
       </c>
-      <c r="E13" s="67" t="str">
+      <c r="E13" s="64" t="str">
         <v>Travel</v>
       </c>
-      <c r="F13" s="75">
-        <v>0</v>
-      </c>
-      <c r="H13" s="65"/>
+      <c r="F13" s="72">
+        <v>0</v>
+      </c>
+      <c r="H13" s="62"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="E14" s="67" t="str">
+      <c r="A14" s="61"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="E14" s="64" t="str">
         <v>General expen.</v>
       </c>
-      <c r="F14" s="74">
-        <v>0</v>
-      </c>
-      <c r="H14" s="65"/>
+      <c r="F14" s="71">
+        <v>0</v>
+      </c>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="62"/>
+      <c r="H15" s="62"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="73">
+      <c r="A16" s="70">
         <f>SUBTOTAL(2,Tabela1[Date])</f>
         <v>1</v>
       </c>
@@ -9611,7 +9715,7 @@
       <c r="F17" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="44">
         <v>150</v>
       </c>
       <c r="H17" s="24"/>
@@ -9625,7 +9729,7 @@
       <c r="D18" s="22"/>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
-      <c r="G18" s="47"/>
+      <c r="G18" s="44"/>
       <c r="H18" s="24"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
@@ -9637,7 +9741,7 @@
       <c r="D19" s="22"/>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="47"/>
+      <c r="G19" s="44"/>
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -9649,3203 +9753,3203 @@
       <c r="D20" s="22"/>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
-      <c r="G20" s="47"/>
+      <c r="G20" s="44"/>
       <c r="H20" s="24"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="66"/>
+      <c r="G23" s="63"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="66"/>
+      <c r="G25" s="63"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="66"/>
+      <c r="G26" s="63"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="66"/>
+      <c r="G27" s="63"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="66"/>
+      <c r="G28" s="63"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="65" t="s">
+      <c r="I38" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="66"/>
+      <c r="G137" s="63"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="66"/>
+      <c r="G139" s="63"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="66"/>
+      <c r="G140" s="63"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="66"/>
+      <c r="G141" s="63"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="66"/>
+      <c r="G142" s="63"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="64" t="str">
+      <c r="C248" s="61" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="64" t="str">
+      <c r="C249" s="61" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="69"/>
+      <c r="G249" s="66"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="64" t="str">
+      <c r="C258" s="61" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="64" t="str">
+      <c r="D258" s="61" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="64" t="str">
+      <c r="E258" s="61" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="64" t="str">
+      <c r="F258" s="61" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="64" t="str">
+      <c r="G258" s="61" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="64" t="str">
+      <c r="C267" s="61" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="64" t="str">
+      <c r="C268" s="61" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="64" t="str">
+      <c r="C269" s="61" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="64" t="str">
+      <c r="C270" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="64" t="str">
+      <c r="C271" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="64" t="str">
+      <c r="C272" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="64" t="str">
+      <c r="C273" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="64" t="str">
+      <c r="C274" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="64" t="str">
+      <c r="C275" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="64" t="str">
+      <c r="C276" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="64" t="str">
+      <c r="C277" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="64" t="str">
+      <c r="C278" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="64" t="str">
+      <c r="C279" s="61" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="64" t="str">
+      <c r="C280" s="61" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="64" t="str">
+      <c r="C281" s="61" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="64" t="str">
+      <c r="C282" s="61" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="66"/>
-      <c r="H282" s="70"/>
+      <c r="G282" s="63"/>
+      <c r="H282" s="67"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="65"/>
-      <c r="C283" s="65"/>
-      <c r="D283" s="65"/>
-      <c r="E283" s="71"/>
-      <c r="F283" s="71"/>
-      <c r="G283" s="66"/>
-      <c r="H283" s="70"/>
+      <c r="B283" s="62"/>
+      <c r="C283" s="62"/>
+      <c r="D283" s="62"/>
+      <c r="E283" s="68"/>
+      <c r="F283" s="68"/>
+      <c r="G283" s="63"/>
+      <c r="H283" s="67"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="65"/>
-      <c r="C284" s="65"/>
-      <c r="D284" s="65"/>
-      <c r="E284" s="71"/>
-      <c r="F284" s="71"/>
-      <c r="G284" s="66"/>
-      <c r="H284" s="70"/>
+      <c r="B284" s="62"/>
+      <c r="C284" s="62"/>
+      <c r="D284" s="62"/>
+      <c r="E284" s="68"/>
+      <c r="F284" s="68"/>
+      <c r="G284" s="63"/>
+      <c r="H284" s="67"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="65"/>
-      <c r="C285" s="65"/>
-      <c r="D285" s="65"/>
-      <c r="E285" s="71"/>
-      <c r="F285" s="71"/>
-      <c r="G285" s="66"/>
-      <c r="H285" s="70"/>
+      <c r="B285" s="62"/>
+      <c r="C285" s="62"/>
+      <c r="D285" s="62"/>
+      <c r="E285" s="68"/>
+      <c r="F285" s="68"/>
+      <c r="G285" s="63"/>
+      <c r="H285" s="67"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="65"/>
-      <c r="C286" s="72"/>
-      <c r="D286" s="72"/>
-      <c r="E286" s="71"/>
-      <c r="F286" s="71"/>
-      <c r="G286" s="66"/>
-      <c r="H286" s="70"/>
+      <c r="B286" s="62"/>
+      <c r="C286" s="69"/>
+      <c r="D286" s="69"/>
+      <c r="E286" s="68"/>
+      <c r="F286" s="68"/>
+      <c r="G286" s="63"/>
+      <c r="H286" s="67"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="65"/>
-      <c r="C287" s="65"/>
-      <c r="D287" s="65"/>
-      <c r="G287" s="65"/>
+      <c r="B287" s="62"/>
+      <c r="C287" s="62"/>
+      <c r="D287" s="62"/>
+      <c r="G287" s="62"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="65"/>
-      <c r="C288" s="65"/>
-      <c r="D288" s="65"/>
-      <c r="G288" s="65"/>
+      <c r="B288" s="62"/>
+      <c r="C288" s="62"/>
+      <c r="D288" s="62"/>
+      <c r="G288" s="62"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="65"/>
-      <c r="C289" s="65"/>
-      <c r="D289" s="65"/>
-      <c r="G289" s="65"/>
+      <c r="B289" s="62"/>
+      <c r="C289" s="62"/>
+      <c r="D289" s="62"/>
+      <c r="G289" s="62"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="65"/>
-      <c r="C290" s="65"/>
-      <c r="D290" s="65"/>
-      <c r="G290" s="65"/>
+      <c r="B290" s="62"/>
+      <c r="C290" s="62"/>
+      <c r="D290" s="62"/>
+      <c r="G290" s="62"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="65"/>
-      <c r="C291" s="65"/>
-      <c r="D291" s="65"/>
-      <c r="G291" s="65"/>
+      <c r="B291" s="62"/>
+      <c r="C291" s="62"/>
+      <c r="D291" s="62"/>
+      <c r="G291" s="62"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="65"/>
-      <c r="C292" s="65"/>
-      <c r="D292" s="65"/>
-      <c r="G292" s="65"/>
+      <c r="B292" s="62"/>
+      <c r="C292" s="62"/>
+      <c r="D292" s="62"/>
+      <c r="G292" s="62"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="65"/>
-      <c r="C293" s="65"/>
-      <c r="D293" s="65"/>
-      <c r="G293" s="65"/>
+      <c r="B293" s="62"/>
+      <c r="C293" s="62"/>
+      <c r="D293" s="62"/>
+      <c r="G293" s="62"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="64" t="str">
+      <c r="C294" s="61" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="64" t="str">
+      <c r="C295" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="64" t="str">
+      <c r="C296" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="64" t="str">
+      <c r="C297" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="64" t="str">
+      <c r="C298" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="64" t="str">
+      <c r="C299" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="64" t="str">
+      <c r="C300" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="64" t="str">
+      <c r="C301" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="64" t="str">
+      <c r="C302" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="64" t="str">
+      <c r="C303" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="64" t="str">
+      <c r="C304" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="64" t="str">
+      <c r="C305" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="64" t="str">
+      <c r="C306" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="64" t="str">
+      <c r="C307" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="64" t="str">
+      <c r="C308" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="64" t="str">
+      <c r="C309" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="64" t="str">
+      <c r="C310" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="64" t="str">
+      <c r="C311" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="64" t="str">
+      <c r="C312" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="64" t="str">
+      <c r="C313" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="64" t="str">
+      <c r="C314" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="64" t="str">
+      <c r="C315" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="64" t="str">
+      <c r="C316" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="64" t="str">
+      <c r="C317" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="64" t="str">
+      <c r="C318" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="64" t="str">
+      <c r="C319" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="64" t="str">
+      <c r="C320" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="64" t="str">
+      <c r="C321" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="64" t="str">
+      <c r="C322" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="64" t="str">
+      <c r="C323" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="64" t="str">
+      <c r="C324" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="64" t="str">
+      <c r="C325" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="64" t="str">
+      <c r="C326" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="64" t="str">
+      <c r="C327" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="64" t="str">
+      <c r="C328" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="64" t="str">
+      <c r="C329" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="64" t="str">
+      <c r="C330" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="64" t="str">
+      <c r="C331" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="64" t="str">
+      <c r="C332" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="64" t="str">
+      <c r="C333" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="64" t="str">
+      <c r="C334" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="64" t="str">
+      <c r="C335" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="64" t="str">
+      <c r="C336" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="64" t="str">
+      <c r="C337" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="64" t="str">
+      <c r="C338" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="64" t="str">
+      <c r="C339" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="64" t="str">
+      <c r="C340" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="64" t="str">
+      <c r="C341" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="64" t="str">
+      <c r="C342" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="64" t="str">
+      <c r="C343" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="64" t="str">
+      <c r="C344" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="64" t="str">
+      <c r="C345" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="64" t="str">
+      <c r="C346" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="64" t="str">
+      <c r="C347" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="64" t="str">
+      <c r="C348" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="64" t="str">
+      <c r="C349" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="64" t="str">
+      <c r="C350" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="64" t="str">
+      <c r="C351" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="64" t="str">
+      <c r="C352" s="61" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="64" t="str">
+      <c r="C353" s="61" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="64" t="str">
+      <c r="C354" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="64" t="str">
+      <c r="C355" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="64" t="str">
+      <c r="C356" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="64" t="str">
+      <c r="C357" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="64" t="str">
+      <c r="C358" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="64" t="str">
+      <c r="C359" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="64" t="str">
+      <c r="C360" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="64" t="str">
+      <c r="C361" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="64" t="str">
+      <c r="C362" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="64" t="str">
+      <c r="C363" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="64" t="str">
+      <c r="C364" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="64" t="str">
+      <c r="C365" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="64" t="str">
+      <c r="C366" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="64" t="str">
+      <c r="C367" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="64" t="str">
+      <c r="C368" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="64" t="str">
+      <c r="C369" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="64" t="str">
+      <c r="C370" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="64" t="str">
+      <c r="C371" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="64" t="str">
+      <c r="C372" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="64" t="str">
+      <c r="C373" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="64" t="str">
+      <c r="C374" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="64" t="str">
+      <c r="C375" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="64" t="str">
+      <c r="C376" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="64" t="str">
+      <c r="C377" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="64" t="str">
+      <c r="C378" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="64" t="str">
+      <c r="C379" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="64" t="str">
+      <c r="C380" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="64" t="str">
+      <c r="C381" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="64" t="str">
+      <c r="C382" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="64" t="str">
+      <c r="C383" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="64" t="str">
+      <c r="C384" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="64" t="str">
+      <c r="C385" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="64" t="str">
+      <c r="C386" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="64" t="str">
+      <c r="C387" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="64" t="str">
+      <c r="C388" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="64" t="str">
+      <c r="C389" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="64" t="str">
+      <c r="C390" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="64" t="str">
+      <c r="C391" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="64" t="str">
+      <c r="C392" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="64" t="str">
+      <c r="C393" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="64" t="str">
+      <c r="C394" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="64" t="str">
+      <c r="C395" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="64" t="str">
+      <c r="C396" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="64" t="str">
+      <c r="C397" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="64" t="str">
+      <c r="C398" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="64" t="str">
+      <c r="C399" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="64" t="str">
+      <c r="C400" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="64" t="str">
+      <c r="C401" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="64" t="str">
+      <c r="C402" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="64" t="str">
+      <c r="C403" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="64" t="str">
+      <c r="C404" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="64" t="str">
+      <c r="C405" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="64" t="str">
+      <c r="C406" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="64" t="str">
+      <c r="C407" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="64" t="str">
+      <c r="C408" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="64" t="str">
+      <c r="C409" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="64" t="str">
+      <c r="C410" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="64" t="str">
+      <c r="C411" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="64" t="str">
+      <c r="C412" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="64" t="str">
+      <c r="C413" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="64" t="str">
+      <c r="C414" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="64" t="str">
+      <c r="C415" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="64" t="str">
+      <c r="C416" s="61" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="64" t="str">
+      <c r="C417" s="61" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="64" t="str">
+      <c r="C418" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="64" t="str">
+      <c r="C419" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="64" t="str">
+      <c r="C420" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="64" t="str">
+      <c r="C421" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="64" t="str">
+      <c r="C422" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="64" t="str">
+      <c r="C423" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="64" t="str">
+      <c r="C424" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="64" t="str">
+      <c r="C425" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="64" t="str">
+      <c r="C426" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="64" t="str">
+      <c r="C427" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="64" t="str">
+      <c r="C428" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="64" t="str">
+      <c r="C429" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="64" t="str">
+      <c r="C430" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="64" t="str">
+      <c r="C431" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="64" t="str">
+      <c r="C432" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="64" t="str">
+      <c r="C433" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="64" t="str">
+      <c r="C434" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="64" t="str">
+      <c r="C435" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="64" t="str">
+      <c r="C436" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="64" t="str">
+      <c r="C437" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="64" t="str">
+      <c r="C438" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="64" t="str">
+      <c r="C439" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="64" t="str">
+      <c r="C440" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="64" t="str">
+      <c r="C441" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="64" t="str">
+      <c r="C442" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="64" t="str">
+      <c r="C443" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="64" t="str">
+      <c r="C444" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="64" t="str">
+      <c r="C445" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="64" t="str">
+      <c r="C446" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="64" t="str">
+      <c r="C447" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="64" t="str">
+      <c r="C448" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="64" t="str">
+      <c r="C449" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="64" t="str">
+      <c r="C450" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="64" t="str">
+      <c r="C451" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="64" t="str">
+      <c r="C452" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="64" t="str">
+      <c r="C453" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="64" t="str">
+      <c r="C454" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="64" t="str">
+      <c r="C455" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="64" t="str">
+      <c r="C456" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="64" t="str">
+      <c r="C457" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="64" t="str">
+      <c r="C458" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="64" t="str">
+      <c r="C459" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="64" t="str">
+      <c r="C460" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="64" t="str">
+      <c r="C461" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="64" t="str">
+      <c r="C462" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="64" t="str">
+      <c r="C463" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="64" t="str">
+      <c r="C464" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="64" t="str">
+      <c r="C465" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="64" t="str">
+      <c r="C466" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="64" t="str">
+      <c r="C467" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="64" t="str">
+      <c r="C468" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="64" t="str">
+      <c r="C469" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="64" t="str">
+      <c r="C470" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="64" t="str">
+      <c r="C471" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="64" t="str">
+      <c r="C472" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="64" t="str">
+      <c r="C473" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="64" t="str">
+      <c r="C474" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="64" t="str">
+      <c r="C475" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="64" t="str">
+      <c r="C476" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="64" t="str">
+      <c r="C477" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="64" t="str">
+      <c r="C478" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="64" t="str">
+      <c r="C479" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="64" t="str">
+      <c r="C480" s="61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="64" t="str">
+      <c r="C481" s="61" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="64" t="str">
+      <c r="C482" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="64" t="str">
+      <c r="C483" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="64" t="str">
+      <c r="C484" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="64" t="str">
+      <c r="C485" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="64" t="str">
+      <c r="C486" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="64" t="str">
+      <c r="C487" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="64" t="str">
+      <c r="C488" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="64" t="str">
+      <c r="C489" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="64" t="str">
+      <c r="C490" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="64" t="str">
+      <c r="C491" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="64" t="str">
+      <c r="C492" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="64" t="str">
+      <c r="C493" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="64" t="str">
+      <c r="C494" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="64" t="str">
+      <c r="C495" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="64" t="str">
+      <c r="C496" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="64" t="str">
+      <c r="C497" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="64" t="str">
+      <c r="C498" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="64" t="str">
+      <c r="C499" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="64" t="str">
+      <c r="C500" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="64" t="str">
+      <c r="C501" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="64" t="str">
+      <c r="C502" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="64" t="str">
+      <c r="C503" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="64" t="str">
+      <c r="C504" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="64" t="str">
+      <c r="C505" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="64" t="str">
+      <c r="C506" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="64" t="str">
+      <c r="C507" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="64" t="str">
+      <c r="C508" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="64" t="str">
+      <c r="C509" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="64" t="str">
+      <c r="C510" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="64" t="str">
+      <c r="C511" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="64" t="str">
+      <c r="C512" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="64" t="str">
+      <c r="C513" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="64" t="str">
+      <c r="C514" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="64" t="str">
+      <c r="C515" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="64" t="str">
+      <c r="C516" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="64" t="str">
+      <c r="C517" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="64" t="str">
+      <c r="C518" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="64" t="str">
+      <c r="C519" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="64" t="str">
+      <c r="C520" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="64" t="str">
+      <c r="C521" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="64" t="str">
+      <c r="C522" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="64" t="str">
+      <c r="C523" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="64" t="str">
+      <c r="C524" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="64" t="str">
+      <c r="C525" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="64" t="str">
+      <c r="C526" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="64" t="str">
+      <c r="C527" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="64" t="str">
+      <c r="C528" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="64" t="str">
+      <c r="C529" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="64" t="str">
+      <c r="C530" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="64" t="str">
+      <c r="C531" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="64" t="str">
+      <c r="C532" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="64" t="str">
+      <c r="C533" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="64" t="str">
+      <c r="C534" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="64" t="str">
+      <c r="C535" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="64" t="str">
+      <c r="C536" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="64" t="str">
+      <c r="C537" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="64" t="str">
+      <c r="C538" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="64" t="str">
+      <c r="C539" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="64" t="str">
+      <c r="C540" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="64" t="str">
+      <c r="C541" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="64" t="str">
+      <c r="C542" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="64" t="str">
+      <c r="C543" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="64" t="str">
+      <c r="C544" s="61" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="64" t="str">
+      <c r="C545" s="61" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="64" t="str">
+      <c r="C546" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="64" t="str">
+      <c r="C547" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="64" t="str">
+      <c r="C548" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="64" t="str">
+      <c r="C549" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="64" t="str">
+      <c r="C550" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="64" t="str">
+      <c r="C551" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="64" t="str">
+      <c r="C552" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="64" t="str">
+      <c r="C553" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="64" t="str">
+      <c r="C554" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="64" t="str">
+      <c r="C555" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="64" t="str">
+      <c r="C556" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="64" t="str">
+      <c r="C557" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="64" t="str">
+      <c r="C558" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="64" t="str">
+      <c r="C559" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="64" t="str">
+      <c r="C560" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="64" t="str">
+      <c r="C561" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="64" t="str">
+      <c r="C562" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="64" t="str">
+      <c r="C563" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="64" t="str">
+      <c r="C564" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="64" t="str">
+      <c r="C565" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="64" t="str">
+      <c r="C566" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="64" t="str">
+      <c r="C567" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="64" t="str">
+      <c r="C568" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="64" t="str">
+      <c r="C569" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="64" t="str">
+      <c r="C570" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="64" t="str">
+      <c r="C571" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="64" t="str">
+      <c r="C572" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="64" t="str">
+      <c r="C573" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="64" t="str">
+      <c r="C574" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="64" t="str">
+      <c r="C575" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="64" t="str">
+      <c r="C576" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="64" t="str">
+      <c r="C577" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="64" t="str">
+      <c r="C578" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="64" t="str">
+      <c r="C579" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="64" t="str">
+      <c r="C580" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="64" t="str">
+      <c r="C581" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="64" t="str">
+      <c r="C582" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="64" t="str">
+      <c r="C583" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="64" t="str">
+      <c r="C584" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="64" t="str">
+      <c r="C585" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="64" t="str">
+      <c r="C586" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="64" t="str">
+      <c r="C587" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="64" t="str">
+      <c r="C588" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="64" t="str">
+      <c r="C589" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="64" t="str">
+      <c r="C590" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="64" t="str">
+      <c r="C591" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="64" t="str">
+      <c r="C592" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="64" t="str">
+      <c r="C593" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="64" t="str">
+      <c r="C594" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="64" t="str">
+      <c r="C595" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="64" t="str">
+      <c r="C596" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="64" t="str">
+      <c r="C597" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="64" t="str">
+      <c r="C598" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="64" t="str">
+      <c r="C599" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="64" t="str">
+      <c r="C600" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="64" t="str">
+      <c r="C601" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="64" t="str">
+      <c r="C602" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="64" t="str">
+      <c r="C603" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="64" t="str">
+      <c r="C604" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="64" t="str">
+      <c r="C605" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="64" t="str">
+      <c r="C606" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="64" t="str">
+      <c r="C607" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="64" t="str">
+      <c r="C608" s="61" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="64" t="str">
+      <c r="C609" s="61" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="64" t="str">
+      <c r="C610" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="64" t="str">
+      <c r="C611" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="64" t="str">
+      <c r="C612" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="64" t="str">
+      <c r="C613" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="64" t="str">
+      <c r="C614" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="64" t="str">
+      <c r="C615" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="64" t="str">
+      <c r="C616" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="64" t="str">
+      <c r="C617" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="64" t="str">
+      <c r="C618" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="64" t="str">
+      <c r="C619" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="64" t="str">
+      <c r="C620" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="64" t="str">
+      <c r="C621" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="64" t="str">
+      <c r="C622" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="64" t="str">
+      <c r="C623" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="64" t="str">
+      <c r="C624" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="64" t="str">
+      <c r="C625" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="64" t="str">
+      <c r="C626" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="64" t="str">
+      <c r="C627" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="64" t="str">
+      <c r="C628" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="64" t="str">
+      <c r="C629" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="64" t="str">
+      <c r="C630" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="64" t="str">
+      <c r="C631" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="64" t="str">
+      <c r="C632" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="64" t="str">
+      <c r="C633" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="64" t="str">
+      <c r="C634" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="64" t="str">
+      <c r="C635" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="64" t="str">
+      <c r="C636" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="64" t="str">
+      <c r="C637" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="64" t="str">
+      <c r="C638" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="64" t="str">
+      <c r="C639" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="64" t="str">
+      <c r="C640" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="64" t="str">
+      <c r="C641" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="64" t="str">
+      <c r="C642" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="64" t="str">
+      <c r="C643" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="64" t="str">
+      <c r="C644" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="64" t="str">
+      <c r="C645" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="64" t="str">
+      <c r="C646" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="64" t="str">
+      <c r="C647" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="64" t="str">
+      <c r="C648" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="64" t="str">
+      <c r="C649" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="64" t="str">
+      <c r="C650" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="64" t="str">
+      <c r="C651" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="64" t="str">
+      <c r="C652" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="64" t="str">
+      <c r="C653" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="64" t="str">
+      <c r="C654" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="64" t="str">
+      <c r="C655" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="64" t="str">
+      <c r="C656" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="64" t="str">
+      <c r="C657" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="64" t="str">
+      <c r="C658" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="64" t="str">
+      <c r="C659" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="64" t="str">
+      <c r="C660" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="64" t="str">
+      <c r="C661" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="64" t="str">
+      <c r="C662" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="64" t="str">
+      <c r="C663" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="64" t="str">
+      <c r="C664" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="64" t="str">
+      <c r="C665" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="64" t="str">
+      <c r="C666" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="64" t="str">
+      <c r="C667" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="64" t="str">
+      <c r="C668" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="64" t="str">
+      <c r="C669" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="64" t="str">
+      <c r="C670" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="64" t="str">
+      <c r="C671" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="64" t="str">
+      <c r="C672" s="61" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="64" t="str">
+      <c r="C673" s="61" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="64" t="str">
+      <c r="C674" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="64" t="str">
+      <c r="C675" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="64" t="str">
+      <c r="C676" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="64" t="str">
+      <c r="C677" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="64" t="str">
+      <c r="C678" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="64" t="str">
+      <c r="C679" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="64" t="str">
+      <c r="C680" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="64" t="str">
+      <c r="C681" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="64" t="str">
+      <c r="C682" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="64" t="str">
+      <c r="C683" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="64" t="str">
+      <c r="C684" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="64" t="str">
+      <c r="C685" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="64" t="str">
+      <c r="C686" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="64" t="str">
+      <c r="C687" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="64" t="str">
+      <c r="C688" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="64" t="str">
+      <c r="C689" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="64" t="str">
+      <c r="C690" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="64" t="str">
+      <c r="C691" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="64" t="str">
+      <c r="C692" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="64" t="str">
+      <c r="C693" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="64" t="str">
+      <c r="C694" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="64" t="str">
+      <c r="C695" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="64" t="str">
+      <c r="C696" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="64" t="str">
+      <c r="C697" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="64" t="str">
+      <c r="C698" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="64" t="str">
+      <c r="C699" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="64" t="str">
+      <c r="C700" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="64" t="str">
+      <c r="C701" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="64" t="str">
+      <c r="C702" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="64" t="str">
+      <c r="C703" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="64" t="str">
+      <c r="C704" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="64" t="str">
+      <c r="C705" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="64" t="str">
+      <c r="C706" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="64" t="str">
+      <c r="C707" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="64" t="str">
+      <c r="C708" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="64" t="str">
+      <c r="C709" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="64" t="str">
+      <c r="C710" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="64" t="str">
+      <c r="C711" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="64" t="str">
+      <c r="C712" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="64" t="str">
+      <c r="C713" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="64" t="str">
+      <c r="C714" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="64" t="str">
+      <c r="C715" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="64" t="str">
+      <c r="C716" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="64" t="str">
+      <c r="C717" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="64" t="str">
+      <c r="C718" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="64" t="str">
+      <c r="C719" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="64" t="str">
+      <c r="C720" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="64" t="str">
+      <c r="C721" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="64" t="str">
+      <c r="C722" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="64" t="str">
+      <c r="C723" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="64" t="str">
+      <c r="C724" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="64" t="str">
+      <c r="C725" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="64" t="str">
+      <c r="C726" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="64" t="str">
+      <c r="C727" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="64" t="str">
+      <c r="C728" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="64" t="str">
+      <c r="C729" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="64" t="str">
+      <c r="C730" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="64" t="str">
+      <c r="C731" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="64" t="str">
+      <c r="C732" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="64" t="str">
+      <c r="C733" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="64" t="str">
+      <c r="C734" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="64" t="str">
+      <c r="C735" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="64" t="str">
+      <c r="C736" s="61" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="64" t="str">
+      <c r="C737" s="61" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="64" t="str">
+      <c r="C738" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="64" t="str">
+      <c r="C739" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="64" t="str">
+      <c r="C740" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="64" t="str">
+      <c r="C741" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="64" t="str">
+      <c r="C742" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="64" t="str">
+      <c r="C743" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="64" t="str">
+      <c r="C744" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="64" t="str">
+      <c r="C745" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="64" t="str">
+      <c r="C746" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="64" t="str">
+      <c r="C747" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="64" t="str">
+      <c r="C748" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="64" t="str">
+      <c r="C749" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="64" t="str">
+      <c r="C750" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="64" t="str">
+      <c r="C751" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="64" t="str">
+      <c r="C752" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="64" t="str">
+      <c r="C753" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="64" t="str">
+      <c r="C754" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="64" t="str">
+      <c r="C755" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="64" t="str">
+      <c r="C756" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="64" t="str">
+      <c r="C757" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="64" t="str">
+      <c r="C758" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="64" t="str">
+      <c r="C759" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="64" t="str">
+      <c r="C760" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="64" t="str">
+      <c r="C761" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="64" t="str">
+      <c r="C762" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="64" t="str">
+      <c r="C763" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="64" t="str">
+      <c r="C764" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="64" t="str">
+      <c r="C765" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="64" t="str">
+      <c r="C766" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="64" t="str">
+      <c r="C767" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="64" t="str">
+      <c r="C768" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="64" t="str">
+      <c r="C769" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="64" t="str">
+      <c r="C770" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="64" t="str">
+      <c r="C771" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="64" t="str">
+      <c r="C772" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="64" t="str">
+      <c r="C773" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="64" t="str">
+      <c r="C774" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="64" t="str">
+      <c r="C775" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="64" t="str">
+      <c r="C776" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="64" t="str">
+      <c r="C777" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="64" t="str">
+      <c r="C778" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="64" t="str">
+      <c r="C779" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="64" t="str">
+      <c r="C780" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="64" t="str">
+      <c r="C781" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="64" t="str">
+      <c r="C782" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="64" t="str">
+      <c r="C783" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="64" t="str">
+      <c r="C784" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="64" t="str">
+      <c r="C785" s="61" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
@@ -12986,637 +13090,637 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="46">
+      <c r="G3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="46">
+      <c r="J3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="46">
+      <c r="K3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="46">
+      <c r="M3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="46">
+      <c r="B4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="46">
+      <c r="I4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="46">
+      <c r="J4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="46">
+      <c r="K4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="46">
+      <c r="L4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="46">
+      <c r="M4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="46">
+      <c r="B5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="46">
+      <c r="G6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="46">
+      <c r="K6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="46">
+      <c r="H7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="46">
+      <c r="K7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="46">
+      <c r="L7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="46">
+      <c r="H8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="46">
+      <c r="J8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="46">
+      <c r="J9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46">
+      <c r="K9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="46">
+      <c r="L9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="46">
+      <c r="J10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46">
+      <c r="K10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="46">
+      <c r="L10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="46">
+      <c r="M10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="46">
+      <c r="K11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="46">
+      <c r="L11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="46">
+      <c r="M11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="46">
+      <c r="J12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="46">
+      <c r="J13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="46">
+      <c r="L13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="46">
+      <c r="M13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="46">
+      <c r="L14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="46">
+      <c r="M14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
@@ -13625,51 +13729,51 @@
       <c r="A16" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="43">
         <f>ROUND(SUM(B3:B7)-SUM(B8:B14),2)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="43">
         <f t="shared" ref="C16:M16" si="0">ROUND(SUM(C3:C7)-SUM(C8:C14),2)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="46">
+      <c r="L16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M16" s="46">
+      <c r="M16" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -13793,107 +13897,107 @@
       </c>
     </row>
     <row r="3" spans="1:13" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="43">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="43">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="43">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="43">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="43">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="46">
+      <c r="G3" s="43">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="43">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="43">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="46">
+      <c r="J3" s="43">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="46">
+      <c r="K3" s="43">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="43">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="46">
+      <c r="M3" s="43">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="57">
         <f>B3-(SUM(B7:B18))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="57">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="60">
+      <c r="I4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="60">
+      <c r="J4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="60">
+      <c r="K4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="60">
+      <c r="L4" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="60">
+      <c r="M4" s="57">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>0</v>
       </c>
@@ -13914,43 +14018,43 @@
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="44" t="s">
+      <c r="K6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="41" t="s">
         <v>20</v>
       </c>
     </row>
@@ -13958,51 +14062,51 @@
       <c r="A7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="46">
+      <c r="H7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="46">
+      <c r="K7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="46">
+      <c r="L7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
@@ -14011,51 +14115,51 @@
       <c r="A8" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="46">
+      <c r="H8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="46">
+      <c r="J8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
@@ -14064,51 +14168,51 @@
       <c r="A9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="46">
+      <c r="J9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46">
+      <c r="K9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="46">
+      <c r="L9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="46">
+      <c r="M9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
@@ -14117,51 +14221,51 @@
       <c r="A10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="46">
+      <c r="I10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="46">
+      <c r="J10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46">
+      <c r="K10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="46">
+      <c r="L10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="46">
+      <c r="M10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
@@ -14170,51 +14274,51 @@
       <c r="A11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="46">
+      <c r="K11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="46">
+      <c r="L11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="46">
+      <c r="M11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
@@ -14223,51 +14327,51 @@
       <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="46">
+      <c r="J12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
@@ -14276,104 +14380,104 @@
       <c r="A13" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="46">
+      <c r="J13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="46">
+      <c r="L13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="46">
+      <c r="M13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="46">
+      <c r="L14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="46">
+      <c r="M14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
@@ -14382,51 +14486,51 @@
       <c r="A15" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="46">
+      <c r="J15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="46">
+      <c r="L15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="46">
+      <c r="M15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
@@ -14435,51 +14539,51 @@
       <c r="A16" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="46">
+      <c r="L16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="46">
+      <c r="M16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
@@ -14488,51 +14592,51 @@
       <c r="A17" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="46">
+      <c r="J17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="46">
+      <c r="L17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="46">
+      <c r="M17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
@@ -14541,51 +14645,51 @@
       <c r="A18" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="46">
+      <c r="H18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="46">
+      <c r="J18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="46">
+      <c r="K18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="46">
+      <c r="L18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="46">
+      <c r="M18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
@@ -14608,51 +14712,51 @@
       <c r="A20" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="61">
+      <c r="B20" s="58">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="61">
+      <c r="C20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="61">
+      <c r="J20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="61">
+      <c r="K20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="61">
+      <c r="L20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="61">
+      <c r="M20" s="58">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -14698,16 +14802,16 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="78" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="78" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="78" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="78" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="78" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="78" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="78" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="78"/>
-    <col min="14" max="14" width="7.140625" style="78" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="78"/>
+    <col min="1" max="1" width="8.5703125" style="75" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="75" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="75" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="75" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="75" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="75"/>
+    <col min="14" max="14" width="7.140625" style="75" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="75"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
@@ -14741,188 +14845,188 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="78" t="s">
+      <c r="I5" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="79" t="s">
+      <c r="J5" s="76" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="78" t="str" cm="1">
+      <c r="B6" s="75" t="str" cm="1">
         <f t="array" ref="B6:B17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="C6" s="80" cm="1">
+      <c r="C6" s="77" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic - Categories'!C2))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="78" t="str" cm="1">
+      <c r="I6" s="75" t="str" cm="1">
         <f t="array" ref="I6:I17">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="J6" s="80" cm="1">
+      <c r="J6" s="77" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Categories='Graphic - Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="78" t="str">
+      <c r="B7" s="75" t="str">
         <v>February</v>
       </c>
-      <c r="C7" s="80">
-        <v>0</v>
-      </c>
-      <c r="I7" s="78" t="str">
+      <c r="C7" s="77">
+        <v>0</v>
+      </c>
+      <c r="I7" s="75" t="str">
         <v>February</v>
       </c>
-      <c r="J7" s="80">
+      <c r="J7" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="78" t="str">
+      <c r="B8" s="75" t="str">
         <v>March</v>
       </c>
-      <c r="C8" s="80">
-        <v>0</v>
-      </c>
-      <c r="I8" s="78" t="str">
+      <c r="C8" s="77">
+        <v>0</v>
+      </c>
+      <c r="I8" s="75" t="str">
         <v>March</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="78" t="str">
+      <c r="B9" s="75" t="str">
         <v>April</v>
       </c>
-      <c r="C9" s="80">
-        <v>0</v>
-      </c>
-      <c r="I9" s="78" t="str">
+      <c r="C9" s="77">
+        <v>0</v>
+      </c>
+      <c r="I9" s="75" t="str">
         <v>April</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="78" t="str">
+      <c r="B10" s="75" t="str">
         <v>May</v>
       </c>
-      <c r="C10" s="80">
-        <v>0</v>
-      </c>
-      <c r="I10" s="78" t="str">
+      <c r="C10" s="77">
+        <v>0</v>
+      </c>
+      <c r="I10" s="75" t="str">
         <v>May</v>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="78" t="str">
+      <c r="B11" s="75" t="str">
         <v>June</v>
       </c>
-      <c r="C11" s="80">
-        <v>0</v>
-      </c>
-      <c r="I11" s="78" t="str">
+      <c r="C11" s="77">
+        <v>0</v>
+      </c>
+      <c r="I11" s="75" t="str">
         <v>June</v>
       </c>
-      <c r="J11" s="80">
+      <c r="J11" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="78" t="str">
+      <c r="B12" s="75" t="str">
         <v>July</v>
       </c>
-      <c r="C12" s="80">
-        <v>0</v>
-      </c>
-      <c r="I12" s="78" t="str">
+      <c r="C12" s="77">
+        <v>0</v>
+      </c>
+      <c r="I12" s="75" t="str">
         <v>July</v>
       </c>
-      <c r="J12" s="80">
+      <c r="J12" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="78" t="str">
+      <c r="B13" s="75" t="str">
         <v>August</v>
       </c>
-      <c r="C13" s="80">
-        <v>0</v>
-      </c>
-      <c r="I13" s="78" t="str">
+      <c r="C13" s="77">
+        <v>0</v>
+      </c>
+      <c r="I13" s="75" t="str">
         <v>August</v>
       </c>
-      <c r="J13" s="80">
+      <c r="J13" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="78" t="str">
+      <c r="B14" s="75" t="str">
         <v>September</v>
       </c>
-      <c r="C14" s="80">
-        <v>0</v>
-      </c>
-      <c r="I14" s="78" t="str">
+      <c r="C14" s="77">
+        <v>0</v>
+      </c>
+      <c r="I14" s="75" t="str">
         <v>September</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="78" t="str">
+      <c r="B15" s="75" t="str">
         <v>October</v>
       </c>
-      <c r="C15" s="80">
-        <v>0</v>
-      </c>
-      <c r="I15" s="78" t="str">
+      <c r="C15" s="77">
+        <v>0</v>
+      </c>
+      <c r="I15" s="75" t="str">
         <v>October</v>
       </c>
-      <c r="J15" s="80">
+      <c r="J15" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="78" t="str">
+      <c r="B16" s="75" t="str">
         <v>November</v>
       </c>
-      <c r="C16" s="80">
-        <v>0</v>
-      </c>
-      <c r="I16" s="78" t="str">
+      <c r="C16" s="77">
+        <v>0</v>
+      </c>
+      <c r="I16" s="75" t="str">
         <v>November</v>
       </c>
-      <c r="J16" s="80">
+      <c r="J16" s="77">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="78" t="str">
+      <c r="B17" s="75" t="str">
         <v>December</v>
       </c>
-      <c r="C17" s="80">
-        <v>0</v>
-      </c>
-      <c r="I17" s="78" t="str">
+      <c r="C17" s="77">
+        <v>0</v>
+      </c>
+      <c r="I17" s="75" t="str">
         <v>December</v>
       </c>
-      <c r="J17" s="80">
+      <c r="J17" s="77">
         <v>0</v>
       </c>
     </row>
@@ -14992,47 +15096,47 @@
       <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="83" t="s">
+      <c r="K2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="84"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="83" t="s">
+      <c r="N2" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="84"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="48">
+      <c r="C3" s="45">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="49">
+      <c r="D3" s="46">
         <f>SUM('Net Salary'!B$13:B$14)</f>
         <v>0</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="54">
+      <c r="F3" s="51">
         <f>SUM(Expenses!B20:B20)</f>
         <v>0</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="48">
+      <c r="H3" s="45">
         <f>I3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="48">
         <f>Expenses!B4</f>
         <v>0</v>
       </c>
       <c r="K3" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="49">
+      <c r="L3" s="46">
         <f>SUM('Net Salary'!B3:M7)</f>
         <v>0</v>
       </c>
@@ -15041,7 +15145,7 @@
         <f t="array" ref="N3:N14">Categories</f>
         <v>Bills</v>
       </c>
-      <c r="O3" s="58">
+      <c r="O3" s="55">
         <f>SUM(Expenses!B7:M7)</f>
         <v>0</v>
       </c>
@@ -15051,32 +15155,32 @@
         <v>8</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="48">
+      <c r="C4" s="45">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D4" s="49">
+      <c r="D4" s="46">
         <f>SUM('Net Salary'!C$13:C$14)</f>
         <v>0</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="54">
+      <c r="F4" s="51">
         <f>SUM(Expenses!C20:C20)</f>
         <v>0</v>
       </c>
       <c r="G4" s="7"/>
-      <c r="H4" s="48">
+      <c r="H4" s="45">
         <f t="shared" ref="H4:H14" si="0">I4-I3</f>
         <v>0</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="48">
         <f>Expenses!C4</f>
         <v>0</v>
       </c>
       <c r="K4" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="46">
         <f>SUM('Net Salary'!B8:M12)</f>
         <v>0</v>
       </c>
@@ -15084,7 +15188,7 @@
       <c r="N4" s="28" t="str">
         <v>Car maintenance</v>
       </c>
-      <c r="O4" s="58">
+      <c r="O4" s="55">
         <f>SUM(Expenses!B8:M8)</f>
         <v>0</v>
       </c>
@@ -15094,32 +15198,32 @@
         <v>9</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="48">
+      <c r="C5" s="45">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="46">
         <f>SUM('Net Salary'!D$13:D$14)</f>
         <v>0</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="54">
+      <c r="F5" s="51">
         <f>SUM(Expenses!D20:D20)</f>
         <v>0</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="48">
+      <c r="H5" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="48">
         <f>Expenses!D4</f>
         <v>0</v>
       </c>
       <c r="K5" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="46">
         <f>SUM('Net Salary'!B16:M16)</f>
         <v>0</v>
       </c>
@@ -15127,7 +15231,7 @@
       <c r="N5" s="28" t="str">
         <v>Clothing</v>
       </c>
-      <c r="O5" s="58">
+      <c r="O5" s="55">
         <f>SUM(Expenses!B9:M9)</f>
         <v>0</v>
       </c>
@@ -15137,32 +15241,32 @@
         <v>10</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="48">
+      <c r="C6" s="45">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="46">
         <f>SUM('Net Salary'!E$13:E$14)</f>
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="54">
+      <c r="F6" s="51">
         <f>SUM(Expenses!E20:E20)</f>
         <v>0</v>
       </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="48">
+      <c r="H6" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="48">
         <f>Expenses!E4</f>
         <v>0</v>
       </c>
       <c r="K6" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="46">
         <f>SUM(Expenses!B7:B17,Expenses!C7:C17,Expenses!D7:D17,Expenses!E7:E17,Expenses!F7:F17,Expenses!G7:G17,Expenses!H7:H17,Expenses!I7:I17,Expenses!J7:J17,Expenses!K7:K17,Expenses!L7:L17,Expenses!M7:M17)</f>
         <v>0</v>
       </c>
@@ -15170,7 +15274,7 @@
       <c r="N6" s="28" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="55">
         <f>SUM(Expenses!B10:M10)</f>
         <v>0</v>
       </c>
@@ -15180,32 +15284,32 @@
         <v>11</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="48">
+      <c r="C7" s="45">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="D7" s="49">
+      <c r="D7" s="46">
         <f>SUM('Net Salary'!F$13:F$14)</f>
         <v>0</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="54">
+      <c r="F7" s="51">
         <f>SUM(Expenses!F20:F20)</f>
         <v>0</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="48">
+      <c r="H7" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="48">
         <f>Expenses!F4</f>
         <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="46">
         <f>SUM(Expenses!B18:B18,Expenses!C18:C18,Expenses!D18:D18,Expenses!E18:E18,Expenses!F18:F18,Expenses!G18:G18,Expenses!H18:H18,Expenses!I18:I18,Expenses!J18:J18,Expenses!K18:K18,Expenses!L18:L18,Expenses!M18:M18)</f>
         <v>0</v>
       </c>
@@ -15213,7 +15317,7 @@
       <c r="N7" s="28" t="str">
         <v>Food</v>
       </c>
-      <c r="O7" s="58">
+      <c r="O7" s="55">
         <f>SUM(Expenses!B11:M11)</f>
         <v>0</v>
       </c>
@@ -15223,32 +15327,32 @@
         <v>12</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="48">
+      <c r="C8" s="45">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="D8" s="49">
+      <c r="D8" s="46">
         <f>SUM('Net Salary'!G$13:G$14)</f>
         <v>0</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="54">
+      <c r="F8" s="51">
         <f>SUM(Expenses!G20:G20)</f>
         <v>0</v>
       </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="48">
+      <c r="H8" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="48">
         <f>Expenses!G4</f>
         <v>0</v>
       </c>
       <c r="K8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="49">
+      <c r="L8" s="46">
         <f>SUM(L6:L7)</f>
         <v>0</v>
       </c>
@@ -15256,7 +15360,7 @@
       <c r="N8" s="28" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="O8" s="58">
+      <c r="O8" s="55">
         <f>SUM(Expenses!B12:M12)</f>
         <v>0</v>
       </c>
@@ -15266,32 +15370,32 @@
         <v>13</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="48">
+      <c r="C9" s="45">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="46">
         <f>SUM('Net Salary'!H$13:H$14)</f>
         <v>0</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="54">
+      <c r="F9" s="51">
         <f>SUM(Expenses!H20:H20)</f>
         <v>0</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="48">
+      <c r="H9" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="51">
+      <c r="I9" s="48">
         <f>Expenses!H4</f>
         <v>0</v>
       </c>
       <c r="K9" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="51">
+      <c r="L9" s="48">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
@@ -15299,7 +15403,7 @@
       <c r="N9" s="28" t="str">
         <v>Hang out</v>
       </c>
-      <c r="O9" s="58">
+      <c r="O9" s="55">
         <f>SUM(Expenses!B13:M13)</f>
         <v>0</v>
       </c>
@@ -15309,32 +15413,32 @@
         <v>14</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="48">
+      <c r="C10" s="45">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="46">
         <f>SUM('Net Salary'!I$13:I$14)</f>
         <v>0</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="54">
+      <c r="F10" s="51">
         <f>SUM(Expenses!I20:I20)</f>
         <v>0</v>
       </c>
       <c r="G10" s="7"/>
-      <c r="H10" s="48">
+      <c r="H10" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="48">
         <f>Expenses!I4</f>
         <v>0</v>
       </c>
       <c r="K10" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="53">
+      <c r="L10" s="50">
         <f>'Graphic - Annual'!D15</f>
         <v>0</v>
       </c>
@@ -15342,7 +15446,7 @@
       <c r="N10" s="28" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="O10" s="58">
+      <c r="O10" s="55">
         <f>SUM(Expenses!B14:M14)</f>
         <v>0</v>
       </c>
@@ -15352,25 +15456,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="48">
+      <c r="C11" s="45">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="46">
         <f>SUM('Net Salary'!J$13:J$14)</f>
         <v>0</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="54">
+      <c r="F11" s="51">
         <f>SUM(Expenses!J20:J20)</f>
         <v>0</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="48">
+      <c r="H11" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="48">
         <f>Expenses!J4</f>
         <v>0</v>
       </c>
@@ -15379,7 +15483,7 @@
       <c r="N11" s="26" t="str">
         <v>Insurance</v>
       </c>
-      <c r="O11" s="58">
+      <c r="O11" s="55">
         <f>SUM(Expenses!B15:M15)</f>
         <v>0</v>
       </c>
@@ -15389,25 +15493,25 @@
         <v>16</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="48">
+      <c r="C12" s="45">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="46">
         <f>SUM('Net Salary'!K$13:K$14)</f>
         <v>0</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="54">
+      <c r="F12" s="51">
         <f>SUM(Expenses!K20:K20)</f>
         <v>0</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="48">
+      <c r="H12" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="48">
         <f>Expenses!K4</f>
         <v>0</v>
       </c>
@@ -15416,7 +15520,7 @@
       <c r="N12" s="26" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="O12" s="58">
+      <c r="O12" s="55">
         <f>SUM(Expenses!B16:M16)</f>
         <v>0</v>
       </c>
@@ -15427,25 +15531,25 @@
         <v>17</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="48">
+      <c r="C13" s="45">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="46">
         <f>SUM('Net Salary'!L$13:L$14)</f>
         <v>0</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="54">
+      <c r="F13" s="51">
         <f>SUM(Expenses!L20:L20)</f>
         <v>0</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="48">
+      <c r="H13" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="48">
         <f>Expenses!L4</f>
         <v>0</v>
       </c>
@@ -15454,7 +15558,7 @@
       <c r="N13" s="26" t="str">
         <v>Travel</v>
       </c>
-      <c r="O13" s="58">
+      <c r="O13" s="55">
         <f>SUM(Expenses!B17:M17)</f>
         <v>0</v>
       </c>
@@ -15465,32 +15569,32 @@
         <v>18</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="48">
+      <c r="C14" s="45">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="46">
         <f>SUM('Net Salary'!M$13:M$14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="54">
+      <c r="F14" s="51">
         <f>SUM(Expenses!M20:N20)</f>
         <v>0</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="48">
+      <c r="H14" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="48">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
       <c r="N14" s="27" t="str">
         <v>General expen.</v>
       </c>
-      <c r="O14" s="59">
+      <c r="O14" s="56">
         <f>SUM(Expenses!B18:M18)</f>
         <v>0</v>
       </c>
@@ -15500,16 +15604,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="50">
+      <c r="C15" s="47">
         <f>SUM(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="46">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="54">
+      <c r="F15" s="51">
         <f>SUM(F3:F14)</f>
         <v>0</v>
       </c>
@@ -15517,7 +15621,7 @@
       <c r="H15" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="53">
+      <c r="I15" s="50">
         <f>'Graphic - Annual'!L9</f>
         <v>0</v>
       </c>
@@ -15527,16 +15631,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="50">
+      <c r="C16" s="47">
         <f>AVERAGE(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="46">
         <f>AVERAGE(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="55">
+      <c r="F16" s="52">
         <f>AVERAGE(F3:F14)</f>
         <v>0</v>
       </c>
@@ -15549,16 +15653,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="48">
+      <c r="C17" s="45">
         <f>SUM(C3:C8)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="48">
         <f>SUM(D3:D8)</f>
         <v>0</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="56">
+      <c r="F17" s="53">
         <f>SUM(F3:F8)</f>
         <v>0</v>
       </c>
@@ -15570,16 +15674,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="52">
+      <c r="C18" s="49">
         <f>SUM($C$9:$C$14)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="50">
         <f>SUM($D$9:$D$14)</f>
         <v>0</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="57">
+      <c r="F18" s="54">
         <f>SUM($F$9:$F$14)</f>
         <v>0</v>
       </c>

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE05060-9B67-491E-9CF2-60561E1B1743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A13132F-B618-47D6-80E1-C7DEB0EDA386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="15" r:id="rId1"/>
     <sheet name="Balance &amp; Tracking" sheetId="12" r:id="rId2"/>
-    <sheet name="Net Salary" sheetId="8" state="hidden" r:id="rId3"/>
-    <sheet name="Expenses" sheetId="1" state="hidden" r:id="rId4"/>
-    <sheet name="Graphic - Categories" sheetId="14" r:id="rId5"/>
-    <sheet name="Graphic - Annual" sheetId="13" r:id="rId6"/>
+    <sheet name="Net Salary" sheetId="8" r:id="rId3"/>
+    <sheet name="Expenses" sheetId="1" r:id="rId4"/>
+    <sheet name="Graphic Categories" sheetId="14" r:id="rId5"/>
+    <sheet name="Graphic Annual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Assets">'Data Validation'!$B$5:$B$7</definedName>
-    <definedName name="Dash">'Graphic - Annual'!$A$1:$P$26</definedName>
+    <definedName name="Dash">'Graphic Annual'!$A$1:$P$26</definedName>
     <definedName name="Discount">'Data Validation'!$H$5:$H$9</definedName>
     <definedName name="Expenses">'Data Validation'!$D$5:$D$16</definedName>
     <definedName name="Income">'Data Validation'!$J$5:$J$9</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -783,15 +783,15 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -2919,7 +2919,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graphic - Categories'!$C$5</c:f>
+              <c:f>'Graphic Categories'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3020,7 +3020,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Categories'!$B$6:$B$17</c:f>
+              <c:f>'Graphic Categories'!$B$6:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3064,7 +3064,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Categories'!$C$6:$C$17</c:f>
+              <c:f>'Graphic Categories'!$C$6:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -3309,7 +3309,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graphic - Categories'!$J$5</c:f>
+              <c:f>'Graphic Categories'!$J$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3410,7 +3410,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Categories'!$I$6:$I$17</c:f>
+              <c:f>'Graphic Categories'!$I$6:$I$17</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3454,7 +3454,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Categories'!$J$6:$J$17</c:f>
+              <c:f>'Graphic Categories'!$J$6:$J$17</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -3699,7 +3699,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$C$2</c:f>
+              <c:f>'Graphic Annual'!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3757,7 +3757,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$A$3:$A$14</c:f>
+              <c:f>'Graphic Annual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -3801,7 +3801,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Annual'!$C$3:$C$14</c:f>
+              <c:f>'Graphic Annual'!$C$3:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -3855,7 +3855,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$F$2</c:f>
+              <c:f>'Graphic Annual'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3968,7 +3968,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$A$3:$A$14</c:f>
+              <c:f>'Graphic Annual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -4012,7 +4012,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Annual'!$F$3:$F$14</c:f>
+              <c:f>'Graphic Annual'!$F$3:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -4081,7 +4081,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$D$2</c:f>
+              <c:f>'Graphic Annual'!$D$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4112,7 +4112,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$A$3:$A$14</c:f>
+              <c:f>'Graphic Annual'!$A$3:$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -4156,7 +4156,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Annual'!$D$3:$D$14</c:f>
+              <c:f>'Graphic Annual'!$D$3:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -4281,7 +4281,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>'Graphic - Annual'!$I$3:$I$14</c:f>
+              <c:f>'Graphic Annual'!$I$3:$I$14</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="12"/>
@@ -4658,11 +4658,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Graphic - Annual'!$K$2:$K$10</c15:sqref>
+                    <c15:sqref>'Graphic Annual'!$K$2:$K$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Graphic - Annual'!$K$3:$K$7,'Graphic - Annual'!$K$10)</c:f>
+              <c:f>('Graphic Annual'!$K$3:$K$7,'Graphic Annual'!$K$10)</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -4691,11 +4691,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>'Graphic - Annual'!$L$2:$L$10</c15:sqref>
+                    <c15:sqref>'Graphic Annual'!$L$2:$L$10</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>('Graphic - Annual'!$L$3:$L$7,'Graphic - Annual'!$L$10)</c:f>
+              <c:f>('Graphic Annual'!$L$3:$L$7,'Graphic Annual'!$L$10)</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="6"/>
@@ -4972,7 +4972,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Graphic - Annual'!$N$3:$N$13</c:f>
+              <c:f>'Graphic Annual'!$N$3:$N$13</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
@@ -5013,7 +5013,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graphic - Annual'!$O$3:$O$13</c:f>
+              <c:f>'Graphic Annual'!$O$3:$O$13</c:f>
               <c:numCache>
                 <c:formatCode>_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* "-"??_ ;_-@_ </c:formatCode>
                 <c:ptCount val="11"/>
@@ -9477,27 +9477,27 @@
   <dimension ref="B2:P16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="82" customWidth="1"/>
-    <col min="3" max="3" width="3.5703125" style="82" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="82" customWidth="1"/>
-    <col min="5" max="5" width="3.5703125" style="82" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="82" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" style="82" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="82" customWidth="1"/>
-    <col min="9" max="9" width="3.5703125" style="82" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="82" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" style="82" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="82" customWidth="1"/>
-    <col min="13" max="13" width="3.5703125" style="82" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="82" customWidth="1"/>
-    <col min="15" max="15" width="3.5703125" style="82" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="82" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="82"/>
+    <col min="1" max="1" width="3.5703125" style="80" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="80" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="80" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="80" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="80" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="80" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="80" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="80" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="80" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="80" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="80" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="80" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="80" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="80" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="80" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="80" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="80"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>77</v>
       </c>
     </row>
@@ -9528,192 +9528,192 @@
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="83" t="s">
+      <c r="D5" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="83" t="s">
+      <c r="F5" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="83" t="s">
+      <c r="H5" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="83" t="s">
+      <c r="J5" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="84" t="str" cm="1">
+      <c r="L5" s="82" t="str" cm="1">
         <f t="array" ref="L5:L7">Assets</f>
         <v>Bank 1</v>
       </c>
-      <c r="N5" s="84" t="str" cm="1">
+      <c r="N5" s="82" t="str" cm="1">
         <f t="array" ref="N5:N9">Income</f>
         <v>Salary</v>
       </c>
-      <c r="P5" s="84" t="s">
+      <c r="P5" s="82" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="83" t="s">
+      <c r="J6" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="84" t="str">
+      <c r="L6" s="82" t="str">
         <v>Bank 2</v>
       </c>
-      <c r="N6" s="84" t="str">
+      <c r="N6" s="82" t="str">
         <v>Seals</v>
       </c>
-      <c r="P6" s="84" t="s">
+      <c r="P6" s="82" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="83" t="s">
+      <c r="H7" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="83" t="s">
+      <c r="J7" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="84" t="str">
+      <c r="L7" s="82" t="str">
         <v>Wallet</v>
       </c>
-      <c r="N7" s="84" t="str">
+      <c r="N7" s="82" t="str">
         <v>Rent</v>
       </c>
-      <c r="P7" s="84" t="s">
+      <c r="P7" s="82" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D8" s="83" t="s">
+      <c r="D8" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="83" t="s">
+      <c r="H8" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="83" t="s">
+      <c r="J8" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="84" t="str">
+      <c r="N8" s="82" t="str">
         <v>Seals II</v>
       </c>
-      <c r="P8" s="84" t="s">
+      <c r="P8" s="82" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="83" t="s">
+      <c r="H9" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="83" t="s">
+      <c r="J9" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="84" t="str">
+      <c r="N9" s="82" t="str">
         <v>Other - Income</v>
       </c>
-      <c r="P9" s="84" t="s">
+      <c r="P9" s="82" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D10" s="83" t="s">
+      <c r="D10" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="84" t="str" cm="1">
+      <c r="N10" s="82" t="str" cm="1">
         <f t="array" ref="N10:N14">Discount</f>
         <v>Tax I</v>
       </c>
-      <c r="P10" s="84" t="s">
+      <c r="P10" s="82" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="84" t="str">
+      <c r="N11" s="82" t="str">
         <v>Tax II</v>
       </c>
-      <c r="P11" s="84" t="s">
+      <c r="P11" s="82" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="84" t="str">
+      <c r="N12" s="82" t="str">
         <v>Bank Fee I</v>
       </c>
-      <c r="P12" s="84" t="s">
+      <c r="P12" s="82" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D13" s="83" t="s">
+      <c r="D13" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="84" t="str">
+      <c r="N13" s="82" t="str">
         <v>Bank Fee II</v>
       </c>
-      <c r="P13" s="84" t="s">
+      <c r="P13" s="82" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="N14" s="84" t="str">
+      <c r="N14" s="82" t="str">
         <v>Other - Discount</v>
       </c>
-      <c r="P14" s="84" t="s">
+      <c r="P14" s="82" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="N15" s="84" t="str" cm="1">
+      <c r="N15" s="82" t="str" cm="1">
         <f t="array" ref="N15:N16">Investments</f>
         <v>Stock Market</v>
       </c>
-      <c r="P15" s="84" t="s">
+      <c r="P15" s="82" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D16" s="83" t="s">
+      <c r="D16" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="84" t="str">
+      <c r="N16" s="82" t="str">
         <v>Real Estate</v>
       </c>
-      <c r="P16" s="84" t="s">
+      <c r="P16" s="82" t="s">
         <v>18</v>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="42">
-        <f>VLOOKUP(B2,'Graphic - Annual'!A3:I14,9,FALSE)</f>
+        <f>VLOOKUP(B2,'Graphic Annual'!A3:I14,9,FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="64" t="str">
@@ -9812,7 +9812,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="42">
-        <f>'Graphic - Annual'!I15</f>
+        <f>'Graphic Annual'!I15</f>
         <v>0</v>
       </c>
       <c r="E6" s="64" t="str">
@@ -15139,7 +15139,7 @@
         <v>January</v>
       </c>
       <c r="C6" s="77" cm="1">
-        <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic - Categories'!C2))</f>
+        <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic Categories'!C2))</f>
         <v>0</v>
       </c>
       <c r="I6" s="75" t="str" cm="1">
@@ -15147,7 +15147,7 @@
         <v>January</v>
       </c>
       <c r="J6" s="77" cm="1">
-        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses='Graphic - Categories'!J2))</f>
+        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses='Graphic Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
@@ -15371,15 +15371,15 @@
       <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="80" t="s">
+      <c r="K2" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="81"/>
+      <c r="L2" s="84"/>
       <c r="M2" s="25"/>
-      <c r="N2" s="80" t="s">
+      <c r="N2" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="81"/>
+      <c r="O2" s="84"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str" cm="1">
@@ -15715,7 +15715,7 @@
         <v>37</v>
       </c>
       <c r="L10" s="50">
-        <f>'Graphic - Annual'!D15</f>
+        <f>'Graphic Annual'!D15</f>
         <v>0</v>
       </c>
       <c r="M10" s="7"/>
@@ -15898,7 +15898,7 @@
         <v>40</v>
       </c>
       <c r="I15" s="50">
-        <f>'Graphic - Annual'!L9</f>
+        <f>'Graphic Annual'!L9</f>
         <v>0</v>
       </c>
     </row>

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E718BE-20FB-4337-A5EE-979BD24B9C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE05060-9B67-491E-9CF2-60561E1B1743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Balance &amp; Tracking" sheetId="12" r:id="rId1"/>
-    <sheet name="Net Salary" sheetId="8" r:id="rId2"/>
-    <sheet name="Expenses" sheetId="1" r:id="rId3"/>
-    <sheet name="Graphic - Categories" sheetId="14" r:id="rId4"/>
-    <sheet name="Graphic - Annual" sheetId="13" r:id="rId5"/>
+    <sheet name="Data Validation" sheetId="15" r:id="rId1"/>
+    <sheet name="Balance &amp; Tracking" sheetId="12" r:id="rId2"/>
+    <sheet name="Net Salary" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="Expenses" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Graphic - Categories" sheetId="14" r:id="rId5"/>
+    <sheet name="Graphic - Annual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Assets">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
-    <definedName name="Categories">Expenses!$A$7:$A$18</definedName>
+    <definedName name="Assets">'Data Validation'!$B$5:$B$7</definedName>
     <definedName name="Dash">'Graphic - Annual'!$A$1:$P$26</definedName>
-    <definedName name="Discount">'Net Salary'!$A$8:$A$12</definedName>
-    <definedName name="Expenses">Expenses!$A$7:$A$18</definedName>
-    <definedName name="Income">'Net Salary'!$A$3:$A$7</definedName>
-    <definedName name="Investments">'Net Salary'!$A$13:$A$14</definedName>
-    <definedName name="Months">'Net Salary'!$B$2:$M$2</definedName>
-    <definedName name="Net_Salary">'Net Salary'!$A$3:$A$14</definedName>
-    <definedName name="Transfer">'Balance &amp; Tracking'!$B$9:$B$11</definedName>
-    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="2" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
+    <definedName name="Discount">'Data Validation'!$H$5:$H$9</definedName>
+    <definedName name="Expenses">'Data Validation'!$D$5:$D$16</definedName>
+    <definedName name="Income">'Data Validation'!$J$5:$J$9</definedName>
+    <definedName name="Investments">'Data Validation'!$F$5:$F$6</definedName>
+    <definedName name="Months">'Data Validation'!$P$5:$P$16</definedName>
+    <definedName name="Net_Salary">'Data Validation'!$N$5:$N$16</definedName>
+    <definedName name="Transfer">'Data Validation'!$L$5:$L$7</definedName>
+    <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="3" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
   <si>
     <t>Total</t>
   </si>
@@ -236,9 +236,6 @@
     <t>Tax II</t>
   </si>
   <si>
-    <t>Stock M. I</t>
-  </si>
-  <si>
     <t>Tax I</t>
   </si>
   <si>
@@ -249,9 +246,6 @@
   </si>
   <si>
     <t>Bills</t>
-  </si>
-  <si>
-    <t>Car maintenance</t>
   </si>
   <si>
     <t>Clothing</t>
@@ -272,16 +266,10 @@
     <t>Net_Salary</t>
   </si>
   <si>
-    <t>Salary II</t>
-  </si>
-  <si>
     <t>Seals II</t>
   </si>
   <si>
     <t>Bank Fee II</t>
-  </si>
-  <si>
-    <t>Stock M. II</t>
   </si>
   <si>
     <t>Personal Care</t>
@@ -300,6 +288,27 @@
   </si>
   <si>
     <t>Debt/ Income</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Stock Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car </t>
+  </si>
+  <si>
+    <t>*Feel free to change the blue values as you wish. However, if you need to remove or add new values, you may need to adjust the spreadsheet accordingly.</t>
   </si>
 </sst>
 </file>
@@ -351,7 +360,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,6 +388,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,7 +592,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -768,6 +789,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1214,7 +1238,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Car maintenance</c:v>
+                  <c:v>Car </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4955,7 +4979,7 @@
                   <c:v>Bills</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Car maintenance</c:v>
+                  <c:v>Car </c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Clothing</c:v>
@@ -9025,15 +9049,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>6336</xdr:colOff>
+      <xdr:colOff>6328</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>11315</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>27158</xdr:colOff>
+      <xdr:colOff>27150</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>101850</xdr:rowOff>
+      <xdr:rowOff>90535</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9446,6 +9470,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37BC3379-970E-4EAE-8D75-6CE2D033D7D2}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="B2:P16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" style="82" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="82" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="82" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="82" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="82" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="82" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="82" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="82" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="82" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="82" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="82" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="82" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="82" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="82" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="82" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="82" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="82"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="84" t="str" cm="1">
+        <f t="array" ref="L5:L7">Assets</f>
+        <v>Bank 1</v>
+      </c>
+      <c r="N5" s="84" t="str" cm="1">
+        <f t="array" ref="N5:N9">Income</f>
+        <v>Salary</v>
+      </c>
+      <c r="P5" s="84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="83" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="83" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="84" t="str">
+        <v>Bank 2</v>
+      </c>
+      <c r="N6" s="84" t="str">
+        <v>Seals</v>
+      </c>
+      <c r="P6" s="84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="83" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="84" t="str">
+        <v>Wallet</v>
+      </c>
+      <c r="N7" s="84" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="P7" s="84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D8" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="84" t="str">
+        <v>Seals II</v>
+      </c>
+      <c r="P8" s="84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D9" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="83" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="84" t="str">
+        <v>Other - Income</v>
+      </c>
+      <c r="P9" s="84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D10" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="84" t="str" cm="1">
+        <f t="array" ref="N10:N14">Discount</f>
+        <v>Tax I</v>
+      </c>
+      <c r="P10" s="84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D11" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="84" t="str">
+        <v>Tax II</v>
+      </c>
+      <c r="P11" s="84" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D12" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="84" t="str">
+        <v>Bank Fee I</v>
+      </c>
+      <c r="P12" s="84" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D13" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="84" t="str">
+        <v>Bank Fee II</v>
+      </c>
+      <c r="P13" s="84" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D14" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="84" t="str">
+        <v>Other - Discount</v>
+      </c>
+      <c r="P14" s="84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D15" s="83" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="84" t="str" cm="1">
+        <f t="array" ref="N15:N16">Investments</f>
+        <v>Stock Market</v>
+      </c>
+      <c r="P15" s="84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D16" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="84" t="str">
+        <v>Real Estate</v>
+      </c>
+      <c r="P16" s="84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0180935C-8656-4D81-89AE-9797F0D184CE}">
   <sheetPr codeName="Planilha1">
     <tabColor theme="0"/>
@@ -9489,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="64" t="str" cm="1">
-        <f t="array" ref="E3:E14">IF(B3="Expenses",Categories,IF(B3="Net Salary",Net_Salary,""))</f>
+        <f t="array" ref="E3:E14">IF(B3="Expenses",Expenses,IF(B3="Net Salary",Net_Salary,""))</f>
         <v>Bills</v>
       </c>
       <c r="F3" s="72" cm="1">
@@ -9500,14 +9777,14 @@
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" s="79" t="e">
         <f>HLOOKUP(B2,Expenses!B2:M20,19,FALSE)/HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E4" s="64" t="str">
-        <v>Car maintenance</v>
+        <v xml:space="preserve">Car </v>
       </c>
       <c r="F4" s="72">
         <v>0</v>
@@ -9557,7 +9834,7 @@
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>0</v>
@@ -9571,8 +9848,9 @@
       <c r="H8" s="62"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="15" t="s">
-        <v>24</v>
+      <c r="B9" s="15" t="str" cm="1">
+        <f t="array" ref="B9:B11">Assets</f>
+        <v>Bank 1</v>
       </c>
       <c r="C9" s="43" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
@@ -9588,8 +9866,8 @@
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
-      <c r="B10" s="15" t="s">
-        <v>25</v>
+      <c r="B10" s="15" t="str">
+        <v>Bank 2</v>
       </c>
       <c r="C10" s="43" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
@@ -9605,8 +9883,8 @@
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61"/>
-      <c r="B11" s="15" t="s">
-        <v>26</v>
+      <c r="B11" s="15" t="str">
+        <v>Wallet</v>
       </c>
       <c r="C11" s="43" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
@@ -9700,7 +9978,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="21">
-        <v>44927</v>
+        <v>45292</v>
       </c>
       <c r="C17" s="22" t="str">
         <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
@@ -12978,7 +13256,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Expenses, Net Salary"</formula1>
     </dataValidation>
@@ -12993,6 +13271,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D20" xr:uid="{0261ACD4-BAB2-4EA0-87AC-74F751F397E2}">
       <formula1>"Income, Discount, Investments, Expenses, Transfer"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
+      <formula1>Months</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -13022,21 +13303,11 @@
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9270E47-B020-4CBF-A3A9-E523B28C14E7}">
-          <x14:formula1>
-            <xm:f>'Net Salary'!$B$2:$M$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
   </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2">
     <tabColor theme="0"/>
@@ -13052,46 +13323,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>18</v>
+      <c r="B2" s="32" t="str" cm="1">
+        <f t="array" ref="B2:M2">TRANSPOSE(Months)</f>
+        <v>January</v>
+      </c>
+      <c r="C2" s="32" t="str">
+        <v>February</v>
+      </c>
+      <c r="D2" s="32" t="str">
+        <v>March</v>
+      </c>
+      <c r="E2" s="32" t="str">
+        <v>April</v>
+      </c>
+      <c r="F2" s="32" t="str">
+        <v>May</v>
+      </c>
+      <c r="G2" s="32" t="str">
+        <v>June</v>
+      </c>
+      <c r="H2" s="32" t="str">
+        <v>July</v>
+      </c>
+      <c r="I2" s="32" t="str">
+        <v>August</v>
+      </c>
+      <c r="J2" s="32" t="str">
+        <v>September</v>
+      </c>
+      <c r="K2" s="32" t="str">
+        <v>October</v>
+      </c>
+      <c r="L2" s="32" t="str">
+        <v>November</v>
+      </c>
+      <c r="M2" s="32" t="str">
+        <v>December</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
-        <v>49</v>
+      <c r="A3" s="31" t="str" cm="1">
+        <f t="array" ref="A3:A14">Net_Salary</f>
+        <v>Salary</v>
       </c>
       <c r="B3" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
@@ -13143,8 +13416,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>50</v>
+      <c r="A4" s="31" t="str">
+        <v>Seals</v>
       </c>
       <c r="B4" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
@@ -13196,8 +13469,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
-        <v>65</v>
+      <c r="A5" s="31" t="str">
+        <v>Rent</v>
       </c>
       <c r="B5" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
@@ -13249,8 +13522,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>66</v>
+      <c r="A6" s="31" t="str">
+        <v>Seals II</v>
       </c>
       <c r="B6" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
@@ -13302,8 +13575,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
-        <v>51</v>
+      <c r="A7" s="31" t="str">
+        <v>Other - Income</v>
       </c>
       <c r="B7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
@@ -13355,8 +13628,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>54</v>
+      <c r="A8" s="31" t="str">
+        <v>Tax I</v>
       </c>
       <c r="B8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
@@ -13408,8 +13681,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
-        <v>52</v>
+      <c r="A9" s="31" t="str">
+        <v>Tax II</v>
       </c>
       <c r="B9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
@@ -13461,8 +13734,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>72</v>
+      <c r="A10" s="31" t="str">
+        <v>Bank Fee I</v>
       </c>
       <c r="B10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
@@ -13514,8 +13787,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>67</v>
+      <c r="A11" s="31" t="str">
+        <v>Bank Fee II</v>
       </c>
       <c r="B11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
@@ -13567,8 +13840,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>55</v>
+      <c r="A12" s="31" t="str">
+        <v>Other - Discount</v>
       </c>
       <c r="B12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
@@ -13620,8 +13893,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>53</v>
+      <c r="A13" s="31" t="str">
+        <v>Stock Market</v>
       </c>
       <c r="B13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
@@ -13673,8 +13946,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
-        <v>68</v>
+      <c r="A14" s="31" t="str">
+        <v>Real Estate</v>
       </c>
       <c r="B14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A14)</f>
@@ -13839,7 +14112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha3">
     <tabColor theme="0"/>
@@ -13859,41 +14132,42 @@
   <sheetData>
     <row r="2" spans="1:13" s="33" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35"/>
-      <c r="B2" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>18</v>
+      <c r="B2" s="32" t="str" cm="1">
+        <f t="array" ref="B2:M2">TRANSPOSE(Months)</f>
+        <v>January</v>
+      </c>
+      <c r="C2" s="32" t="str">
+        <v>February</v>
+      </c>
+      <c r="D2" s="32" t="str">
+        <v>March</v>
+      </c>
+      <c r="E2" s="32" t="str">
+        <v>April</v>
+      </c>
+      <c r="F2" s="32" t="str">
+        <v>May</v>
+      </c>
+      <c r="G2" s="32" t="str">
+        <v>June</v>
+      </c>
+      <c r="H2" s="32" t="str">
+        <v>July</v>
+      </c>
+      <c r="I2" s="32" t="str">
+        <v>August</v>
+      </c>
+      <c r="J2" s="32" t="str">
+        <v>September</v>
+      </c>
+      <c r="K2" s="32" t="str">
+        <v>October</v>
+      </c>
+      <c r="L2" s="32" t="str">
+        <v>November</v>
+      </c>
+      <c r="M2" s="32" t="str">
+        <v>December</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -14059,8 +14333,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>57</v>
+      <c r="A7" s="15" t="str" cm="1">
+        <f t="array" ref="A7:A18">Expenses</f>
+        <v>Bills</v>
       </c>
       <c r="B7" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A7)</f>
@@ -14112,8 +14387,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>58</v>
+      <c r="A8" s="15" t="str">
+        <v xml:space="preserve">Car </v>
       </c>
       <c r="B8" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A8)</f>
@@ -14165,8 +14440,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>59</v>
+      <c r="A9" s="15" t="str">
+        <v>Clothing</v>
       </c>
       <c r="B9" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A9)</f>
@@ -14218,8 +14493,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>60</v>
+      <c r="A10" s="15" t="str">
+        <v>Eletron n' games</v>
       </c>
       <c r="B10" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A10)</f>
@@ -14271,8 +14546,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>56</v>
+      <c r="A11" s="15" t="str">
+        <v>Food</v>
       </c>
       <c r="B11" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A11)</f>
@@ -14324,8 +14599,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>5</v>
+      <c r="A12" s="15" t="str">
+        <v>Gasolina</v>
       </c>
       <c r="B12" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A12)</f>
@@ -14377,8 +14652,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
-        <v>61</v>
+      <c r="A13" s="15" t="str">
+        <v>Hang out</v>
       </c>
       <c r="B13" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
@@ -14430,8 +14705,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59" t="s">
-        <v>62</v>
+      <c r="A14" s="59" t="str">
+        <v>Healthcare</v>
       </c>
       <c r="B14" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A14)</f>
@@ -14483,8 +14758,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>71</v>
+      <c r="A15" s="15" t="str">
+        <v>Insurance</v>
       </c>
       <c r="B15" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A15)</f>
@@ -14536,8 +14811,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
-        <v>69</v>
+      <c r="A16" s="15" t="str">
+        <v>Personal Care</v>
       </c>
       <c r="B16" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A16)</f>
@@ -14589,8 +14864,8 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>70</v>
+      <c r="A17" s="15" t="str">
+        <v>Travel</v>
       </c>
       <c r="B17" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A17)</f>
@@ -14642,8 +14917,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
-        <v>63</v>
+      <c r="A18" s="15" t="str">
+        <v>General expen.</v>
       </c>
       <c r="B18" s="43">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A18)</f>
@@ -14797,7 +15072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BFD9AA-7466-45C1-AB6A-4AD451301F03}">
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
@@ -14816,7 +15091,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>49</v>
@@ -14825,7 +15100,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
@@ -14860,7 +15135,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="75" t="str" cm="1">
-        <f t="array" ref="B6:B17">TRANSPOSE(Months)</f>
+        <f t="array" ref="B6:B17">Months</f>
         <v>January</v>
       </c>
       <c r="C6" s="77" cm="1">
@@ -14868,11 +15143,11 @@
         <v>0</v>
       </c>
       <c r="I6" s="75" t="str" cm="1">
-        <f t="array" ref="I6:I17">TRANSPOSE(Months)</f>
+        <f t="array" ref="I6:I17">Months</f>
         <v>January</v>
       </c>
       <c r="J6" s="77" cm="1">
-        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Categories='Graphic - Categories'!J2))</f>
+        <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses='Graphic - Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
@@ -15044,7 +15319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD330F4-3FAE-447F-BF05-82EFBCBD7BD0}">
   <sheetPr codeName="Planilha6">
     <tabColor theme="1"/>
@@ -15107,8 +15382,9 @@
       <c r="O2" s="81"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>7</v>
+      <c r="A3" s="5" t="str" cm="1">
+        <f t="array" ref="A3:A14">Months</f>
+        <v>January</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="45">
@@ -15142,7 +15418,7 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="28" t="str" cm="1">
-        <f t="array" ref="N3:N14">Categories</f>
+        <f t="array" ref="N3:N14">Expenses</f>
         <v>Bills</v>
       </c>
       <c r="O3" s="55">
@@ -15151,8 +15427,8 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
+      <c r="A4" s="5" t="str">
+        <v>February</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="45">
@@ -15186,7 +15462,7 @@
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="28" t="str">
-        <v>Car maintenance</v>
+        <v xml:space="preserve">Car </v>
       </c>
       <c r="O4" s="55">
         <f>SUM(Expenses!B8:M8)</f>
@@ -15194,8 +15470,8 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>9</v>
+      <c r="A5" s="5" t="str">
+        <v>March</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="45">
@@ -15237,8 +15513,8 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
+      <c r="A6" s="5" t="str">
+        <v>April</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="45">
@@ -15280,8 +15556,8 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
+      <c r="A7" s="5" t="str">
+        <v>May</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="45">
@@ -15323,8 +15599,8 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
+      <c r="A8" s="5" t="str">
+        <v>June</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="45">
@@ -15366,8 +15642,8 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>13</v>
+      <c r="A9" s="5" t="str">
+        <v>July</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="45">
@@ -15409,8 +15685,8 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>14</v>
+      <c r="A10" s="5" t="str">
+        <v>August</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="45">
@@ -15452,8 +15728,8 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>15</v>
+      <c r="A11" s="5" t="str">
+        <v>September</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="45">
@@ -15489,8 +15765,8 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>16</v>
+      <c r="A12" s="5" t="str">
+        <v>October</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="45">
@@ -15527,8 +15803,8 @@
       <c r="P12" s="4"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>17</v>
+      <c r="A13" s="5" t="str">
+        <v>November</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="45">
@@ -15565,8 +15841,8 @@
       <c r="P13" s="4"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
+      <c r="A14" s="5" t="str">
+        <v>December</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="45">

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A13132F-B618-47D6-80E1-C7DEB0EDA386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4305E4-7384-4859-8511-AFC34D38E465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -592,7 +592,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -631,9 +631,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -673,30 +670,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -734,7 +713,6 @@
     <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -790,6 +768,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9477,243 +9466,243 @@
   <dimension ref="B2:P16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="80" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="80" customWidth="1"/>
-    <col min="3" max="3" width="3.5703125" style="80" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" style="80" customWidth="1"/>
-    <col min="5" max="5" width="3.5703125" style="80" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="80" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" style="80" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="80" customWidth="1"/>
-    <col min="9" max="9" width="3.5703125" style="80" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="80" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" style="80" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="80" customWidth="1"/>
-    <col min="13" max="13" width="3.5703125" style="80" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="80" customWidth="1"/>
-    <col min="15" max="15" width="3.5703125" style="80" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="80" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="80"/>
+    <col min="1" max="1" width="3.5703125" style="72" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="72" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="72" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="72" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="72" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="72" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="3.5703125" style="72" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="72" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="72" customWidth="1"/>
+    <col min="13" max="13" width="3.5703125" style="72" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="72" customWidth="1"/>
+    <col min="15" max="15" width="3.5703125" style="72" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="72" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="72"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="72" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="N4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="28" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="81" t="s">
+      <c r="J5" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="82" t="str" cm="1">
+      <c r="L5" s="74" t="str" cm="1">
         <f t="array" ref="L5:L7">Assets</f>
         <v>Bank 1</v>
       </c>
-      <c r="N5" s="82" t="str" cm="1">
+      <c r="N5" s="74" t="str" cm="1">
         <f t="array" ref="N5:N9">Income</f>
         <v>Salary</v>
       </c>
-      <c r="P5" s="82" t="s">
+      <c r="P5" s="74" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="81" t="s">
+      <c r="J6" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="82" t="str">
+      <c r="L6" s="74" t="str">
         <v>Bank 2</v>
       </c>
-      <c r="N6" s="82" t="str">
+      <c r="N6" s="74" t="str">
         <v>Seals</v>
       </c>
-      <c r="P6" s="82" t="s">
+      <c r="P6" s="74" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="81" t="s">
+      <c r="J7" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="82" t="str">
+      <c r="L7" s="74" t="str">
         <v>Wallet</v>
       </c>
-      <c r="N7" s="82" t="str">
+      <c r="N7" s="74" t="str">
         <v>Rent</v>
       </c>
-      <c r="P7" s="82" t="s">
+      <c r="P7" s="74" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="81" t="s">
+      <c r="J8" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="82" t="str">
+      <c r="N8" s="74" t="str">
         <v>Seals II</v>
       </c>
-      <c r="P8" s="82" t="s">
+      <c r="P8" s="74" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="H9" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="81" t="s">
+      <c r="J9" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="82" t="str">
+      <c r="N9" s="74" t="str">
         <v>Other - Income</v>
       </c>
-      <c r="P9" s="82" t="s">
+      <c r="P9" s="74" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D10" s="81" t="s">
+      <c r="D10" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="82" t="str" cm="1">
+      <c r="N10" s="74" t="str" cm="1">
         <f t="array" ref="N10:N14">Discount</f>
         <v>Tax I</v>
       </c>
-      <c r="P10" s="82" t="s">
+      <c r="P10" s="74" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="82" t="str">
+      <c r="N11" s="74" t="str">
         <v>Tax II</v>
       </c>
-      <c r="P11" s="82" t="s">
+      <c r="P11" s="74" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="82" t="str">
+      <c r="N12" s="74" t="str">
         <v>Bank Fee I</v>
       </c>
-      <c r="P12" s="82" t="s">
+      <c r="P12" s="74" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D13" s="81" t="s">
+      <c r="D13" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="82" t="str">
+      <c r="N13" s="74" t="str">
         <v>Bank Fee II</v>
       </c>
-      <c r="P13" s="82" t="s">
+      <c r="P13" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D14" s="81" t="s">
+      <c r="D14" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="N14" s="82" t="str">
+      <c r="N14" s="74" t="str">
         <v>Other - Discount</v>
       </c>
-      <c r="P14" s="82" t="s">
+      <c r="P14" s="74" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="N15" s="82" t="str" cm="1">
+      <c r="N15" s="74" t="str" cm="1">
         <f t="array" ref="N15:N16">Investments</f>
         <v>Stock Market</v>
       </c>
-      <c r="P15" s="82" t="s">
+      <c r="P15" s="74" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D16" s="81" t="s">
+      <c r="D16" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="82" t="str">
+      <c r="N16" s="74" t="str">
         <v>Real Estate</v>
       </c>
-      <c r="P16" s="82" t="s">
+      <c r="P16" s="74" t="s">
         <v>18</v>
       </c>
     </row>
@@ -9730,3504 +9719,3504 @@
   <dimension ref="A1:I785"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="60" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="61" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="61" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="62" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="65" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="64" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="62" customWidth="1"/>
-    <col min="10" max="10" width="10" style="62" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="62"/>
+    <col min="1" max="1" width="14.28515625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="52" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="53" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="53" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="54" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="57" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="56" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="54" customWidth="1"/>
+    <col min="10" max="10" width="10" style="54" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="73" t="s">
+      <c r="C2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="F2" s="66" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="35">
         <f>IF(B3="Expenses",HLOOKUP(B2,Expenses!B2:M20,19,FALSE),IF(B3="Net Salary",HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE),""))</f>
         <v>0</v>
       </c>
-      <c r="E3" s="64" t="str" cm="1">
+      <c r="E3" s="56" t="str" cm="1">
         <f t="array" ref="E3:E14">IF(B3="Expenses",Expenses,IF(B3="Net Salary",Net_Salary,""))</f>
         <v>Bills</v>
       </c>
-      <c r="F3" s="72" cm="1">
+      <c r="F3" s="64" cm="1">
         <f t="array" ref="F3:F14">IF(B3="Expenses",_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses!B2:M2=B2),IF(B3="Net Salary",_xlfn._xlws.FILTER('Net Salary'!B3:M14,'Net Salary'!B2:M2=B2),""))</f>
         <v>0</v>
       </c>
-      <c r="H3" s="62"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="79" t="e">
+      <c r="C4" s="71" t="e">
         <f>HLOOKUP(B2,Expenses!B2:M20,19,FALSE)/HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E4" s="64" t="str">
+      <c r="E4" s="56" t="str">
         <v xml:space="preserve">Car </v>
       </c>
-      <c r="F4" s="72">
-        <v>0</v>
-      </c>
-      <c r="H4" s="62"/>
+      <c r="F4" s="64">
+        <v>0</v>
+      </c>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="35">
         <f>VLOOKUP(B2,'Graphic Annual'!A3:I14,9,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="64" t="str">
+      <c r="E5" s="56" t="str">
         <v>Clothing</v>
       </c>
-      <c r="F5" s="72">
-        <v>0</v>
-      </c>
-      <c r="H5" s="62"/>
+      <c r="F5" s="64">
+        <v>0</v>
+      </c>
+      <c r="H5" s="54"/>
     </row>
     <row r="6" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="35">
         <f>'Graphic Annual'!I15</f>
         <v>0</v>
       </c>
-      <c r="E6" s="64" t="str">
+      <c r="E6" s="56" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="F6" s="72">
-        <v>0</v>
-      </c>
-      <c r="H6" s="62"/>
+      <c r="F6" s="64">
+        <v>0</v>
+      </c>
+      <c r="H6" s="54"/>
     </row>
     <row r="7" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="64" t="str">
+      <c r="E7" s="56" t="str">
         <v>Food</v>
       </c>
-      <c r="F7" s="72">
-        <v>0</v>
-      </c>
-      <c r="H7" s="62"/>
+      <c r="F7" s="64">
+        <v>0</v>
+      </c>
+      <c r="H7" s="54"/>
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="64" t="str">
+      <c r="C8" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="56" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="F8" s="72">
-        <v>0</v>
-      </c>
-      <c r="H8" s="62"/>
+      <c r="F8" s="64">
+        <v>0</v>
+      </c>
+      <c r="H8" s="54"/>
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="str" cm="1">
         <f t="array" ref="B9:B11">Assets</f>
         <v>Bank 1</v>
       </c>
-      <c r="C9" s="43" cm="1">
+      <c r="C9" s="36" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>150</v>
       </c>
-      <c r="E9" s="64" t="str">
+      <c r="E9" s="56" t="str">
         <v>Hang out</v>
       </c>
-      <c r="F9" s="72">
-        <v>0</v>
-      </c>
-      <c r="H9" s="62"/>
+      <c r="F9" s="64">
+        <v>0</v>
+      </c>
+      <c r="H9" s="54"/>
     </row>
     <row r="10" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="61"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="15" t="str">
         <v>Bank 2</v>
       </c>
-      <c r="C10" s="43" cm="1">
+      <c r="C10" s="36" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E10" s="64" t="str">
+      <c r="E10" s="56" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="F10" s="72">
-        <v>0</v>
-      </c>
-      <c r="H10" s="62"/>
+      <c r="F10" s="64">
+        <v>0</v>
+      </c>
+      <c r="H10" s="54"/>
     </row>
     <row r="11" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="61"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="15" t="str">
         <v>Wallet</v>
       </c>
-      <c r="C11" s="43" cm="1">
+      <c r="C11" s="36" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="64" t="str">
+      <c r="E11" s="56" t="str">
         <v>Insurance</v>
       </c>
-      <c r="F11" s="72">
-        <v>0</v>
-      </c>
-      <c r="H11" s="62"/>
+      <c r="F11" s="64">
+        <v>0</v>
+      </c>
+      <c r="H11" s="54"/>
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="61"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="36">
         <f ca="1">SUM(C9:C11)</f>
         <v>150</v>
       </c>
-      <c r="E12" s="64" t="str">
+      <c r="E12" s="56" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="F12" s="72">
-        <v>0</v>
-      </c>
-      <c r="H12" s="62"/>
+      <c r="F12" s="64">
+        <v>0</v>
+      </c>
+      <c r="H12" s="54"/>
     </row>
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="35">
         <f ca="1">ROUND(C5-C12,2)</f>
         <v>-150</v>
       </c>
-      <c r="E13" s="64" t="str">
+      <c r="E13" s="56" t="str">
         <v>Travel</v>
       </c>
-      <c r="F13" s="72">
-        <v>0</v>
-      </c>
-      <c r="H13" s="62"/>
+      <c r="F13" s="64">
+        <v>0</v>
+      </c>
+      <c r="H13" s="54"/>
     </row>
     <row r="14" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="E14" s="64" t="str">
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="E14" s="56" t="str">
         <v>General expen.</v>
       </c>
-      <c r="F14" s="71">
-        <v>0</v>
-      </c>
-      <c r="H14" s="62"/>
+      <c r="F14" s="63">
+        <v>0</v>
+      </c>
+      <c r="H14" s="54"/>
     </row>
     <row r="15" spans="1:8" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="68"/>
-      <c r="B15" s="62"/>
-      <c r="H15" s="62"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="54"/>
+      <c r="H15" s="54"/>
     </row>
     <row r="16" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="70">
+      <c r="A16" s="62">
         <f>SUBTOTAL(2,Tabela1[Date])</f>
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>45292</v>
       </c>
-      <c r="C17" s="22" t="str">
+      <c r="C17" s="21" t="str">
         <f t="shared" ref="C17:C20" si="0">IF(ISBLANK(B17),"",PROPER(TEXT(B17,"MMMM")))</f>
         <v>Janeiro</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="37">
         <v>150</v>
       </c>
-      <c r="H17" s="24"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="22" t="str">
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="24"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="22" t="str">
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="24"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="22" t="str">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="24"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G23" s="63"/>
+      <c r="G23" s="55"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G25" s="63"/>
+      <c r="G25" s="55"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G26" s="63"/>
+      <c r="G26" s="55"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G27" s="63"/>
+      <c r="G27" s="55"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G28" s="63"/>
+      <c r="G28" s="55"/>
     </row>
     <row r="38" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="62" t="s">
+      <c r="I38" s="54" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="63"/>
+      <c r="G137" s="55"/>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G139" s="63"/>
+      <c r="G139" s="55"/>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G140" s="63"/>
+      <c r="G140" s="55"/>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G141" s="63"/>
+      <c r="G141" s="55"/>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G142" s="63"/>
+      <c r="G142" s="55"/>
     </row>
     <row r="248" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C248" s="61" t="str">
+      <c r="C248" s="53" t="str">
         <f>IF(ISBLANK(B248),"",PROPER(TEXT(B248,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="249" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C249" s="61" t="str">
+      <c r="C249" s="53" t="str">
         <f>IF(ISBLANK(B249),"",PROPER(TEXT(B249,"MMMM")))</f>
         <v/>
       </c>
-      <c r="G249" s="66"/>
+      <c r="G249" s="58"/>
     </row>
     <row r="258" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C258" s="61" t="str">
+      <c r="C258" s="53" t="str">
         <f>IF(ISBLANK(B258),"",PROPER(TEXT(B258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="D258" s="61" t="str">
+      <c r="D258" s="53" t="str">
         <f t="shared" ref="D258:G258" si="1">IF(ISBLANK(C258),"",PROPER(TEXT(C258,"MMMM")))</f>
         <v/>
       </c>
-      <c r="E258" s="61" t="str">
+      <c r="E258" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F258" s="61" t="str">
+      <c r="F258" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="G258" s="61" t="str">
+      <c r="G258" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C267" s="61" t="str">
+      <c r="C267" s="53" t="str">
         <f t="shared" ref="C267" si="2">IF(ISBLANK(B267),"",PROPER(TEXT(B267,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="268" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C268" s="61" t="str">
+      <c r="C268" s="53" t="str">
         <f t="shared" ref="C268:C282" si="3">IF(ISBLANK(B268),"",PROPER(TEXT(B268,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="269" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C269" s="61" t="str">
+      <c r="C269" s="53" t="str">
         <f t="shared" ref="C269:C279" si="4">IF(ISBLANK(B269),"",PROPER(TEXT(B269,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="270" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C270" s="61" t="str">
+      <c r="C270" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="271" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C271" s="61" t="str">
+      <c r="C271" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="272" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C272" s="61" t="str">
+      <c r="C272" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="273" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C273" s="61" t="str">
+      <c r="C273" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="274" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C274" s="61" t="str">
+      <c r="C274" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="275" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C275" s="61" t="str">
+      <c r="C275" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="276" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C276" s="61" t="str">
+      <c r="C276" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="277" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C277" s="61" t="str">
+      <c r="C277" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="278" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C278" s="61" t="str">
+      <c r="C278" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="279" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C279" s="61" t="str">
+      <c r="C279" s="53" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="280" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C280" s="61" t="str">
+      <c r="C280" s="53" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="281" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C281" s="61" t="str">
+      <c r="C281" s="53" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="282" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C282" s="61" t="str">
+      <c r="C282" s="53" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G282" s="63"/>
-      <c r="H282" s="67"/>
+      <c r="G282" s="55"/>
+      <c r="H282" s="59"/>
     </row>
     <row r="283" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B283" s="62"/>
-      <c r="C283" s="62"/>
-      <c r="D283" s="62"/>
-      <c r="E283" s="68"/>
-      <c r="F283" s="68"/>
-      <c r="G283" s="63"/>
-      <c r="H283" s="67"/>
+      <c r="B283" s="54"/>
+      <c r="C283" s="54"/>
+      <c r="D283" s="54"/>
+      <c r="E283" s="60"/>
+      <c r="F283" s="60"/>
+      <c r="G283" s="55"/>
+      <c r="H283" s="59"/>
     </row>
     <row r="284" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B284" s="62"/>
-      <c r="C284" s="62"/>
-      <c r="D284" s="62"/>
-      <c r="E284" s="68"/>
-      <c r="F284" s="68"/>
-      <c r="G284" s="63"/>
-      <c r="H284" s="67"/>
+      <c r="B284" s="54"/>
+      <c r="C284" s="54"/>
+      <c r="D284" s="54"/>
+      <c r="E284" s="60"/>
+      <c r="F284" s="60"/>
+      <c r="G284" s="55"/>
+      <c r="H284" s="59"/>
     </row>
     <row r="285" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B285" s="62"/>
-      <c r="C285" s="62"/>
-      <c r="D285" s="62"/>
-      <c r="E285" s="68"/>
-      <c r="F285" s="68"/>
-      <c r="G285" s="63"/>
-      <c r="H285" s="67"/>
+      <c r="B285" s="54"/>
+      <c r="C285" s="54"/>
+      <c r="D285" s="54"/>
+      <c r="E285" s="60"/>
+      <c r="F285" s="60"/>
+      <c r="G285" s="55"/>
+      <c r="H285" s="59"/>
     </row>
     <row r="286" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B286" s="62"/>
-      <c r="C286" s="69"/>
-      <c r="D286" s="69"/>
-      <c r="E286" s="68"/>
-      <c r="F286" s="68"/>
-      <c r="G286" s="63"/>
-      <c r="H286" s="67"/>
+      <c r="B286" s="54"/>
+      <c r="C286" s="61"/>
+      <c r="D286" s="61"/>
+      <c r="E286" s="60"/>
+      <c r="F286" s="60"/>
+      <c r="G286" s="55"/>
+      <c r="H286" s="59"/>
     </row>
     <row r="287" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B287" s="62"/>
-      <c r="C287" s="62"/>
-      <c r="D287" s="62"/>
-      <c r="G287" s="62"/>
+      <c r="B287" s="54"/>
+      <c r="C287" s="54"/>
+      <c r="D287" s="54"/>
+      <c r="G287" s="54"/>
     </row>
     <row r="288" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B288" s="62"/>
-      <c r="C288" s="62"/>
-      <c r="D288" s="62"/>
-      <c r="G288" s="62"/>
+      <c r="B288" s="54"/>
+      <c r="C288" s="54"/>
+      <c r="D288" s="54"/>
+      <c r="G288" s="54"/>
     </row>
     <row r="289" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B289" s="62"/>
-      <c r="C289" s="62"/>
-      <c r="D289" s="62"/>
-      <c r="G289" s="62"/>
+      <c r="B289" s="54"/>
+      <c r="C289" s="54"/>
+      <c r="D289" s="54"/>
+      <c r="G289" s="54"/>
     </row>
     <row r="290" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B290" s="62"/>
-      <c r="C290" s="62"/>
-      <c r="D290" s="62"/>
-      <c r="G290" s="62"/>
+      <c r="B290" s="54"/>
+      <c r="C290" s="54"/>
+      <c r="D290" s="54"/>
+      <c r="G290" s="54"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B291" s="62"/>
-      <c r="C291" s="62"/>
-      <c r="D291" s="62"/>
-      <c r="G291" s="62"/>
+      <c r="B291" s="54"/>
+      <c r="C291" s="54"/>
+      <c r="D291" s="54"/>
+      <c r="G291" s="54"/>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B292" s="62"/>
-      <c r="C292" s="62"/>
-      <c r="D292" s="62"/>
-      <c r="G292" s="62"/>
+      <c r="B292" s="54"/>
+      <c r="C292" s="54"/>
+      <c r="D292" s="54"/>
+      <c r="G292" s="54"/>
     </row>
     <row r="293" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B293" s="62"/>
-      <c r="C293" s="62"/>
-      <c r="D293" s="62"/>
-      <c r="G293" s="62"/>
+      <c r="B293" s="54"/>
+      <c r="C293" s="54"/>
+      <c r="D293" s="54"/>
+      <c r="G293" s="54"/>
     </row>
     <row r="294" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C294" s="61" t="str">
+      <c r="C294" s="53" t="str">
         <f t="shared" ref="C294:C352" si="5">IF(ISBLANK(B294),"",PROPER(TEXT(B294,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C295" s="61" t="str">
+      <c r="C295" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C296" s="61" t="str">
+      <c r="C296" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C297" s="61" t="str">
+      <c r="C297" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C298" s="61" t="str">
+      <c r="C298" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C299" s="61" t="str">
+      <c r="C299" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C300" s="61" t="str">
+      <c r="C300" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C301" s="61" t="str">
+      <c r="C301" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C302" s="61" t="str">
+      <c r="C302" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C303" s="61" t="str">
+      <c r="C303" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C304" s="61" t="str">
+      <c r="C304" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C305" s="61" t="str">
+      <c r="C305" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C306" s="61" t="str">
+      <c r="C306" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C307" s="61" t="str">
+      <c r="C307" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" s="61" t="str">
+      <c r="C308" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C309" s="61" t="str">
+      <c r="C309" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C310" s="61" t="str">
+      <c r="C310" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C311" s="61" t="str">
+      <c r="C311" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C312" s="61" t="str">
+      <c r="C312" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C313" s="61" t="str">
+      <c r="C313" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C314" s="61" t="str">
+      <c r="C314" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C315" s="61" t="str">
+      <c r="C315" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C316" s="61" t="str">
+      <c r="C316" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C317" s="61" t="str">
+      <c r="C317" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C318" s="61" t="str">
+      <c r="C318" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C319" s="61" t="str">
+      <c r="C319" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C320" s="61" t="str">
+      <c r="C320" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C321" s="61" t="str">
+      <c r="C321" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C322" s="61" t="str">
+      <c r="C322" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C323" s="61" t="str">
+      <c r="C323" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C324" s="61" t="str">
+      <c r="C324" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C325" s="61" t="str">
+      <c r="C325" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C326" s="61" t="str">
+      <c r="C326" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C327" s="61" t="str">
+      <c r="C327" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C328" s="61" t="str">
+      <c r="C328" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C329" s="61" t="str">
+      <c r="C329" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C330" s="61" t="str">
+      <c r="C330" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C331" s="61" t="str">
+      <c r="C331" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C332" s="61" t="str">
+      <c r="C332" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C333" s="61" t="str">
+      <c r="C333" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C334" s="61" t="str">
+      <c r="C334" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C335" s="61" t="str">
+      <c r="C335" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C336" s="61" t="str">
+      <c r="C336" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C337" s="61" t="str">
+      <c r="C337" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C338" s="61" t="str">
+      <c r="C338" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C339" s="61" t="str">
+      <c r="C339" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C340" s="61" t="str">
+      <c r="C340" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C341" s="61" t="str">
+      <c r="C341" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C342" s="61" t="str">
+      <c r="C342" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C343" s="61" t="str">
+      <c r="C343" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C344" s="61" t="str">
+      <c r="C344" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C345" s="61" t="str">
+      <c r="C345" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C346" s="61" t="str">
+      <c r="C346" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C347" s="61" t="str">
+      <c r="C347" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C348" s="61" t="str">
+      <c r="C348" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C349" s="61" t="str">
+      <c r="C349" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C350" s="61" t="str">
+      <c r="C350" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C351" s="61" t="str">
+      <c r="C351" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C352" s="61" t="str">
+      <c r="C352" s="53" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C353" s="61" t="str">
+      <c r="C353" s="53" t="str">
         <f t="shared" ref="C353:C416" si="6">IF(ISBLANK(B353),"",PROPER(TEXT(B353,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C354" s="61" t="str">
+      <c r="C354" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C355" s="61" t="str">
+      <c r="C355" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C356" s="61" t="str">
+      <c r="C356" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C357" s="61" t="str">
+      <c r="C357" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C358" s="61" t="str">
+      <c r="C358" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C359" s="61" t="str">
+      <c r="C359" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C360" s="61" t="str">
+      <c r="C360" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C361" s="61" t="str">
+      <c r="C361" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C362" s="61" t="str">
+      <c r="C362" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C363" s="61" t="str">
+      <c r="C363" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C364" s="61" t="str">
+      <c r="C364" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C365" s="61" t="str">
+      <c r="C365" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C366" s="61" t="str">
+      <c r="C366" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C367" s="61" t="str">
+      <c r="C367" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C368" s="61" t="str">
+      <c r="C368" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C369" s="61" t="str">
+      <c r="C369" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C370" s="61" t="str">
+      <c r="C370" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C371" s="61" t="str">
+      <c r="C371" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C372" s="61" t="str">
+      <c r="C372" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C373" s="61" t="str">
+      <c r="C373" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C374" s="61" t="str">
+      <c r="C374" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C375" s="61" t="str">
+      <c r="C375" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C376" s="61" t="str">
+      <c r="C376" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C377" s="61" t="str">
+      <c r="C377" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C378" s="61" t="str">
+      <c r="C378" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C379" s="61" t="str">
+      <c r="C379" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C380" s="61" t="str">
+      <c r="C380" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C381" s="61" t="str">
+      <c r="C381" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C382" s="61" t="str">
+      <c r="C382" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C383" s="61" t="str">
+      <c r="C383" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C384" s="61" t="str">
+      <c r="C384" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C385" s="61" t="str">
+      <c r="C385" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C386" s="61" t="str">
+      <c r="C386" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C387" s="61" t="str">
+      <c r="C387" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C388" s="61" t="str">
+      <c r="C388" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C389" s="61" t="str">
+      <c r="C389" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C390" s="61" t="str">
+      <c r="C390" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C391" s="61" t="str">
+      <c r="C391" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C392" s="61" t="str">
+      <c r="C392" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C393" s="61" t="str">
+      <c r="C393" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C394" s="61" t="str">
+      <c r="C394" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C395" s="61" t="str">
+      <c r="C395" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C396" s="61" t="str">
+      <c r="C396" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C397" s="61" t="str">
+      <c r="C397" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="398" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C398" s="61" t="str">
+      <c r="C398" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C399" s="61" t="str">
+      <c r="C399" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C400" s="61" t="str">
+      <c r="C400" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C401" s="61" t="str">
+      <c r="C401" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C402" s="61" t="str">
+      <c r="C402" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C403" s="61" t="str">
+      <c r="C403" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C404" s="61" t="str">
+      <c r="C404" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C405" s="61" t="str">
+      <c r="C405" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C406" s="61" t="str">
+      <c r="C406" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C407" s="61" t="str">
+      <c r="C407" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C408" s="61" t="str">
+      <c r="C408" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C409" s="61" t="str">
+      <c r="C409" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C410" s="61" t="str">
+      <c r="C410" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C411" s="61" t="str">
+      <c r="C411" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C412" s="61" t="str">
+      <c r="C412" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C413" s="61" t="str">
+      <c r="C413" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C414" s="61" t="str">
+      <c r="C414" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C415" s="61" t="str">
+      <c r="C415" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C416" s="61" t="str">
+      <c r="C416" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C417" s="61" t="str">
+      <c r="C417" s="53" t="str">
         <f t="shared" ref="C417:C480" si="7">IF(ISBLANK(B417),"",PROPER(TEXT(B417,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="418" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C418" s="61" t="str">
+      <c r="C418" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C419" s="61" t="str">
+      <c r="C419" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C420" s="61" t="str">
+      <c r="C420" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C421" s="61" t="str">
+      <c r="C421" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C422" s="61" t="str">
+      <c r="C422" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C423" s="61" t="str">
+      <c r="C423" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C424" s="61" t="str">
+      <c r="C424" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C425" s="61" t="str">
+      <c r="C425" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C426" s="61" t="str">
+      <c r="C426" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C427" s="61" t="str">
+      <c r="C427" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C428" s="61" t="str">
+      <c r="C428" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C429" s="61" t="str">
+      <c r="C429" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C430" s="61" t="str">
+      <c r="C430" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C431" s="61" t="str">
+      <c r="C431" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C432" s="61" t="str">
+      <c r="C432" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C433" s="61" t="str">
+      <c r="C433" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C434" s="61" t="str">
+      <c r="C434" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C435" s="61" t="str">
+      <c r="C435" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C436" s="61" t="str">
+      <c r="C436" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C437" s="61" t="str">
+      <c r="C437" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C438" s="61" t="str">
+      <c r="C438" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C439" s="61" t="str">
+      <c r="C439" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C440" s="61" t="str">
+      <c r="C440" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C441" s="61" t="str">
+      <c r="C441" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C442" s="61" t="str">
+      <c r="C442" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C443" s="61" t="str">
+      <c r="C443" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C444" s="61" t="str">
+      <c r="C444" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C445" s="61" t="str">
+      <c r="C445" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C446" s="61" t="str">
+      <c r="C446" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C447" s="61" t="str">
+      <c r="C447" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C448" s="61" t="str">
+      <c r="C448" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C449" s="61" t="str">
+      <c r="C449" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C450" s="61" t="str">
+      <c r="C450" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C451" s="61" t="str">
+      <c r="C451" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C452" s="61" t="str">
+      <c r="C452" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C453" s="61" t="str">
+      <c r="C453" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C454" s="61" t="str">
+      <c r="C454" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C455" s="61" t="str">
+      <c r="C455" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C456" s="61" t="str">
+      <c r="C456" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C457" s="61" t="str">
+      <c r="C457" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C458" s="61" t="str">
+      <c r="C458" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C459" s="61" t="str">
+      <c r="C459" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C460" s="61" t="str">
+      <c r="C460" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C461" s="61" t="str">
+      <c r="C461" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C462" s="61" t="str">
+      <c r="C462" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C463" s="61" t="str">
+      <c r="C463" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C464" s="61" t="str">
+      <c r="C464" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C465" s="61" t="str">
+      <c r="C465" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C466" s="61" t="str">
+      <c r="C466" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C467" s="61" t="str">
+      <c r="C467" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C468" s="61" t="str">
+      <c r="C468" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C469" s="61" t="str">
+      <c r="C469" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C470" s="61" t="str">
+      <c r="C470" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C471" s="61" t="str">
+      <c r="C471" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C472" s="61" t="str">
+      <c r="C472" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C473" s="61" t="str">
+      <c r="C473" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C474" s="61" t="str">
+      <c r="C474" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C475" s="61" t="str">
+      <c r="C475" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C476" s="61" t="str">
+      <c r="C476" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C477" s="61" t="str">
+      <c r="C477" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C478" s="61" t="str">
+      <c r="C478" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C479" s="61" t="str">
+      <c r="C479" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C480" s="61" t="str">
+      <c r="C480" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C481" s="61" t="str">
+      <c r="C481" s="53" t="str">
         <f t="shared" ref="C481:C544" si="8">IF(ISBLANK(B481),"",PROPER(TEXT(B481,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="482" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C482" s="61" t="str">
+      <c r="C482" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C483" s="61" t="str">
+      <c r="C483" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C484" s="61" t="str">
+      <c r="C484" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C485" s="61" t="str">
+      <c r="C485" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C486" s="61" t="str">
+      <c r="C486" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C487" s="61" t="str">
+      <c r="C487" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C488" s="61" t="str">
+      <c r="C488" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C489" s="61" t="str">
+      <c r="C489" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C490" s="61" t="str">
+      <c r="C490" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C491" s="61" t="str">
+      <c r="C491" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C492" s="61" t="str">
+      <c r="C492" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C493" s="61" t="str">
+      <c r="C493" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C494" s="61" t="str">
+      <c r="C494" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C495" s="61" t="str">
+      <c r="C495" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C496" s="61" t="str">
+      <c r="C496" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C497" s="61" t="str">
+      <c r="C497" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C498" s="61" t="str">
+      <c r="C498" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C499" s="61" t="str">
+      <c r="C499" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C500" s="61" t="str">
+      <c r="C500" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C501" s="61" t="str">
+      <c r="C501" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C502" s="61" t="str">
+      <c r="C502" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C503" s="61" t="str">
+      <c r="C503" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C504" s="61" t="str">
+      <c r="C504" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C505" s="61" t="str">
+      <c r="C505" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C506" s="61" t="str">
+      <c r="C506" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C507" s="61" t="str">
+      <c r="C507" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C508" s="61" t="str">
+      <c r="C508" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C509" s="61" t="str">
+      <c r="C509" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C510" s="61" t="str">
+      <c r="C510" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C511" s="61" t="str">
+      <c r="C511" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C512" s="61" t="str">
+      <c r="C512" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C513" s="61" t="str">
+      <c r="C513" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C514" s="61" t="str">
+      <c r="C514" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C515" s="61" t="str">
+      <c r="C515" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C516" s="61" t="str">
+      <c r="C516" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C517" s="61" t="str">
+      <c r="C517" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C518" s="61" t="str">
+      <c r="C518" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C519" s="61" t="str">
+      <c r="C519" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C520" s="61" t="str">
+      <c r="C520" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C521" s="61" t="str">
+      <c r="C521" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C522" s="61" t="str">
+      <c r="C522" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C523" s="61" t="str">
+      <c r="C523" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C524" s="61" t="str">
+      <c r="C524" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C525" s="61" t="str">
+      <c r="C525" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C526" s="61" t="str">
+      <c r="C526" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C527" s="61" t="str">
+      <c r="C527" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C528" s="61" t="str">
+      <c r="C528" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C529" s="61" t="str">
+      <c r="C529" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C530" s="61" t="str">
+      <c r="C530" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C531" s="61" t="str">
+      <c r="C531" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C532" s="61" t="str">
+      <c r="C532" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C533" s="61" t="str">
+      <c r="C533" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C534" s="61" t="str">
+      <c r="C534" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C535" s="61" t="str">
+      <c r="C535" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C536" s="61" t="str">
+      <c r="C536" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C537" s="61" t="str">
+      <c r="C537" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C538" s="61" t="str">
+      <c r="C538" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C539" s="61" t="str">
+      <c r="C539" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C540" s="61" t="str">
+      <c r="C540" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C541" s="61" t="str">
+      <c r="C541" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C542" s="61" t="str">
+      <c r="C542" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C543" s="61" t="str">
+      <c r="C543" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C544" s="61" t="str">
+      <c r="C544" s="53" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C545" s="61" t="str">
+      <c r="C545" s="53" t="str">
         <f t="shared" ref="C545:C608" si="9">IF(ISBLANK(B545),"",PROPER(TEXT(B545,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="546" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C546" s="61" t="str">
+      <c r="C546" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C547" s="61" t="str">
+      <c r="C547" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C548" s="61" t="str">
+      <c r="C548" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C549" s="61" t="str">
+      <c r="C549" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C550" s="61" t="str">
+      <c r="C550" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C551" s="61" t="str">
+      <c r="C551" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C552" s="61" t="str">
+      <c r="C552" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C553" s="61" t="str">
+      <c r="C553" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C554" s="61" t="str">
+      <c r="C554" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C555" s="61" t="str">
+      <c r="C555" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C556" s="61" t="str">
+      <c r="C556" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C557" s="61" t="str">
+      <c r="C557" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C558" s="61" t="str">
+      <c r="C558" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C559" s="61" t="str">
+      <c r="C559" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C560" s="61" t="str">
+      <c r="C560" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C561" s="61" t="str">
+      <c r="C561" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C562" s="61" t="str">
+      <c r="C562" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C563" s="61" t="str">
+      <c r="C563" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C564" s="61" t="str">
+      <c r="C564" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C565" s="61" t="str">
+      <c r="C565" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C566" s="61" t="str">
+      <c r="C566" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C567" s="61" t="str">
+      <c r="C567" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C568" s="61" t="str">
+      <c r="C568" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C569" s="61" t="str">
+      <c r="C569" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C570" s="61" t="str">
+      <c r="C570" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C571" s="61" t="str">
+      <c r="C571" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C572" s="61" t="str">
+      <c r="C572" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C573" s="61" t="str">
+      <c r="C573" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C574" s="61" t="str">
+      <c r="C574" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C575" s="61" t="str">
+      <c r="C575" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C576" s="61" t="str">
+      <c r="C576" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C577" s="61" t="str">
+      <c r="C577" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C578" s="61" t="str">
+      <c r="C578" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C579" s="61" t="str">
+      <c r="C579" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C580" s="61" t="str">
+      <c r="C580" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C581" s="61" t="str">
+      <c r="C581" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C582" s="61" t="str">
+      <c r="C582" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C583" s="61" t="str">
+      <c r="C583" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C584" s="61" t="str">
+      <c r="C584" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C585" s="61" t="str">
+      <c r="C585" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C586" s="61" t="str">
+      <c r="C586" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C587" s="61" t="str">
+      <c r="C587" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C588" s="61" t="str">
+      <c r="C588" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C589" s="61" t="str">
+      <c r="C589" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C590" s="61" t="str">
+      <c r="C590" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C591" s="61" t="str">
+      <c r="C591" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C592" s="61" t="str">
+      <c r="C592" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C593" s="61" t="str">
+      <c r="C593" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C594" s="61" t="str">
+      <c r="C594" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C595" s="61" t="str">
+      <c r="C595" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C596" s="61" t="str">
+      <c r="C596" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C597" s="61" t="str">
+      <c r="C597" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C598" s="61" t="str">
+      <c r="C598" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C599" s="61" t="str">
+      <c r="C599" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C600" s="61" t="str">
+      <c r="C600" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C601" s="61" t="str">
+      <c r="C601" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C602" s="61" t="str">
+      <c r="C602" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C603" s="61" t="str">
+      <c r="C603" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C604" s="61" t="str">
+      <c r="C604" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C605" s="61" t="str">
+      <c r="C605" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C606" s="61" t="str">
+      <c r="C606" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C607" s="61" t="str">
+      <c r="C607" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C608" s="61" t="str">
+      <c r="C608" s="53" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C609" s="61" t="str">
+      <c r="C609" s="53" t="str">
         <f t="shared" ref="C609:C672" si="10">IF(ISBLANK(B609),"",PROPER(TEXT(B609,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="610" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C610" s="61" t="str">
+      <c r="C610" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C611" s="61" t="str">
+      <c r="C611" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C612" s="61" t="str">
+      <c r="C612" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C613" s="61" t="str">
+      <c r="C613" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C614" s="61" t="str">
+      <c r="C614" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C615" s="61" t="str">
+      <c r="C615" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C616" s="61" t="str">
+      <c r="C616" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C617" s="61" t="str">
+      <c r="C617" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C618" s="61" t="str">
+      <c r="C618" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C619" s="61" t="str">
+      <c r="C619" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C620" s="61" t="str">
+      <c r="C620" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C621" s="61" t="str">
+      <c r="C621" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C622" s="61" t="str">
+      <c r="C622" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C623" s="61" t="str">
+      <c r="C623" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C624" s="61" t="str">
+      <c r="C624" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C625" s="61" t="str">
+      <c r="C625" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C626" s="61" t="str">
+      <c r="C626" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C627" s="61" t="str">
+      <c r="C627" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C628" s="61" t="str">
+      <c r="C628" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C629" s="61" t="str">
+      <c r="C629" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C630" s="61" t="str">
+      <c r="C630" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C631" s="61" t="str">
+      <c r="C631" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C632" s="61" t="str">
+      <c r="C632" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C633" s="61" t="str">
+      <c r="C633" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C634" s="61" t="str">
+      <c r="C634" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C635" s="61" t="str">
+      <c r="C635" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C636" s="61" t="str">
+      <c r="C636" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C637" s="61" t="str">
+      <c r="C637" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C638" s="61" t="str">
+      <c r="C638" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C639" s="61" t="str">
+      <c r="C639" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C640" s="61" t="str">
+      <c r="C640" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C641" s="61" t="str">
+      <c r="C641" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C642" s="61" t="str">
+      <c r="C642" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C643" s="61" t="str">
+      <c r="C643" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C644" s="61" t="str">
+      <c r="C644" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C645" s="61" t="str">
+      <c r="C645" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C646" s="61" t="str">
+      <c r="C646" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C647" s="61" t="str">
+      <c r="C647" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C648" s="61" t="str">
+      <c r="C648" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C649" s="61" t="str">
+      <c r="C649" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C650" s="61" t="str">
+      <c r="C650" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C651" s="61" t="str">
+      <c r="C651" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C652" s="61" t="str">
+      <c r="C652" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="653" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C653" s="61" t="str">
+      <c r="C653" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C654" s="61" t="str">
+      <c r="C654" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C655" s="61" t="str">
+      <c r="C655" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C656" s="61" t="str">
+      <c r="C656" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C657" s="61" t="str">
+      <c r="C657" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C658" s="61" t="str">
+      <c r="C658" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C659" s="61" t="str">
+      <c r="C659" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C660" s="61" t="str">
+      <c r="C660" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C661" s="61" t="str">
+      <c r="C661" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C662" s="61" t="str">
+      <c r="C662" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C663" s="61" t="str">
+      <c r="C663" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C664" s="61" t="str">
+      <c r="C664" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C665" s="61" t="str">
+      <c r="C665" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C666" s="61" t="str">
+      <c r="C666" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C667" s="61" t="str">
+      <c r="C667" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C668" s="61" t="str">
+      <c r="C668" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C669" s="61" t="str">
+      <c r="C669" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C670" s="61" t="str">
+      <c r="C670" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C671" s="61" t="str">
+      <c r="C671" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C672" s="61" t="str">
+      <c r="C672" s="53" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C673" s="61" t="str">
+      <c r="C673" s="53" t="str">
         <f t="shared" ref="C673:C736" si="11">IF(ISBLANK(B673),"",PROPER(TEXT(B673,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="674" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C674" s="61" t="str">
+      <c r="C674" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C675" s="61" t="str">
+      <c r="C675" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C676" s="61" t="str">
+      <c r="C676" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C677" s="61" t="str">
+      <c r="C677" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C678" s="61" t="str">
+      <c r="C678" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C679" s="61" t="str">
+      <c r="C679" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C680" s="61" t="str">
+      <c r="C680" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C681" s="61" t="str">
+      <c r="C681" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C682" s="61" t="str">
+      <c r="C682" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C683" s="61" t="str">
+      <c r="C683" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C684" s="61" t="str">
+      <c r="C684" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C685" s="61" t="str">
+      <c r="C685" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C686" s="61" t="str">
+      <c r="C686" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C687" s="61" t="str">
+      <c r="C687" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C688" s="61" t="str">
+      <c r="C688" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C689" s="61" t="str">
+      <c r="C689" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C690" s="61" t="str">
+      <c r="C690" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C691" s="61" t="str">
+      <c r="C691" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C692" s="61" t="str">
+      <c r="C692" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C693" s="61" t="str">
+      <c r="C693" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C694" s="61" t="str">
+      <c r="C694" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C695" s="61" t="str">
+      <c r="C695" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C696" s="61" t="str">
+      <c r="C696" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C697" s="61" t="str">
+      <c r="C697" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C698" s="61" t="str">
+      <c r="C698" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="699" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C699" s="61" t="str">
+      <c r="C699" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="700" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C700" s="61" t="str">
+      <c r="C700" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="701" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C701" s="61" t="str">
+      <c r="C701" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="702" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C702" s="61" t="str">
+      <c r="C702" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="703" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C703" s="61" t="str">
+      <c r="C703" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="704" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C704" s="61" t="str">
+      <c r="C704" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="705" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C705" s="61" t="str">
+      <c r="C705" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="706" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C706" s="61" t="str">
+      <c r="C706" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="707" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C707" s="61" t="str">
+      <c r="C707" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="708" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C708" s="61" t="str">
+      <c r="C708" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="709" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C709" s="61" t="str">
+      <c r="C709" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="710" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C710" s="61" t="str">
+      <c r="C710" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="711" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C711" s="61" t="str">
+      <c r="C711" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="712" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C712" s="61" t="str">
+      <c r="C712" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="713" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C713" s="61" t="str">
+      <c r="C713" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="714" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C714" s="61" t="str">
+      <c r="C714" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="715" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C715" s="61" t="str">
+      <c r="C715" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="716" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C716" s="61" t="str">
+      <c r="C716" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="717" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C717" s="61" t="str">
+      <c r="C717" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="718" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C718" s="61" t="str">
+      <c r="C718" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="719" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C719" s="61" t="str">
+      <c r="C719" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="720" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C720" s="61" t="str">
+      <c r="C720" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="721" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C721" s="61" t="str">
+      <c r="C721" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="722" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C722" s="61" t="str">
+      <c r="C722" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="723" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C723" s="61" t="str">
+      <c r="C723" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="724" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C724" s="61" t="str">
+      <c r="C724" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="725" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C725" s="61" t="str">
+      <c r="C725" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="726" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C726" s="61" t="str">
+      <c r="C726" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="727" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C727" s="61" t="str">
+      <c r="C727" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="728" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C728" s="61" t="str">
+      <c r="C728" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="729" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C729" s="61" t="str">
+      <c r="C729" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="730" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C730" s="61" t="str">
+      <c r="C730" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="731" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C731" s="61" t="str">
+      <c r="C731" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="732" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C732" s="61" t="str">
+      <c r="C732" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="733" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C733" s="61" t="str">
+      <c r="C733" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="734" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C734" s="61" t="str">
+      <c r="C734" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="735" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C735" s="61" t="str">
+      <c r="C735" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="736" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C736" s="61" t="str">
+      <c r="C736" s="53" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="737" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C737" s="61" t="str">
+      <c r="C737" s="53" t="str">
         <f t="shared" ref="C737:C785" si="12">IF(ISBLANK(B737),"",PROPER(TEXT(B737,"MMMM")))</f>
         <v/>
       </c>
     </row>
     <row r="738" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C738" s="61" t="str">
+      <c r="C738" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="739" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C739" s="61" t="str">
+      <c r="C739" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="740" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C740" s="61" t="str">
+      <c r="C740" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="741" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C741" s="61" t="str">
+      <c r="C741" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="742" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C742" s="61" t="str">
+      <c r="C742" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="743" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C743" s="61" t="str">
+      <c r="C743" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="744" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C744" s="61" t="str">
+      <c r="C744" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="745" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C745" s="61" t="str">
+      <c r="C745" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="746" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C746" s="61" t="str">
+      <c r="C746" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="747" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C747" s="61" t="str">
+      <c r="C747" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="748" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C748" s="61" t="str">
+      <c r="C748" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="749" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C749" s="61" t="str">
+      <c r="C749" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="750" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C750" s="61" t="str">
+      <c r="C750" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="751" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C751" s="61" t="str">
+      <c r="C751" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="752" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C752" s="61" t="str">
+      <c r="C752" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="753" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C753" s="61" t="str">
+      <c r="C753" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="754" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C754" s="61" t="str">
+      <c r="C754" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="755" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C755" s="61" t="str">
+      <c r="C755" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="756" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C756" s="61" t="str">
+      <c r="C756" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="757" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C757" s="61" t="str">
+      <c r="C757" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="758" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C758" s="61" t="str">
+      <c r="C758" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="759" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C759" s="61" t="str">
+      <c r="C759" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="760" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C760" s="61" t="str">
+      <c r="C760" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="761" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C761" s="61" t="str">
+      <c r="C761" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="762" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C762" s="61" t="str">
+      <c r="C762" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="763" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C763" s="61" t="str">
+      <c r="C763" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="764" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C764" s="61" t="str">
+      <c r="C764" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="765" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C765" s="61" t="str">
+      <c r="C765" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="766" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C766" s="61" t="str">
+      <c r="C766" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="767" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C767" s="61" t="str">
+      <c r="C767" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="768" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C768" s="61" t="str">
+      <c r="C768" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="769" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C769" s="61" t="str">
+      <c r="C769" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="770" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C770" s="61" t="str">
+      <c r="C770" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="771" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C771" s="61" t="str">
+      <c r="C771" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="772" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C772" s="61" t="str">
+      <c r="C772" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="773" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C773" s="61" t="str">
+      <c r="C773" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="774" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C774" s="61" t="str">
+      <c r="C774" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="775" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C775" s="61" t="str">
+      <c r="C775" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="776" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C776" s="61" t="str">
+      <c r="C776" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="777" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C777" s="61" t="str">
+      <c r="C777" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="778" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C778" s="61" t="str">
+      <c r="C778" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="779" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C779" s="61" t="str">
+      <c r="C779" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="780" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C780" s="61" t="str">
+      <c r="C780" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="781" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C781" s="61" t="str">
+      <c r="C781" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="782" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C782" s="61" t="str">
+      <c r="C782" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="783" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C783" s="61" t="str">
+      <c r="C783" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="784" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C784" s="61" t="str">
+      <c r="C784" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="785" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C785" s="61" t="str">
+      <c r="C785" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
@@ -13323,736 +13312,736 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="32" t="str" cm="1">
+      <c r="B2" s="28" t="str" cm="1">
         <f t="array" ref="B2:M2">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="C2" s="32" t="str">
+      <c r="C2" s="28" t="str">
         <v>February</v>
       </c>
-      <c r="D2" s="32" t="str">
+      <c r="D2" s="28" t="str">
         <v>March</v>
       </c>
-      <c r="E2" s="32" t="str">
+      <c r="E2" s="28" t="str">
         <v>April</v>
       </c>
-      <c r="F2" s="32" t="str">
+      <c r="F2" s="28" t="str">
         <v>May</v>
       </c>
-      <c r="G2" s="32" t="str">
+      <c r="G2" s="28" t="str">
         <v>June</v>
       </c>
-      <c r="H2" s="32" t="str">
+      <c r="H2" s="28" t="str">
         <v>July</v>
       </c>
-      <c r="I2" s="32" t="str">
+      <c r="I2" s="28" t="str">
         <v>August</v>
       </c>
-      <c r="J2" s="32" t="str">
+      <c r="J2" s="28" t="str">
         <v>September</v>
       </c>
-      <c r="K2" s="32" t="str">
+      <c r="K2" s="28" t="str">
         <v>October</v>
       </c>
-      <c r="L2" s="32" t="str">
+      <c r="L2" s="28" t="str">
         <v>November</v>
       </c>
-      <c r="M2" s="32" t="str">
+      <c r="M2" s="28" t="str">
         <v>December</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="str" cm="1">
+      <c r="A3" s="30" t="str" cm="1">
         <f t="array" ref="A3:A14">Net_Salary</f>
         <v>Salary</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="43">
+      <c r="J3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="43">
+      <c r="K3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="43">
+      <c r="M3" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="str">
+      <c r="A4" s="30" t="str">
         <v>Seals</v>
       </c>
-      <c r="B4" s="43">
+      <c r="B4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="43">
+      <c r="G4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="43">
+      <c r="J4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="43">
+      <c r="K4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="43">
+      <c r="M4" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="str">
+      <c r="A5" s="30" t="str">
         <v>Rent</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="str">
+      <c r="A6" s="30" t="str">
         <v>Seals II</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="str">
+      <c r="A7" s="30" t="str">
         <v>Other - Income</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43">
+      <c r="K7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="str">
+      <c r="A8" s="30" t="str">
         <v>Tax I</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="str">
+      <c r="A9" s="30" t="str">
         <v>Tax II</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="str">
+      <c r="A10" s="30" t="str">
         <v>Bank Fee I</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="43">
+      <c r="J10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="str">
+      <c r="A11" s="30" t="str">
         <v>Bank Fee II</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="str">
+      <c r="A12" s="30" t="str">
         <v>Other - Discount</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="str">
+      <c r="A13" s="30" t="str">
         <v>Stock Market</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="str">
+      <c r="A14" s="30" t="str">
         <v>Real Estate</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="43">
+      <c r="J14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="43">
+      <c r="L14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="43">
+      <c r="A16" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="36">
         <f>ROUND(SUM(B3:B7)-SUM(B8:B14),2)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="36">
         <f t="shared" ref="C16:M16" si="0">ROUND(SUM(C3:C7)-SUM(C8:C14),2)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L16" s="43">
+      <c r="L16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M16" s="43">
+      <c r="M16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="18.55" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="str">
+      <c r="A18" s="30" t="str">
         <f>A10</f>
         <v>Bank Fee I</v>
       </c>
@@ -14120,215 +14109,215 @@
   <dimension ref="A2:N20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="35" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" style="35" customWidth="1"/>
-    <col min="5" max="10" width="17.85546875" style="35" customWidth="1"/>
-    <col min="11" max="13" width="17.7109375" style="35" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="35" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="35"/>
+    <col min="1" max="1" width="17.140625" style="33" customWidth="1"/>
+    <col min="2" max="4" width="17.7109375" style="33" customWidth="1"/>
+    <col min="5" max="10" width="17.85546875" style="33" customWidth="1"/>
+    <col min="11" max="13" width="17.7109375" style="33" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="33" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="32" t="str" cm="1">
+    <row r="2" spans="1:13" s="31" customFormat="1" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33"/>
+      <c r="B2" s="28" t="str" cm="1">
         <f t="array" ref="B2:M2">TRANSPOSE(Months)</f>
         <v>January</v>
       </c>
-      <c r="C2" s="32" t="str">
+      <c r="C2" s="28" t="str">
         <v>February</v>
       </c>
-      <c r="D2" s="32" t="str">
+      <c r="D2" s="28" t="str">
         <v>March</v>
       </c>
-      <c r="E2" s="32" t="str">
+      <c r="E2" s="28" t="str">
         <v>April</v>
       </c>
-      <c r="F2" s="32" t="str">
+      <c r="F2" s="28" t="str">
         <v>May</v>
       </c>
-      <c r="G2" s="32" t="str">
+      <c r="G2" s="28" t="str">
         <v>June</v>
       </c>
-      <c r="H2" s="32" t="str">
+      <c r="H2" s="28" t="str">
         <v>July</v>
       </c>
-      <c r="I2" s="32" t="str">
+      <c r="I2" s="28" t="str">
         <v>August</v>
       </c>
-      <c r="J2" s="32" t="str">
+      <c r="J2" s="28" t="str">
         <v>September</v>
       </c>
-      <c r="K2" s="32" t="str">
+      <c r="K2" s="28" t="str">
         <v>October</v>
       </c>
-      <c r="L2" s="32" t="str">
+      <c r="L2" s="28" t="str">
         <v>November</v>
       </c>
-      <c r="M2" s="32" t="str">
+      <c r="M2" s="28" t="str">
         <v>December</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="34" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+    <row r="3" spans="1:13" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="78">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="78">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="78">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="78">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="78">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="78">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="78">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="78">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="43">
+      <c r="J3" s="78">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="43">
+      <c r="K3" s="78">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="78">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="43">
+      <c r="M3" s="78">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="57">
+      <c r="B4" s="79">
         <f>B3-(SUM(B7:B18))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="79">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="57">
+      <c r="G4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="57">
+      <c r="H4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="57">
+      <c r="I4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="57">
+      <c r="J4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="57">
+      <c r="K4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="57">
+      <c r="L4" s="79">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="57">
+      <c r="M4" s="79">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="41" t="s">
+      <c r="L6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="41" t="s">
+      <c r="M6" s="28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -14337,51 +14326,51 @@
         <f t="array" ref="A7:A18">Expenses</f>
         <v>Bills</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="43">
+      <c r="J7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43">
+      <c r="K7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="43">
+      <c r="M7" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
@@ -14390,51 +14379,51 @@
       <c r="A8" s="15" t="str">
         <v xml:space="preserve">Car </v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
@@ -14443,51 +14432,51 @@
       <c r="A9" s="15" t="str">
         <v>Clothing</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="43">
+      <c r="J9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43">
+      <c r="K9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="43">
+      <c r="M9" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
@@ -14496,51 +14485,51 @@
       <c r="A10" s="15" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="43">
+      <c r="J10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
@@ -14549,51 +14538,51 @@
       <c r="A11" s="15" t="str">
         <v>Food</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
@@ -14602,51 +14591,51 @@
       <c r="A12" s="15" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43">
+      <c r="K12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="43">
+      <c r="M12" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
@@ -14655,104 +14644,104 @@
       <c r="A13" s="15" t="str">
         <v>Hang out</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43">
+      <c r="K13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="43">
+      <c r="M13" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59" t="str">
+      <c r="A14" s="51" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="43">
+      <c r="J14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="43">
+      <c r="K14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="43">
+      <c r="L14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
@@ -14761,51 +14750,51 @@
       <c r="A15" s="15" t="str">
         <v>Insurance</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="43">
+      <c r="H15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="43">
+      <c r="M15" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
@@ -14814,51 +14803,51 @@
       <c r="A16" s="15" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="43">
+      <c r="K16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="43">
+      <c r="L16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="43">
+      <c r="M16" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
@@ -14867,175 +14856,175 @@
       <c r="A17" s="15" t="str">
         <v>Travel</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="43">
+      <c r="H17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="43">
+      <c r="K17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="43">
+      <c r="M17" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="str">
         <v>General expen.</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="43">
+      <c r="H18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="43">
+      <c r="J18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="43">
+      <c r="K18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="43">
+      <c r="M18" s="78">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-    </row>
-    <row r="20" spans="1:14" s="34" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="58">
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+    </row>
+    <row r="20" spans="1:14" s="32" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="50">
         <f t="shared" ref="B20:M20" si="1">SUM(B7:B18)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="58">
+      <c r="G20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20" s="58">
+      <c r="H20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="58">
+      <c r="I20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="58">
+      <c r="J20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="58">
+      <c r="K20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L20" s="58">
+      <c r="L20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="58">
+      <c r="M20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20" s="36"/>
+      <c r="N20" s="34"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:A17">
@@ -15049,15 +15038,6 @@
       <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="iconSet" priority="1">
-      <iconSet>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="200"/>
-        <cfvo type="num" val="350"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N4:XFD4">
     <cfRule type="iconSet" priority="14">
       <iconSet>
@@ -15077,231 +15057,231 @@
   <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="75" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" style="75" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="75" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="75" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="75" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" style="75" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="75"/>
-    <col min="14" max="14" width="7.140625" style="75" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="75"/>
+    <col min="1" max="1" width="8.5703125" style="67" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" style="67" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" style="67" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="67" customWidth="1"/>
+    <col min="9" max="10" width="17.140625" style="67" customWidth="1"/>
+    <col min="11" max="13" width="9.140625" style="67"/>
+    <col min="14" max="14" width="7.140625" style="67" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="67"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="28" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="38">
+      <c r="B3" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="81">
         <f>SUM(C6:C17)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="38">
+      <c r="I3" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="81">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="75" t="s">
+      <c r="I5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="76" t="s">
+      <c r="J5" s="68" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="75" t="str" cm="1">
+      <c r="B6" s="67" t="str" cm="1">
         <f t="array" ref="B6:B17">Months</f>
         <v>January</v>
       </c>
-      <c r="C6" s="77" cm="1">
+      <c r="C6" s="69" cm="1">
         <f t="array" ref="C6:C17">TRANSPOSE(_xlfn._xlws.FILTER('Net Salary'!B3:M14,Net_Salary='Graphic Categories'!C2))</f>
         <v>0</v>
       </c>
-      <c r="I6" s="75" t="str" cm="1">
+      <c r="I6" s="67" t="str" cm="1">
         <f t="array" ref="I6:I17">Months</f>
         <v>January</v>
       </c>
-      <c r="J6" s="77" cm="1">
+      <c r="J6" s="69" cm="1">
         <f t="array" ref="J6:J17">TRANSPOSE(_xlfn._xlws.FILTER(Expenses!B7:M18,Expenses='Graphic Categories'!J2))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="75" t="str">
+      <c r="B7" s="67" t="str">
         <v>February</v>
       </c>
-      <c r="C7" s="77">
-        <v>0</v>
-      </c>
-      <c r="I7" s="75" t="str">
+      <c r="C7" s="69">
+        <v>0</v>
+      </c>
+      <c r="I7" s="67" t="str">
         <v>February</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="75" t="str">
+      <c r="B8" s="67" t="str">
         <v>March</v>
       </c>
-      <c r="C8" s="77">
-        <v>0</v>
-      </c>
-      <c r="I8" s="75" t="str">
+      <c r="C8" s="69">
+        <v>0</v>
+      </c>
+      <c r="I8" s="67" t="str">
         <v>March</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="75" t="str">
+      <c r="B9" s="67" t="str">
         <v>April</v>
       </c>
-      <c r="C9" s="77">
-        <v>0</v>
-      </c>
-      <c r="I9" s="75" t="str">
+      <c r="C9" s="69">
+        <v>0</v>
+      </c>
+      <c r="I9" s="67" t="str">
         <v>April</v>
       </c>
-      <c r="J9" s="77">
+      <c r="J9" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="75" t="str">
+      <c r="B10" s="67" t="str">
         <v>May</v>
       </c>
-      <c r="C10" s="77">
-        <v>0</v>
-      </c>
-      <c r="I10" s="75" t="str">
+      <c r="C10" s="69">
+        <v>0</v>
+      </c>
+      <c r="I10" s="67" t="str">
         <v>May</v>
       </c>
-      <c r="J10" s="77">
+      <c r="J10" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="75" t="str">
+      <c r="B11" s="67" t="str">
         <v>June</v>
       </c>
-      <c r="C11" s="77">
-        <v>0</v>
-      </c>
-      <c r="I11" s="75" t="str">
+      <c r="C11" s="69">
+        <v>0</v>
+      </c>
+      <c r="I11" s="67" t="str">
         <v>June</v>
       </c>
-      <c r="J11" s="77">
+      <c r="J11" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="75" t="str">
+      <c r="B12" s="67" t="str">
         <v>July</v>
       </c>
-      <c r="C12" s="77">
-        <v>0</v>
-      </c>
-      <c r="I12" s="75" t="str">
+      <c r="C12" s="69">
+        <v>0</v>
+      </c>
+      <c r="I12" s="67" t="str">
         <v>July</v>
       </c>
-      <c r="J12" s="77">
+      <c r="J12" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="75" t="str">
+      <c r="B13" s="67" t="str">
         <v>August</v>
       </c>
-      <c r="C13" s="77">
-        <v>0</v>
-      </c>
-      <c r="I13" s="75" t="str">
+      <c r="C13" s="69">
+        <v>0</v>
+      </c>
+      <c r="I13" s="67" t="str">
         <v>August</v>
       </c>
-      <c r="J13" s="77">
+      <c r="J13" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="75" t="str">
+      <c r="B14" s="67" t="str">
         <v>September</v>
       </c>
-      <c r="C14" s="77">
-        <v>0</v>
-      </c>
-      <c r="I14" s="75" t="str">
+      <c r="C14" s="69">
+        <v>0</v>
+      </c>
+      <c r="I14" s="67" t="str">
         <v>September</v>
       </c>
-      <c r="J14" s="77">
+      <c r="J14" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="75" t="str">
+      <c r="B15" s="67" t="str">
         <v>October</v>
       </c>
-      <c r="C15" s="77">
-        <v>0</v>
-      </c>
-      <c r="I15" s="75" t="str">
+      <c r="C15" s="69">
+        <v>0</v>
+      </c>
+      <c r="I15" s="67" t="str">
         <v>October</v>
       </c>
-      <c r="J15" s="77">
+      <c r="J15" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="75" t="str">
+      <c r="B16" s="67" t="str">
         <v>November</v>
       </c>
-      <c r="C16" s="77">
-        <v>0</v>
-      </c>
-      <c r="I16" s="75" t="str">
+      <c r="C16" s="69">
+        <v>0</v>
+      </c>
+      <c r="I16" s="67" t="str">
         <v>November</v>
       </c>
-      <c r="J16" s="77">
+      <c r="J16" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="75" t="str">
+      <c r="B17" s="67" t="str">
         <v>December</v>
       </c>
-      <c r="C17" s="77">
-        <v>0</v>
-      </c>
-      <c r="I17" s="75" t="str">
+      <c r="C17" s="69">
+        <v>0</v>
+      </c>
+      <c r="I17" s="67" t="str">
         <v>December</v>
       </c>
-      <c r="J17" s="77">
+      <c r="J17" s="69">
         <v>0</v>
       </c>
     </row>
@@ -15371,15 +15351,15 @@
       <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="83" t="s">
+      <c r="K2" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="84"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="83" t="s">
+      <c r="L2" s="76"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="84"/>
+      <c r="O2" s="76"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str" cm="1">
@@ -15387,41 +15367,41 @@
         <v>January</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="45">
+      <c r="C3" s="38">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="39">
         <f>SUM('Net Salary'!B$13:B$14)</f>
         <v>0</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="51">
+      <c r="F3" s="44">
         <f>SUM(Expenses!B20:B20)</f>
         <v>0</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="45">
+      <c r="H3" s="38">
         <f>I3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="48">
+      <c r="I3" s="41">
         <f>Expenses!B4</f>
         <v>0</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="46">
+      <c r="L3" s="39">
         <f>SUM('Net Salary'!B3:M7)</f>
         <v>0</v>
       </c>
       <c r="M3" s="6"/>
-      <c r="N3" s="28" t="str" cm="1">
+      <c r="N3" s="27" t="str" cm="1">
         <f t="array" ref="N3:N14">Expenses</f>
         <v>Bills</v>
       </c>
-      <c r="O3" s="55">
+      <c r="O3" s="48">
         <f>SUM(Expenses!B7:M7)</f>
         <v>0</v>
       </c>
@@ -15431,40 +15411,40 @@
         <v>February</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="45">
+      <c r="C4" s="38">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="39">
         <f>SUM('Net Salary'!C$13:C$14)</f>
         <v>0</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="51">
+      <c r="F4" s="44">
         <f>SUM(Expenses!C20:C20)</f>
         <v>0</v>
       </c>
       <c r="G4" s="7"/>
-      <c r="H4" s="45">
+      <c r="H4" s="38">
         <f t="shared" ref="H4:H14" si="0">I4-I3</f>
         <v>0</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="41">
         <f>Expenses!C4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="46">
+      <c r="L4" s="39">
         <f>SUM('Net Salary'!B8:M12)</f>
         <v>0</v>
       </c>
       <c r="M4" s="6"/>
-      <c r="N4" s="28" t="str">
+      <c r="N4" s="27" t="str">
         <v xml:space="preserve">Car </v>
       </c>
-      <c r="O4" s="55">
+      <c r="O4" s="48">
         <f>SUM(Expenses!B8:M8)</f>
         <v>0</v>
       </c>
@@ -15474,40 +15454,40 @@
         <v>March</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="45">
+      <c r="C5" s="38">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="39">
         <f>SUM('Net Salary'!D$13:D$14)</f>
         <v>0</v>
       </c>
       <c r="E5" s="6"/>
-      <c r="F5" s="51">
+      <c r="F5" s="44">
         <f>SUM(Expenses!D20:D20)</f>
         <v>0</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="45">
+      <c r="H5" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="41">
         <f>Expenses!D4</f>
         <v>0</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="39">
         <f>SUM('Net Salary'!B16:M16)</f>
         <v>0</v>
       </c>
       <c r="M5" s="6"/>
-      <c r="N5" s="28" t="str">
+      <c r="N5" s="27" t="str">
         <v>Clothing</v>
       </c>
-      <c r="O5" s="55">
+      <c r="O5" s="48">
         <f>SUM(Expenses!B9:M9)</f>
         <v>0</v>
       </c>
@@ -15517,40 +15497,40 @@
         <v>April</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="45">
+      <c r="C6" s="38">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="39">
         <f>SUM('Net Salary'!E$13:E$14)</f>
         <v>0</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="51">
+      <c r="F6" s="44">
         <f>SUM(Expenses!E20:E20)</f>
         <v>0</v>
       </c>
       <c r="G6" s="7"/>
-      <c r="H6" s="45">
+      <c r="H6" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="41">
         <f>Expenses!E4</f>
         <v>0</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="K6" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="39">
         <f>SUM(Expenses!B7:B17,Expenses!C7:C17,Expenses!D7:D17,Expenses!E7:E17,Expenses!F7:F17,Expenses!G7:G17,Expenses!H7:H17,Expenses!I7:I17,Expenses!J7:J17,Expenses!K7:K17,Expenses!L7:L17,Expenses!M7:M17)</f>
         <v>0</v>
       </c>
       <c r="M6" s="6"/>
-      <c r="N6" s="28" t="str">
+      <c r="N6" s="27" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="48">
         <f>SUM(Expenses!B10:M10)</f>
         <v>0</v>
       </c>
@@ -15560,40 +15540,40 @@
         <v>May</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="45">
+      <c r="C7" s="38">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="39">
         <f>SUM('Net Salary'!F$13:F$14)</f>
         <v>0</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="51">
+      <c r="F7" s="44">
         <f>SUM(Expenses!F20:F20)</f>
         <v>0</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="45">
+      <c r="H7" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="48">
+      <c r="I7" s="41">
         <f>Expenses!F4</f>
         <v>0</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="46">
+      <c r="L7" s="39">
         <f>SUM(Expenses!B18:B18,Expenses!C18:C18,Expenses!D18:D18,Expenses!E18:E18,Expenses!F18:F18,Expenses!G18:G18,Expenses!H18:H18,Expenses!I18:I18,Expenses!J18:J18,Expenses!K18:K18,Expenses!L18:L18,Expenses!M18:M18)</f>
         <v>0</v>
       </c>
       <c r="M7" s="6"/>
-      <c r="N7" s="28" t="str">
+      <c r="N7" s="27" t="str">
         <v>Food</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="48">
         <f>SUM(Expenses!B11:M11)</f>
         <v>0</v>
       </c>
@@ -15603,40 +15583,40 @@
         <v>June</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="45">
+      <c r="C8" s="38">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="39">
         <f>SUM('Net Salary'!G$13:G$14)</f>
         <v>0</v>
       </c>
       <c r="E8" s="6"/>
-      <c r="F8" s="51">
+      <c r="F8" s="44">
         <f>SUM(Expenses!G20:G20)</f>
         <v>0</v>
       </c>
       <c r="G8" s="7"/>
-      <c r="H8" s="45">
+      <c r="H8" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="48">
+      <c r="I8" s="41">
         <f>Expenses!G4</f>
         <v>0</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="39">
         <f>SUM(L6:L7)</f>
         <v>0</v>
       </c>
       <c r="M8" s="6"/>
-      <c r="N8" s="28" t="str">
+      <c r="N8" s="27" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="O8" s="55">
+      <c r="O8" s="48">
         <f>SUM(Expenses!B12:M12)</f>
         <v>0</v>
       </c>
@@ -15646,40 +15626,40 @@
         <v>July</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="45">
+      <c r="C9" s="38">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="39">
         <f>SUM('Net Salary'!H$13:H$14)</f>
         <v>0</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="51">
+      <c r="F9" s="44">
         <f>SUM(Expenses!H20:H20)</f>
         <v>0</v>
       </c>
       <c r="G9" s="7"/>
-      <c r="H9" s="45">
+      <c r="H9" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9" s="41">
         <f>Expenses!H4</f>
         <v>0</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="48">
+      <c r="L9" s="41">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
       <c r="M9" s="7"/>
-      <c r="N9" s="28" t="str">
+      <c r="N9" s="27" t="str">
         <v>Hang out</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="48">
         <f>SUM(Expenses!B13:M13)</f>
         <v>0</v>
       </c>
@@ -15689,40 +15669,40 @@
         <v>August</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="45">
+      <c r="C10" s="38">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="39">
         <f>SUM('Net Salary'!I$13:I$14)</f>
         <v>0</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="51">
+      <c r="F10" s="44">
         <f>SUM(Expenses!I20:I20)</f>
         <v>0</v>
       </c>
       <c r="G10" s="7"/>
-      <c r="H10" s="45">
+      <c r="H10" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="41">
         <f>Expenses!I4</f>
         <v>0</v>
       </c>
-      <c r="K10" s="27" t="s">
+      <c r="K10" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="50">
+      <c r="L10" s="43">
         <f>'Graphic Annual'!D15</f>
         <v>0</v>
       </c>
       <c r="M10" s="7"/>
-      <c r="N10" s="28" t="str">
+      <c r="N10" s="27" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="O10" s="55">
+      <c r="O10" s="48">
         <f>SUM(Expenses!B14:M14)</f>
         <v>0</v>
       </c>
@@ -15732,34 +15712,34 @@
         <v>September</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="45">
+      <c r="C11" s="38">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="39">
         <f>SUM('Net Salary'!J$13:J$14)</f>
         <v>0</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="51">
+      <c r="F11" s="44">
         <f>SUM(Expenses!J20:J20)</f>
         <v>0</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="45">
+      <c r="H11" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="48">
+      <c r="I11" s="41">
         <f>Expenses!J4</f>
         <v>0</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="26" t="str">
+      <c r="N11" s="25" t="str">
         <v>Insurance</v>
       </c>
-      <c r="O11" s="55">
+      <c r="O11" s="48">
         <f>SUM(Expenses!B15:M15)</f>
         <v>0</v>
       </c>
@@ -15769,34 +15749,34 @@
         <v>October</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="45">
+      <c r="C12" s="38">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="39">
         <f>SUM('Net Salary'!K$13:K$14)</f>
         <v>0</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="51">
+      <c r="F12" s="44">
         <f>SUM(Expenses!K20:K20)</f>
         <v>0</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="45">
+      <c r="H12" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="41">
         <f>Expenses!K4</f>
         <v>0</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="26" t="str">
+      <c r="N12" s="25" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="O12" s="55">
+      <c r="O12" s="48">
         <f>SUM(Expenses!B16:M16)</f>
         <v>0</v>
       </c>
@@ -15807,34 +15787,34 @@
         <v>November</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="45">
+      <c r="C13" s="38">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="39">
         <f>SUM('Net Salary'!L$13:L$14)</f>
         <v>0</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="51">
+      <c r="F13" s="44">
         <f>SUM(Expenses!L20:L20)</f>
         <v>0</v>
       </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="45">
+      <c r="H13" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="41">
         <f>Expenses!L4</f>
         <v>0</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="26" t="str">
+      <c r="N13" s="25" t="str">
         <v>Travel</v>
       </c>
-      <c r="O13" s="55">
+      <c r="O13" s="48">
         <f>SUM(Expenses!B17:M17)</f>
         <v>0</v>
       </c>
@@ -15845,32 +15825,32 @@
         <v>December</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="45">
+      <c r="C14" s="38">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="39">
         <f>SUM('Net Salary'!M$13:M$14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="51">
+      <c r="F14" s="44">
         <f>SUM(Expenses!M20:N20)</f>
         <v>0</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="45">
+      <c r="H14" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="41">
         <f>Expenses!M4</f>
         <v>0</v>
       </c>
-      <c r="N14" s="27" t="str">
+      <c r="N14" s="26" t="str">
         <v>General expen.</v>
       </c>
-      <c r="O14" s="56">
+      <c r="O14" s="49">
         <f>SUM(Expenses!B18:M18)</f>
         <v>0</v>
       </c>
@@ -15880,16 +15860,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="47">
+      <c r="C15" s="40">
         <f>SUM(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="39">
         <f>SUM(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="51">
+      <c r="F15" s="44">
         <f>SUM(F3:F14)</f>
         <v>0</v>
       </c>
@@ -15897,7 +15877,7 @@
       <c r="H15" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="50">
+      <c r="I15" s="43">
         <f>'Graphic Annual'!L9</f>
         <v>0</v>
       </c>
@@ -15907,16 +15887,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="47">
+      <c r="C16" s="40">
         <f>AVERAGE(C3:C14)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="39">
         <f>AVERAGE(D3:D14)</f>
         <v>0</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="52">
+      <c r="F16" s="45">
         <f>AVERAGE(F3:F14)</f>
         <v>0</v>
       </c>
@@ -15929,16 +15909,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="45">
+      <c r="C17" s="38">
         <f>SUM(C3:C8)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="41">
         <f>SUM(D3:D8)</f>
         <v>0</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="53">
+      <c r="F17" s="46">
         <f>SUM(F3:F8)</f>
         <v>0</v>
       </c>
@@ -15950,16 +15930,16 @@
         <v>3</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="49">
+      <c r="C18" s="42">
         <f>SUM($C$9:$C$14)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="43">
         <f>SUM($D$9:$D$14)</f>
         <v>0</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="54">
+      <c r="F18" s="47">
         <f>SUM($F$9:$F$14)</f>
         <v>0</v>
       </c>

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4305E4-7384-4859-8511-AFC34D38E465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5CC3D1-F4E5-480A-BF01-21AE2F02C67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="15" r:id="rId1"/>
     <sheet name="Balance &amp; Tracking" sheetId="12" r:id="rId2"/>
-    <sheet name="Net Salary" sheetId="8" r:id="rId3"/>
-    <sheet name="Expenses" sheetId="1" r:id="rId4"/>
-    <sheet name="Graphic Categories" sheetId="14" r:id="rId5"/>
+    <sheet name="Net Salary" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="Expenses" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Graphic Categories" sheetId="14" state="hidden" r:id="rId5"/>
     <sheet name="Graphic Annual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
@@ -764,12 +764,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -779,6 +773,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13355,51 +13355,51 @@
         <f t="array" ref="A3:A14">Net_Salary</f>
         <v>Salary</v>
       </c>
-      <c r="B3" s="78">
+      <c r="B3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="78">
+      <c r="C3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="78">
+      <c r="D3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="78">
+      <c r="F3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="78">
+      <c r="G3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="78">
+      <c r="H3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="78">
+      <c r="I3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="78">
+      <c r="J3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="78">
+      <c r="K3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="78">
+      <c r="L3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="78">
+      <c r="M3" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A3)</f>
         <v>0</v>
       </c>
@@ -13408,51 +13408,51 @@
       <c r="A4" s="30" t="str">
         <v>Seals</v>
       </c>
-      <c r="B4" s="78">
+      <c r="B4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="78">
+      <c r="F4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="78">
+      <c r="G4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="78">
+      <c r="H4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="78">
+      <c r="I4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="78">
+      <c r="J4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="K4" s="78">
+      <c r="K4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="78">
+      <c r="L4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="78">
+      <c r="M4" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A4)</f>
         <v>0</v>
       </c>
@@ -13461,51 +13461,51 @@
       <c r="A5" s="30" t="str">
         <v>Rent</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="78">
+      <c r="F5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="78">
+      <c r="H5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="78">
+      <c r="I5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="78">
+      <c r="J5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="78">
+      <c r="K5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="78">
+      <c r="L5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="78">
+      <c r="M5" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A5)</f>
         <v>0</v>
       </c>
@@ -13514,51 +13514,51 @@
       <c r="A6" s="30" t="str">
         <v>Seals II</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="78">
+      <c r="F6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="78">
+      <c r="G6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="78">
+      <c r="H6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="78">
+      <c r="I6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="78">
+      <c r="J6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="78">
+      <c r="K6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="78">
+      <c r="L6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="78">
+      <c r="M6" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A6)</f>
         <v>0</v>
       </c>
@@ -13567,51 +13567,51 @@
       <c r="A7" s="30" t="str">
         <v>Other - Income</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="78">
+      <c r="D7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="78">
+      <c r="F7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="78">
+      <c r="G7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="78">
+      <c r="H7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A7)</f>
         <v>0</v>
       </c>
@@ -13620,51 +13620,51 @@
       <c r="A8" s="30" t="str">
         <v>Tax I</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="78">
+      <c r="D8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="78">
+      <c r="F8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="78">
+      <c r="H8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="78">
+      <c r="I8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="78">
+      <c r="J8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="78">
+      <c r="K8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="78">
+      <c r="L8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="78">
+      <c r="M8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A8)</f>
         <v>0</v>
       </c>
@@ -13673,51 +13673,51 @@
       <c r="A9" s="30" t="str">
         <v>Tax II</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="78">
+      <c r="C9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="78">
+      <c r="D9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="78">
+      <c r="F9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="78">
+      <c r="G9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="78">
+      <c r="K9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A9)</f>
         <v>0</v>
       </c>
@@ -13726,51 +13726,51 @@
       <c r="A10" s="30" t="str">
         <v>Bank Fee I</v>
       </c>
-      <c r="B10" s="78">
+      <c r="B10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="78">
+      <c r="F10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="78">
+      <c r="G10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="78">
+      <c r="H10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="78">
+      <c r="I10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="78">
+      <c r="J10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="78">
+      <c r="K10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="78">
+      <c r="L10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A10)</f>
         <v>0</v>
       </c>
@@ -13779,51 +13779,51 @@
       <c r="A11" s="30" t="str">
         <v>Bank Fee II</v>
       </c>
-      <c r="B11" s="78">
+      <c r="B11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="78">
+      <c r="F11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="78">
+      <c r="G11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="78">
+      <c r="H11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="78">
+      <c r="I11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="78">
+      <c r="J11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="78">
+      <c r="K11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="78">
+      <c r="L11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="78">
+      <c r="M11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A11)</f>
         <v>0</v>
       </c>
@@ -13832,51 +13832,51 @@
       <c r="A12" s="30" t="str">
         <v>Other - Discount</v>
       </c>
-      <c r="B12" s="78">
+      <c r="B12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="78">
+      <c r="F12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="78">
+      <c r="G12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="78">
+      <c r="H12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="78">
+      <c r="I12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="78">
+      <c r="J12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="78">
+      <c r="K12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="78">
+      <c r="L12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="78">
+      <c r="M12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A12)</f>
         <v>0</v>
       </c>
@@ -13885,51 +13885,51 @@
       <c r="A13" s="30" t="str">
         <v>Stock Market</v>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="78">
+      <c r="F13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="78">
+      <c r="G13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="78">
+      <c r="I13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="78">
+      <c r="J13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="78">
+      <c r="K13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="78">
+      <c r="L13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="78">
+      <c r="M13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A13)</f>
         <v>0</v>
       </c>
@@ -13938,51 +13938,51 @@
       <c r="A14" s="30" t="str">
         <v>Real Estate</v>
       </c>
-      <c r="B14" s="78">
+      <c r="B14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],B$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],C$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="78">
+      <c r="D14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],D$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="78">
+      <c r="E14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],E$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="78">
+      <c r="F14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],F$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="78">
+      <c r="G14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],G$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="78">
+      <c r="H14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],H$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="78">
+      <c r="I14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],I$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="78">
+      <c r="J14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],J$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="78">
+      <c r="K14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],K$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="78">
+      <c r="L14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],L$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="78">
+      <c r="M14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],M$2,Tabela1[Category],$A14)</f>
         <v>0</v>
       </c>
@@ -14160,107 +14160,107 @@
       </c>
     </row>
     <row r="3" spans="1:13" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="78">
+      <c r="B3" s="76">
         <f>'Net Salary'!B16</f>
         <v>0</v>
       </c>
-      <c r="C3" s="78">
+      <c r="C3" s="76">
         <f>'Net Salary'!C16</f>
         <v>0</v>
       </c>
-      <c r="D3" s="78">
+      <c r="D3" s="76">
         <f>'Net Salary'!D16</f>
         <v>0</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="76">
         <f>'Net Salary'!E16</f>
         <v>0</v>
       </c>
-      <c r="F3" s="78">
+      <c r="F3" s="76">
         <f>'Net Salary'!F16</f>
         <v>0</v>
       </c>
-      <c r="G3" s="78">
+      <c r="G3" s="76">
         <f>'Net Salary'!G16</f>
         <v>0</v>
       </c>
-      <c r="H3" s="78">
+      <c r="H3" s="76">
         <f>'Net Salary'!H16</f>
         <v>0</v>
       </c>
-      <c r="I3" s="78">
+      <c r="I3" s="76">
         <f>'Net Salary'!I16</f>
         <v>0</v>
       </c>
-      <c r="J3" s="78">
+      <c r="J3" s="76">
         <f>'Net Salary'!J16</f>
         <v>0</v>
       </c>
-      <c r="K3" s="78">
+      <c r="K3" s="76">
         <f>'Net Salary'!K16</f>
         <v>0</v>
       </c>
-      <c r="L3" s="78">
+      <c r="L3" s="76">
         <f>'Net Salary'!L16</f>
         <v>0</v>
       </c>
-      <c r="M3" s="78">
+      <c r="M3" s="76">
         <f>'Net Salary'!M16</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="77">
         <f>B3-(SUM(B7:B18))</f>
         <v>0</v>
       </c>
-      <c r="C4" s="79">
+      <c r="C4" s="77">
         <f t="shared" ref="C4:L4" si="0">C3-(SUM(C7:C18))+B4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="79">
+      <c r="E4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="79">
+      <c r="G4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="79">
+      <c r="H4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I4" s="79">
+      <c r="I4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J4" s="79">
+      <c r="J4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K4" s="79">
+      <c r="K4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L4" s="79">
+      <c r="L4" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M4" s="79">
+      <c r="M4" s="77">
         <f>M3-SUM(M7:M18)+L4</f>
         <v>0</v>
       </c>
@@ -14326,51 +14326,51 @@
         <f t="array" ref="A7:A18">Expenses</f>
         <v>Bills</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="78">
+      <c r="D7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="78">
+      <c r="F7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="78">
+      <c r="G7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="78">
+      <c r="H7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A7)</f>
         <v>0</v>
       </c>
@@ -14379,51 +14379,51 @@
       <c r="A8" s="15" t="str">
         <v xml:space="preserve">Car </v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="78">
+      <c r="D8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="78">
+      <c r="F8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="78">
+      <c r="H8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="78">
+      <c r="I8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="78">
+      <c r="J8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="78">
+      <c r="K8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="78">
+      <c r="L8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="78">
+      <c r="M8" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A8)</f>
         <v>0</v>
       </c>
@@ -14432,51 +14432,51 @@
       <c r="A9" s="15" t="str">
         <v>Clothing</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="78">
+      <c r="C9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="78">
+      <c r="D9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="78">
+      <c r="F9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="78">
+      <c r="G9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="78">
+      <c r="K9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A9)</f>
         <v>0</v>
       </c>
@@ -14485,51 +14485,51 @@
       <c r="A10" s="15" t="str">
         <v>Eletron n' games</v>
       </c>
-      <c r="B10" s="78">
+      <c r="B10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="78">
+      <c r="F10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="78">
+      <c r="G10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="78">
+      <c r="H10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="78">
+      <c r="I10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="78">
+      <c r="J10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="78">
+      <c r="K10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="78">
+      <c r="L10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A10)</f>
         <v>0</v>
       </c>
@@ -14538,51 +14538,51 @@
       <c r="A11" s="15" t="str">
         <v>Food</v>
       </c>
-      <c r="B11" s="78">
+      <c r="B11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="78">
+      <c r="F11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="78">
+      <c r="G11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="78">
+      <c r="H11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="78">
+      <c r="I11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="78">
+      <c r="J11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="78">
+      <c r="K11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="78">
+      <c r="L11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="78">
+      <c r="M11" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A11)</f>
         <v>0</v>
       </c>
@@ -14591,51 +14591,51 @@
       <c r="A12" s="15" t="str">
         <v>Gasolina</v>
       </c>
-      <c r="B12" s="78">
+      <c r="B12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="78">
+      <c r="F12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="78">
+      <c r="G12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="78">
+      <c r="H12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="78">
+      <c r="I12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="78">
+      <c r="J12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="78">
+      <c r="K12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="78">
+      <c r="L12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="78">
+      <c r="M12" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A12)</f>
         <v>0</v>
       </c>
@@ -14644,51 +14644,51 @@
       <c r="A13" s="15" t="str">
         <v>Hang out</v>
       </c>
-      <c r="B13" s="78">
+      <c r="B13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="78">
+      <c r="F13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="78">
+      <c r="G13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="78">
+      <c r="I13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="78">
+      <c r="J13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="78">
+      <c r="K13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="78">
+      <c r="L13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="78">
+      <c r="M13" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A13)</f>
         <v>0</v>
       </c>
@@ -14697,51 +14697,51 @@
       <c r="A14" s="51" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="B14" s="78">
+      <c r="B14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="78">
+      <c r="D14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="78">
+      <c r="E14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="78">
+      <c r="F14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="78">
+      <c r="G14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="78">
+      <c r="H14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="78">
+      <c r="I14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="78">
+      <c r="J14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="78">
+      <c r="K14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="78">
+      <c r="L14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="78">
+      <c r="M14" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A14)</f>
         <v>0</v>
       </c>
@@ -14750,51 +14750,51 @@
       <c r="A15" s="15" t="str">
         <v>Insurance</v>
       </c>
-      <c r="B15" s="78">
+      <c r="B15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="78">
+      <c r="E15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="78">
+      <c r="F15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="78">
+      <c r="G15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="78">
+      <c r="H15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="I15" s="78">
+      <c r="I15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="78">
+      <c r="J15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="78">
+      <c r="K15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="78">
+      <c r="L15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="78">
+      <c r="M15" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A15)</f>
         <v>0</v>
       </c>
@@ -14803,51 +14803,51 @@
       <c r="A16" s="15" t="str">
         <v>Personal Care</v>
       </c>
-      <c r="B16" s="78">
+      <c r="B16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="78">
+      <c r="E16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="78">
+      <c r="F16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="78">
+      <c r="G16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="78">
+      <c r="H16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="78">
+      <c r="I16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="78">
+      <c r="J16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="78">
+      <c r="K16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="78">
+      <c r="L16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="78">
+      <c r="M16" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A16)</f>
         <v>0</v>
       </c>
@@ -14856,51 +14856,51 @@
       <c r="A17" s="15" t="str">
         <v>Travel</v>
       </c>
-      <c r="B17" s="78">
+      <c r="B17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="78">
+      <c r="D17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="78">
+      <c r="F17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="78">
+      <c r="G17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="78">
+      <c r="H17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="78">
+      <c r="I17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="78">
+      <c r="J17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="78">
+      <c r="K17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="78">
+      <c r="L17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="78">
+      <c r="M17" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A17)</f>
         <v>0</v>
       </c>
@@ -14909,51 +14909,51 @@
       <c r="A18" s="15" t="str">
         <v>General expen.</v>
       </c>
-      <c r="B18" s="78">
+      <c r="B18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!B$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="78">
+      <c r="C18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!C$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="78">
+      <c r="D18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!D$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!E$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="78">
+      <c r="F18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!F$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="78">
+      <c r="G18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!G$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="78">
+      <c r="H18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!H$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="78">
+      <c r="I18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!I$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="78">
+      <c r="J18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!J$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="78">
+      <c r="K18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!K$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="78">
+      <c r="L18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!L$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="78">
+      <c r="M18" s="76">
         <f>SUMIFS(Tabela1[Amount],Tabela1[Month],Expenses!M$2,Tabela1[Category],Expenses!$A18)</f>
         <v>0</v>
       </c>
@@ -15084,17 +15084,17 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="81">
+      <c r="B3" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="79">
         <f>SUM(C6:C17)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="81">
+      <c r="I3" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="79">
         <f>SUM(J6:J17)</f>
         <v>0</v>
       </c>
@@ -15351,15 +15351,15 @@
       <c r="I2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="75" t="s">
+      <c r="K2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="76"/>
+      <c r="L2" s="81"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="75" t="s">
+      <c r="N2" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="76"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str" cm="1">

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD76F50-314A-46EB-B4CF-07E4C5085A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F84E09-515A-4E60-B7E3-C3B9F395CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,17 +18,26 @@
     <sheet name="Net Salary" sheetId="8" state="hidden" r:id="rId3"/>
     <sheet name="Expenses" sheetId="1" state="hidden" r:id="rId4"/>
     <sheet name="Graphic Categories" sheetId="14" state="hidden" r:id="rId5"/>
-    <sheet name="Graphic Annual" sheetId="13" r:id="rId6"/>
+    <sheet name="Goals" sheetId="16" state="hidden" r:id="rId6"/>
+    <sheet name="Graphic Annual" sheetId="13" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="Accounts" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Accounts">'Data Validation'!$B$5:$B$8</definedName>
     <definedName name="Dash">'Graphic Annual'!$A$1:$P$26</definedName>
+    <definedName name="Discount" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Discount">'Data Validation'!$H$5:$H$9</definedName>
+    <definedName name="Expenses" localSheetId="5">Goals!$D$5:$D$16</definedName>
     <definedName name="Expenses">'Data Validation'!$D$5:$D$16</definedName>
+    <definedName name="Income" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Income">'Data Validation'!$J$5:$J$9</definedName>
+    <definedName name="Investments" localSheetId="5">Goals!$E$5:$E$6</definedName>
     <definedName name="Investments">'Data Validation'!$F$5:$F$6</definedName>
+    <definedName name="Months" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Months">'Data Validation'!$P$5:$P$16</definedName>
+    <definedName name="Net_Salary" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Net_Salary">'Data Validation'!$N$5:$N$16</definedName>
+    <definedName name="Transfer" localSheetId="5">Goals!#REF!</definedName>
     <definedName name="Transfer">'Data Validation'!$L$5:$L$8</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="3" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
   </definedNames>
@@ -75,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="87">
   <si>
     <t>Total</t>
   </si>
@@ -309,6 +318,33 @@
   </si>
   <si>
     <t>Account</t>
+  </si>
+  <si>
+    <t>Goals</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Iphone</t>
+  </si>
+  <si>
+    <t>Console PS5</t>
+  </si>
+  <si>
+    <t>New Car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel </t>
+  </si>
+  <si>
+    <t>Input Goal</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>*Feel free to change the golas and their values as you wish.</t>
   </si>
 </sst>
 </file>
@@ -592,7 +628,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -779,6 +815,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -15306,6 +15349,236 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492BBBFB-0958-43BD-B792-1E8101351275}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
+  <dimension ref="C2:I16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="3.5703125" style="72" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="72" customWidth="1"/>
+    <col min="4" max="6" width="17.140625" style="72" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="72"/>
+    <col min="8" max="9" width="14.28515625" style="72" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="72"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C2" s="72" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" ht="15" x14ac:dyDescent="0.3">
+      <c r="D4" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="28" t="str">
+        <f>'Balance &amp; Tracking'!B12</f>
+        <v>Savings</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="83">
+        <v>450</v>
+      </c>
+      <c r="F5" s="84">
+        <f ca="1">$I$5/E5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="83">
+        <f ca="1">'Balance &amp; Tracking'!C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D6" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="83">
+        <v>350</v>
+      </c>
+      <c r="F6" s="84">
+        <f ca="1">$I$5/E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D7" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="83">
+        <v>12000</v>
+      </c>
+      <c r="F7" s="84">
+        <f ca="1">$I$5/E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D8" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="83">
+        <v>2500</v>
+      </c>
+      <c r="F8" s="84">
+        <f ca="1">$I$5/E8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D9" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="83">
+        <v>1</v>
+      </c>
+      <c r="F9" s="84">
+        <f ca="1">$I$5/E9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D10" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="83">
+        <v>1</v>
+      </c>
+      <c r="F10" s="84">
+        <f ca="1">$I$5/E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D11" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="83">
+        <v>1</v>
+      </c>
+      <c r="F11" s="84">
+        <f ca="1">$I$5/E11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="83">
+        <v>1</v>
+      </c>
+      <c r="F12" s="84">
+        <f ca="1">$I$5/E12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="83">
+        <v>1</v>
+      </c>
+      <c r="F13" s="84">
+        <f ca="1">$I$5/E13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D14" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="83">
+        <v>1</v>
+      </c>
+      <c r="F14" s="84">
+        <f ca="1">$I$5/E14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="83">
+        <v>1</v>
+      </c>
+      <c r="F15" s="84">
+        <f ca="1">$I$5/E15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D16" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="83">
+        <v>1</v>
+      </c>
+      <c r="F16" s="84">
+        <f ca="1">$I$5/E16</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{91AF8D87-94DF-460F-8F09-5DC272DAEDFD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{91AF8D87-94DF-460F-8F09-5DC272DAEDFD}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F5:F16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD330F4-3FAE-447F-BF05-82EFBCBD7BD0}">
   <sheetPr codeName="Planilha6">
     <tabColor theme="1"/>

--- a/Personal Budget.xlsx
+++ b/Personal Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5CC3D1-F4E5-480A-BF01-21AE2F02C67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD76F50-314A-46EB-B4CF-07E4C5085A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="792" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Graphic Annual" sheetId="13" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Assets">'Data Validation'!$B$5:$B$7</definedName>
+    <definedName name="Accounts">'Data Validation'!$B$5:$B$8</definedName>
     <definedName name="Dash">'Graphic Annual'!$A$1:$P$26</definedName>
     <definedName name="Discount">'Data Validation'!$H$5:$H$9</definedName>
     <definedName name="Expenses">'Data Validation'!$D$5:$D$16</definedName>
@@ -29,7 +29,7 @@
     <definedName name="Investments">'Data Validation'!$F$5:$F$6</definedName>
     <definedName name="Months">'Data Validation'!$P$5:$P$16</definedName>
     <definedName name="Net_Salary">'Data Validation'!$N$5:$N$16</definedName>
-    <definedName name="Transfer">'Data Validation'!$L$5:$L$7</definedName>
+    <definedName name="Transfer">'Data Validation'!$L$5:$L$8</definedName>
     <definedName name="Z_12641207_4FA9_4498_AEA1_9BC1962A4F9A_.wvu.Rows" localSheetId="3" hidden="1">Expenses!$6:$6,Expenses!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -158,9 +158,6 @@
     <t>Wallet</t>
   </si>
   <si>
-    <t>Real Balance</t>
-  </si>
-  <si>
     <t>Difference</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>Allocation</t>
   </si>
   <si>
     <t>Description</t>
@@ -284,9 +278,6 @@
     <t>Bank Fee I</t>
   </si>
   <si>
-    <t>Assets</t>
-  </si>
-  <si>
     <t>Debt/ Income</t>
   </si>
   <si>
@@ -309,6 +300,15 @@
   </si>
   <si>
     <t>*Feel free to change the blue values as you wish. However, if you need to remove or add new values, you may need to adjust the spreadsheet accordingly.</t>
+  </si>
+  <si>
+    <t>Savings</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>Account</t>
   </si>
 </sst>
 </file>
@@ -9165,7 +9165,7 @@
     </tableColumn>
     <tableColumn id="6" xr3:uid="{23818CCC-08C7-4066-9B86-98D831460C75}" name="Operation" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{78815540-1C3C-4370-A3E4-1C8E033CFC39}" name="Category" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F153B94E-6C60-4C63-A86C-8519A94E1F13}" name="Allocation" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F153B94E-6C60-4C63-A86C-8519A94E1F13}" name="Account" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{EE54C9A2-2D53-4D6A-93DF-88B691A8C3D9}" name="Amount" dataDxfId="3" dataCellStyle="Moeda"/>
     <tableColumn id="5" xr3:uid="{28149A80-D409-4A63-B4C2-6EDA92C21F54}" name="Description" dataDxfId="2"/>
   </tableColumns>
@@ -9487,33 +9487,33 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="2:16" ht="15" x14ac:dyDescent="0.3">
       <c r="B4" s="28" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P4" s="28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
@@ -9521,19 +9521,19 @@
         <v>24</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H5" s="73" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J5" s="73" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L5" s="74" t="str" cm="1">
-        <f t="array" ref="L5:L7">Assets</f>
+        <f t="array" ref="L5:L8">Accounts</f>
         <v>Bank 1</v>
       </c>
       <c r="N5" s="74" t="str" cm="1">
@@ -9549,16 +9549,16 @@
         <v>25</v>
       </c>
       <c r="D6" s="73" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H6" s="73" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J6" s="73" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L6" s="74" t="str">
         <v>Bank 2</v>
@@ -9575,13 +9575,13 @@
         <v>26</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="73" t="s">
         <v>68</v>
-      </c>
-      <c r="J7" s="73" t="s">
-        <v>71</v>
       </c>
       <c r="L7" s="74" t="str">
         <v>Wallet</v>
@@ -9594,14 +9594,20 @@
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="73" t="s">
+        <v>75</v>
+      </c>
       <c r="D8" s="73" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H8" s="73" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J8" s="73" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="L8" s="74" t="str">
+        <v>Savings</v>
       </c>
       <c r="N8" s="74" t="str">
         <v>Seals II</v>
@@ -9612,13 +9618,13 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D9" s="73" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H9" s="73" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J9" s="73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N9" s="74" t="str">
         <v>Other - Income</v>
@@ -9641,7 +9647,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D11" s="73" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N11" s="74" t="str">
         <v>Tax II</v>
@@ -9652,7 +9658,7 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D12" s="73" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N12" s="74" t="str">
         <v>Bank Fee I</v>
@@ -9663,7 +9669,7 @@
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D13" s="73" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N13" s="74" t="str">
         <v>Bank Fee II</v>
@@ -9674,7 +9680,7 @@
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D14" s="73" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N14" s="74" t="str">
         <v>Other - Discount</v>
@@ -9685,7 +9691,7 @@
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D15" s="73" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N15" s="74" t="str" cm="1">
         <f t="array" ref="N15:N16">Investments</f>
@@ -9697,7 +9703,7 @@
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="D16" s="73" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N16" s="74" t="str">
         <v>Real Estate</v>
@@ -9766,7 +9772,7 @@
     </row>
     <row r="4" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" s="71" t="e">
         <f>HLOOKUP(B2,Expenses!B2:M20,19,FALSE)/HLOOKUP(B2,'Net Salary'!B2:M16,15,FALSE)</f>
@@ -9823,7 +9829,7 @@
     </row>
     <row r="8" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="28" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>0</v>
@@ -9838,11 +9844,11 @@
     </row>
     <row r="9" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="str" cm="1">
-        <f t="array" ref="B9:B11">Assets</f>
+        <f t="array" ref="B9:B12">Accounts</f>
         <v>Bank 1</v>
       </c>
       <c r="C9" s="36" cm="1">
-        <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C9" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Account],B9,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Account],B9,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B9,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>150</v>
       </c>
       <c r="E9" s="56" t="str">
@@ -9859,7 +9865,7 @@
         <v>Bank 2</v>
       </c>
       <c r="C10" s="36" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C10" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Account],B10,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Account],B10,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B10,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E10" s="56" t="str">
@@ -9876,7 +9882,7 @@
         <v>Wallet</v>
       </c>
       <c r="C11" s="36" cm="1">
-        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Allocation],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <f t="array" aca="1" ref="C11" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Account],B11,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Account],B11,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B11,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E11" s="56" t="str">
@@ -9889,12 +9895,12 @@
     </row>
     <row r="12" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="53"/>
-      <c r="B12" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="36">
-        <f ca="1">SUM(C9:C11)</f>
-        <v>150</v>
+      <c r="B12" s="15" t="str">
+        <v>Savings</v>
+      </c>
+      <c r="C12" s="36" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">SUM(SUMIFS(Tabela1[Amount],Tabela1[Operation],{"Income";"Transfer"},Tabela1[Account],B12,Tabela1[Date],"&lt;="&amp;(TODAY())))-SUMIFS(Tabela1[Amount],Tabela1[Operation],"&lt;&gt;Income",Tabela1[Operation],"&lt;&gt;Transfer",Tabela1[Account],B12,Tabela1[Date],"&lt;="&amp;(TODAY())) - SUMIFS(Tabela1[Amount],Tabela1[Category],B12,Tabela1[Date],"&lt;="&amp;(TODAY()))</f>
+        <v>0</v>
       </c>
       <c r="E12" s="56" t="str">
         <v>Personal Care</v>
@@ -9907,10 +9913,10 @@
     <row r="13" spans="1:8" ht="14.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53"/>
       <c r="B13" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="35">
-        <f ca="1">ROUND(C5-C12,2)</f>
+        <f ca="1">ROUND(C5-SUM(C9:C12),2)</f>
         <v>-150</v>
       </c>
       <c r="E13" s="56" t="str">
@@ -9944,25 +9950,25 @@
         <v>1</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="18" t="s">
-        <v>31</v>
-      </c>
       <c r="F16" s="18" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="13.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -9974,10 +9980,10 @@
         <v>Janeiro</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>24</v>
@@ -13256,7 +13262,7 @@
       <formula1>"Receitas, Perdas, Investimentos, Despesas, Transferir"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17:F257" xr:uid="{0D51CC9B-6F94-4F85-BAFC-26C786BB30BC}">
-      <formula1>Assets</formula1>
+      <formula1>Accounts</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17:D20" xr:uid="{0261ACD4-BAB2-4EA0-87AC-74F751F397E2}">
       <formula1>"Income, Discount, Investments, Expenses, Transfer"</formula1>
@@ -14161,7 +14167,7 @@
     </row>
     <row r="3" spans="1:13" s="32" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="75" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="76">
         <f>'Net Salary'!B16</f>
@@ -14282,7 +14288,7 @@
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>20</v>
@@ -15071,16 +15077,16 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I2" s="28" t="s">
         <v>21</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
@@ -15335,10 +15341,10 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3" t="s">
@@ -15346,18 +15352,18 @@
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="80" t="s">
         <v>39</v>
-      </c>
-      <c r="K2" s="80" t="s">
-        <v>41</v>
       </c>
       <c r="L2" s="81"/>
       <c r="M2" s="24"/>
       <c r="N2" s="80" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O2" s="81"/>
     </row>
@@ -15390,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L3" s="39">
         <f>SUM('Net Salary'!B3:M7)</f>
@@ -15434,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L4" s="39">
         <f>SUM('Net Salary'!B8:M12)</f>
@@ -15477,7 +15483,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L5" s="39">
         <f>SUM('Net Salary'!B16:M16)</f>
@@ -15520,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L6" s="39">
         <f>SUM(Expenses!B7:B17,Expenses!C7:C17,Expenses!D7:D17,Expenses!E7:E17,Expenses!F7:F17,Expenses!G7:G17,Expenses!H7:H17,Expenses!I7:I17,Expenses!J7:J17,Expenses!K7:K17,Expenses!L7:L17,Expenses!M7:M17)</f>
@@ -15563,7 +15569,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L7" s="39">
         <f>SUM(Expenses!B18:B18,Expenses!C18:C18,Expenses!D18:D18,Expenses!E18:E18,Expenses!F18:F18,Expenses!G18:G18,Expenses!H18:H18,Expenses!I18:I18,Expenses!J18:J18,Expenses!K18:K18,Expenses!L18:L18,Expenses!M18:M18)</f>
@@ -15606,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L8" s="39">
         <f>SUM(L6:L7)</f>
@@ -15649,7 +15655,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L9" s="41">
         <f>Expenses!M4</f>
@@ -15692,7 +15698,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L10" s="43">
         <f>'Graphic Annual'!D15</f>
@@ -15875,7 +15881,7 @@
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I15" s="43">
         <f>'Graphic Annual'!L9</f>
@@ -15884,7 +15890,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="40">
